--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -18707,7 +18707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 26 October 2026.</t>
+          <t>Last updated: 27 October 2026.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
@@ -18918,7 +18918,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Last updated: 26 October 2026.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Last updated: 27 October 2026.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19381,12 +19381,12 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>list item</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>We don't use cookies, tracking pixels, advertising or outside analytics, and we don't track whether you open our emails. While you have a file open, your browser keeps your personal link for that visit only, so the page can save your answers.</t>
+          <t>&lt;b&gt;Short security notes&lt;/b&gt;, so we can spot and look into misuse: for example, when a link is refused, when someone is blocked for trying too often, and when you confirm, pause, resume, unsubscribe or delete your data. They use our internal number for you, never your email address, your link or your internet address.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;We don't use cookies, tracking pixels, advertising or outside analytics, and we don't track whether you open our emails. While you have a file open, your browser keeps your personal link for that visit only, so the page can save your answers.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Short security notes&lt;/b&gt;, so we can spot and look into misuse: for example, when a link is refused, when someone is blocked for trying too often, and when you confirm, pause, resume, unsubscribe or delete your data. They use our internal number for you, never your email address, your link or your internet address.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19413,12 +19413,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>paragraph</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Our legal basis</t>
+          <t>We don't use cookies, tracking pixels, advertising or outside analytics, and we don't track whether you open our emails. While you have a file open, your browser keeps your personal link for that visit only, so the page can save your answers.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Our legal basis&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;We don't use cookies, tracking pixels, advertising or outside analytics, and we don't track whether you open our emails. While you have a file open, your browser keeps your personal link for that visit only, so the page can save your answers.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19445,12 +19445,12 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>We rely on your consent, which you give when you sign up and confirm your email. It covers the monthly emails, keeping your answers and flight recorder, and recording which screens you reach so we can improve the scenarios.</t>
+          <t>Our legal basis</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
@@ -19462,7 +19462,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;We rely on your consent, which you give when you sign up and confirm your email. It covers the monthly emails, keeping your answers and flight recorder, and recording which screens you reach so we can improve the scenarios.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Our legal basis&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19482,7 +19482,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>You can withdraw your consent at any time using the link at the bottom of any of our emails. To stop the emails, unsubscribe. To withdraw your consent completely, delete your data, and we'll remove everything straight away.</t>
+          <t>We rely on your consent, which you give when you sign up and confirm your email. It covers the monthly emails, keeping your answers and flight recorder, and recording which screens you reach so we can improve the scenarios.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;You can withdraw your consent at any time using the link at the bottom of any of our emails. To stop the emails, unsubscribe. To withdraw your consent completely, delete your data, and we'll remove everything straight away.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;We rely on your consent, which you give when you sign up and confirm your email. It covers the monthly emails, keeping your answers and flight recorder, and recording which screens you reach so we can improve the scenarios.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19509,12 +19509,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>paragraph</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Who else handles your data</t>
+          <t>You can withdraw your consent at any time using the link at the bottom of any of our emails. To stop the emails, unsubscribe. To withdraw your consent completely, delete your data, and we'll remove everything straight away.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Who else handles your data&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;You can withdraw your consent at any time using the link at the bottom of any of our emails. To stop the emails, unsubscribe. To withdraw your consent completely, delete your data, and we'll remove everything straight away.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19541,12 +19541,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>list item</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt; runs the website, stores the data and sends our emails, acting only on our instructions. Your data is stored in AWS's London region. To make pages load quickly, AWS may handle your visit at its nearest location in Europe or North America.</t>
+          <t>Who else handles your data</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt; runs the website, stores the data and sends our emails, acting only on our instructions. Your data is stored in AWS's London region. To make pages load quickly, AWS may handle your visit at its nearest location in Europe or North America.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Who else handles your data&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Google Workspace&lt;/b&gt; holds our email inbox. If you reply to one of our emails, your reply is kept there.</t>
+          <t>&lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt; runs the website, stores the data and sends our emails, acting only on our instructions. Your data is stored in AWS's London region. To make pages load quickly, AWS may handle your visit at its nearest location in Europe or North America.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr"/>
@@ -19590,7 +19590,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Google Workspace&lt;/b&gt; holds our email inbox. If you reply to one of our emails, your reply is kept there.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Amazon Web Services (AWS)&lt;/b&gt; runs the website, stores the data and sends our emails, acting only on our instructions. Your data is stored in AWS's London region. To make pages load quickly, AWS may handle your visit at its nearest location in Europe or North America.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19605,12 +19605,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>list item</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>We never sell your data or share it with anyone else, unless the law requires it.</t>
+          <t>&lt;b&gt;Google Workspace&lt;/b&gt; holds our email inbox. If you reply to one of our emails, your reply is kept there.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;We never sell your data or share it with anyone else, unless the law requires it.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Google Workspace&lt;/b&gt; holds our email inbox. If you reply to one of our emails, your reply is kept there.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19637,12 +19637,12 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>paragraph</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>How long we keep it</t>
+          <t>We never sell your data or share it with anyone else, unless the law requires it.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;How long we keep it&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;We never sell your data or share it with anyone else, unless the law requires it.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19669,12 +19669,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>list item</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;If you don't confirm your email:&lt;/b&gt; we delete your sign-up after 7 days.</t>
+          <t>How long we keep it</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;If you don't confirm your email:&lt;/b&gt; we delete your sign-up after 7 days.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;How long we keep it&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19706,7 +19706,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Everything else:&lt;/b&gt; we delete it 2 years after you last opened one of our files. Unsubscribing stops the emails; your past answers are then deleted 2 years after you last took part.</t>
+          <t>&lt;b&gt;If you don't confirm your email:&lt;/b&gt; we delete your sign-up after 7 days.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Everything else:&lt;/b&gt; we delete it 2 years after you last opened one of our files. Unsubscribing stops the emails; your past answers are then deleted 2 years after you last took part.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;If you don't confirm your email:&lt;/b&gt; we delete your sign-up after 7 days.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;If you ask us to delete your data:&lt;/b&gt; it's removed from the service straight away. Our backups, which let us recover from mistakes, keep a copy for up to 35 days before it disappears for good.</t>
+          <t>&lt;b&gt;Everything else:&lt;/b&gt; we delete it 2 years after you last opened one of our files. Unsubscribing stops the emails; your past answers are then deleted 2 years after you last took part.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr"/>
@@ -19750,7 +19750,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;If you ask us to delete your data:&lt;/b&gt; it's removed from the service straight away. Our backups, which let us recover from mistakes, keep a copy for up to 35 days before it disappears for good.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Everything else:&lt;/b&gt; we delete it 2 years after you last opened one of our files. Unsubscribing stops the emails; your past answers are then deleted 2 years after you last took part.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19770,7 +19770,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Replies you send us&lt;/b&gt; stay in our inbox until we delete them.</t>
+          <t>&lt;b&gt;If you ask us to delete your data:&lt;/b&gt; it's removed from the service straight away. Our backups, which let us recover from mistakes, keep a copy for up to 35 days before it disappears for good.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Replies you send us&lt;/b&gt; stay in our inbox until we delete them.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;If you ask us to delete your data:&lt;/b&gt; it's removed from the service straight away. Our backups, which let us recover from mistakes, keep a copy for up to 35 days before it disappears for good.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19802,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;If an email to you bounces or is marked as spam,&lt;/b&gt; AWS keeps your address on a "do not send" list so we don't email you again.</t>
+          <t>&lt;b&gt;Security notes&lt;/b&gt; are deleted after 90 days. This includes the note that you deleted your data, which shows it was done.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;If an email to you bounces or is marked as spam,&lt;/b&gt; AWS keeps your address on a \"do not send\" list so we don't email you again.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Security notes&lt;/b&gt; are deleted after 90 days. This includes the note that you deleted your data, which shows it was done.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19829,12 +19829,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>list item</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Your rights</t>
+          <t>&lt;b&gt;Replies you send us&lt;/b&gt; stay in our inbox until we delete them.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Your rights&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Replies you send us&lt;/b&gt; stay in our inbox until we delete them.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19861,12 +19861,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>list item</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>You can ask to see the data we hold about you, have it corrected or deleted, limit how we use it, object to how we use it, or receive a copy to take elsewhere. You can take a 3-month break, unsubscribe, or delete everything at once using the link at the bottom of any of our emails. For anything else, reply to any email or write to the address above. We'll respond within a month.</t>
+          <t>&lt;b&gt;If an email to you bounces or is marked as spam,&lt;/b&gt; AWS keeps your address on a "do not send" list so we don't email you again.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;You can ask to see the data we hold about you, have it corrected or deleted, limit how we use it, object to how we use it, or receive a copy to take elsewhere. You can take a 3-month break, unsubscribe, or delete everything at once using the link at the bottom of any of our emails. For anything else, reply to any email or write to the address above. We'll respond within a month.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;If an email to you bounces or is marked as spam,&lt;/b&gt; AWS keeps your address on a \"do not send\" list so we don't email you again.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19893,12 +19893,12 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>If you're unhappy with how we've handled your data, please tell us first. You can also complain to the Information Commissioner's Office (ICO) at &lt;a href="https://ico.org.uk/make-a-complaint/"&gt;ico.org.uk/make-a-complaint&lt;/a&gt;.</t>
+          <t>Your rights</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;If you're unhappy with how we've handled your data, please tell us first. You can also complain to the Information Commissioner's Office (ICO) at &lt;a href=\"https://ico.org.uk/make-a-complaint/\"&gt;ico.org.uk/make-a-complaint&lt;/a&gt;.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Your rights&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19925,12 +19925,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>paragraph</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Changes</t>
+          <t>You can ask to see the data we hold about you, have it corrected or deleted, limit how we use it, object to how we use it, or receive a copy to take elsewhere. You can take a 3-month break, unsubscribe, or delete everything at once using the link at the bottom of any of our emails. For anything else, reply to any email or write to the address above. We'll respond within a month.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -19942,7 +19942,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Changes&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;You can ask to see the data we hold about you, have it corrected or deleted, limit how we use it, object to how we use it, or receive a copy to take elsewhere. You can take a 3-month break, unsubscribe, or delete everything at once using the link at the bottom of any of our emails. For anything else, reply to any email or write to the address above. We'll respond within a month.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19962,7 +19962,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>If we change how we use your data, we'll update this page and change the date at the top. If a change is significant, we'll tell you by email first.</t>
+          <t>If you're unhappy with how we've handled your data, please tell us first. You can also complain to the Information Commissioner's Office (ICO) at &lt;a href="https://ico.org.uk/make-a-complaint/"&gt;ico.org.uk/make-a-complaint&lt;/a&gt;.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -19974,7 +19974,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;If we change how we use your data, we'll update this page and change the date at the top. If a change is significant, we'll tell you by email first.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;If you're unhappy with how we've handled your data, please tell us first. You can also complain to the Information Commissioner's Office (ICO) at &lt;a href=\"https://ico.org.uk/make-a-complaint/\"&gt;ico.org.uk/make-a-complaint&lt;/a&gt;.&lt;"}</t>
         </is>
       </c>
     </row>
@@ -19989,12 +19989,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Back to The Monday After</t>
+          <t>Changes</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -20005,6 +20005,70 @@
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Changes&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Privacy notice</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>If we change how we use your data, we'll update this page and change the date at the top. If a change is significant, we'll tell you by email first.</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>site/privacy.html</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;If we change how we use your data, we'll update this page and change the date at the top. If a change is significant, we'll tell you by email first.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>601</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Privacy notice</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Back to The Monday After</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>site/privacy.html</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>{"kind": "text", "raw": "&gt;Back to The Monday After&lt;"}</t>
         </is>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>The contract sits with HR. IT has never seen it. Your organisation doesn't have a list of its contractors</t>
+          <t>The contract sits with HR. IT has never seen it. Your organisation doesn't have a list of its contractors.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Pick one or two. Your answers shape what happens next</t>
+          <t>Pick one or two. Your answers shape what happens next.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>You can have a sensible conversation with workers representatives. Your proactive approach will be welcomed and they won't use the opportunity to increase tensions in the relationship.</t>
+          <t>You can have a sensible conversation with workers’ representatives. Your proactive approach will be welcomed and they won't use the opportunity to increase tensions in the relationship.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Identify the mission critical work, and model the impact of reduced capacity on service levels.</t>
+          <t>Identify the mission-critical work, and model the impact of reduced capacity on service levels.</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr"/>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>This is HR’s problem.</t>
+          <t>This is HR’s problem</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr"/>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Because you built the list, you can deal directly with contractors and make short term arrangements.</t>
+          <t>Because you built the list, you can deal directly with contractors and make short-term arrangements.</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr"/>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Brief the workers</t>
+          <t>Brief the workers.</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr"/>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Tell the workers what you do and don't know.</t>
+          <t>Tell the workers what you do and don't know</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr"/>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Escalate</t>
+          <t>Escalate.</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Nobody has mapped what else those contractors can reach, and the same agency still supplies them.</t>
+          <t>Nobody has mapped the organisation’s dependence on contractors.</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>The next failure exposes similar supply chain dependencies, gaps in your data and dependence on contractors</t>
+          <t>The next failure exposes similar supply chain dependencies, gaps in your data and dependence on contractors.</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Your only route to these workers was one agency. It was dependent on one provider. One failed so they both failed.</t>
+          <t>Your only route to these workers was one agency. It was dependent on one provider. One failed, so they both failed.</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr"/>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>The HR team is better-placed to manage its suppliers</t>
+          <t>The HR team is better placed to manage its suppliers.</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr"/>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>IT is firmly in charge but can it reduce risk?</t>
+          <t>IT is firmly in charge, but can it reduce risk?</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr"/>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>Finance HR and IT have collaborated successfully and can again</t>
+          <t>Finance, HR and IT worked together successfully and value IT’s governance processes more highly. How can you use that to increase compliance across the organisation?</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Your temps and contractors haven't been paid. Nobody will say why.</t>
+          <t>Your temps and contractors haven't been paid. Nobody knows why.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -15938,7 +15938,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Your temps and contractors haven't been paid. Nobody will say why.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Your temps and contractors haven't been paid. Nobody knows why.&lt;"}</t>
         </is>
       </c>
     </row>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8144,13 +8144,13 @@
           <t>rows › #5 › variants › #2 › summary</t>
         </is>
       </c>
-      <c r="D238" s="3" t="inlineStr"/>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>It was handled quietly. Responsibility still sits with the agency, but you don’t have an organisational view of your contractors for when the next incident occurs.</t>
+        </is>
+      </c>
       <c r="E238" s="4" t="inlineStr"/>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>COPY NEEDED: Visibility, Drain version (no list was built): one-line summary</t>
-        </is>
-      </c>
+      <c r="F238" s="3" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>site/scenarios/incident-file-01.json</t>
@@ -8173,16 +8173,16 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › detail</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="inlineStr"/>
+          <t>rows › #5 › variants › #2 › detail › intro</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>How much of the organisation you can see, and how quickly.</t>
+        </is>
+      </c>
       <c r="E239" s="4" t="inlineStr"/>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>COPY NEEDED: Visibility, Drain version: detail page</t>
-        </is>
-      </c>
+      <c r="F239" s="3" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>site/scenarios/incident-file-01.json</t>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "detail"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › takeBack › label</t>
+          <t>rows › #5 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Find out whether one list of contractors exists, and who owns it.</t>
+          <t>Pay landed and the questions stopped. Getting there took calls to managers, HR and the agency, pieced together by hand over a weekend.</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › takeBack › from</t>
+          <t>rows › #5 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>Nobody wrote down what was found. The names and contacts gathered that weekend sit in inboxes and notebooks.</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › dimension</t>
+          <t>rows › #5 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Decision rights</t>
+          <t>You start from a guess again, and do the same unusual work to find the same people.</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr"/>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "dimension"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8301,12 +8301,12 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › summary</t>
+          <t>rows › #5 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>You and HR settled who decides before the CEO had to ask.</t>
+          <t>The incident log says resolved, no lasting impact. It doesn’t record that nobody could list the people affected.</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › intro</t>
+          <t>rows › #5 › takeBack › label</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Who is allowed to make which call, and whether everyone knows it.</t>
+          <t>Find out whether one list of contractors exists, and who owns it.</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 4, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › monday</t>
+          <t>rows › #5 › takeBack › from</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>The CEO asked who was leading and got one answer.</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr"/>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 4, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -8397,12 +8397,12 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › threeMonths</t>
+          <t>rows › #6 › dimension</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>The agreement was spoken, not written. People remember it differently, and the next contract will be signed without it.</t>
+          <t>Decision rights</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 5, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › nextTime</t>
+          <t>rows › #6 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>The same question is answered in minutes, if the answer is written down.</t>
+          <t>You and HR settled who decides before the CEO had to ask.</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr"/>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › paper</t>
+          <t>rows › #6 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>The delegation scheme says who can sign off payments. But there wasn't clear governance for agreeing to step outside the process.</t>
+          <t>Who is allowed to make which call, and whether everyone knows it.</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › summary</t>
+          <t>rows › #6 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>The CEO asked who was leading and heard two answers.</t>
+          <t>The CEO asked who was leading and got one answer.</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr"/>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8525,16 +8525,16 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="inlineStr"/>
+          <t>rows › #6 › variants › #1 › detail › threeMonths</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>The agreement was spoken, not written. People remember it differently, and the next contract will be signed without it.</t>
+        </is>
+      </c>
       <c r="E250" s="4" t="inlineStr"/>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>COPY NEEDED: Decision rights, Drain version: detail page</t>
-        </is>
-      </c>
+      <c r="F250" s="3" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
           <t>site/scenarios/incident-file-01.json</t>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › takeBack › label</t>
+          <t>rows › #6 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>Write down who decides whether to pay workers outside the usual chain, and check they know it.</t>
+          <t>The same question is answered in minutes, if the answer is written down.</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr"/>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › takeBack › from</t>
+          <t>rows › #6 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Decision rights</t>
+          <t>The delegation scheme says who can sign off payments. But there wasn't clear governance for agreeing to step outside the process.</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr"/>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › dimension</t>
+          <t>rows › #6 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>The CEO asked who was leading and heard two answers.</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr"/>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "dimension"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8653,16 +8653,16 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #1 › summary</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr">
-        <is>
-          <t>You decided what stopped first, so the rest of the work slowed on purpose.</t>
-        </is>
-      </c>
+          <t>rows › #6 › variants › #2 › detail</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="4" t="inlineStr"/>
-      <c r="F254" s="3" t="inlineStr"/>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>COPY NEEDED: Decision rights, Drain version: detail page</t>
+        </is>
+      </c>
       <c r="G254" t="inlineStr">
         <is>
           <t>site/scenarios/incident-file-01.json</t>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail"]</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #1 › detail</t>
+          <t>rows › #6 › takeBack › label</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>You made a proactive decision to communicate that some work has slowed. Colleagues understand why and your teams are working under less pressure as a result.</t>
+          <t>Write down who decides whether to pay workers outside the usual chain, and check they know it.</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr"/>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 0, "detail"]</t>
+          <t>["screens", 8, "rows", 5, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › summary</t>
+          <t>rows › #6 › takeBack › from</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Planned work stopped while you looked after this, and nobody counted what.</t>
+          <t>Decision rights</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › intro</t>
+          <t>rows › #7 › dimension</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>What the rest of the organisation did not get done because of the response.</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr"/>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 6, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › monday</t>
+          <t>rows › #7 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Three people left planned work to cover the weekend. They are compensated but tired. What's the impact on their planned work?</t>
+          <t>You decided what stopped first, so the rest of the work slowed on purpose.</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8813,12 +8813,12 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #7 › variants › #1 › detail</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Two pieces of work have slipped. The reasons are not on any report.</t>
+          <t>You made a proactive decision to communicate that some work has slowed. Colleagues understand why and your teams are working under less pressure as a result.</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr"/>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail"]</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › nextTime</t>
+          <t>rows › #7 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>The same work stops first again, because nobody agreed in advance what should.</t>
+          <t>Planned work stopped while you looked after this, and nobody counted what.</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8877,12 +8877,12 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › paper</t>
+          <t>rows › #7 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>The portfolio report is green for now. The impact of this weekend won't be visible immediately.</t>
+          <t>What the rest of the organisation did not get done because of the response.</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › takeBack › label</t>
+          <t>rows › #7 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>List the work you would stop first in an incident, and tell the people it affects.</t>
+          <t>Three people left planned work to cover the weekend. They are compensated but tired. What's the impact on their planned work?</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › takeBack › from</t>
+          <t>rows › #7 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Two pieces of work have slipped. The reasons are not on any report.</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8973,12 +8973,12 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>footnote</t>
+          <t>rows › #7 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Tap a row for three months on and next time. Flag what you’d take back.</t>
+          <t>The same work stops first again, because nobody agreed in advance what should.</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>["screens", 8, "footnote"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>rows › #7 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>Choose what to take back →</t>
+          <t>The portfolio report is green for now. The impact of this weekend won't be visible immediately.</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr"/>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>["screens", 8, "button"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -9032,17 +9032,17 @@
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>rows › #7 › takeBack › label</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Your move</t>
+          <t>List the work you would stop first in an incident, and tell the people it affects.</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr"/>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>["screens", 9, "header", "label"]</t>
+          <t>["screens", 8, "rows", 6, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -9064,17 +9064,17 @@
       </c>
       <c r="B267" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>rows › #7 › takeBack › from</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>5 of 5</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>["screens", 9, "header", "step"]</t>
+          <t>["screens", 8, "rows", 6, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -9096,17 +9096,17 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>footnote</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Take one thing back.</t>
+          <t>Tap a row for three months on and next time. Flag what you’d take back.</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>["screens", 9, "title"]</t>
+          <t>["screens", 8, "footnote"]</t>
         </is>
       </c>
     </row>
@@ -9128,17 +9128,17 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>button</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>You flagged {count}. Pick the one you’ll actually do. One is enough.</t>
+          <t>Choose what to take back →</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr"/>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>["screens", 9, "intro"]</t>
+          <t>["screens", 8, "button"]</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>You didn’t flag anything this time. You can go back to the ledger and flag something, or close the file.</t>
+          <t>The Monday After · Your move</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>["screens", 9, "none"]</t>
+          <t>["screens", 9, "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>whenKicker</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>By when</t>
+          <t>5 of 5</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr"/>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenKicker"]</t>
+          <t>["screens", 9, "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #1 › label</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>1 week</t>
+          <t>Take one thing back.</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr"/>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 0, "label"]</t>
+          <t>["screens", 9, "title"]</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #1 › phrase</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>By one week from today.</t>
+          <t>You flagged {count}. Pick the one you’ll actually do. One is enough.</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr"/>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 0, "phrase"]</t>
+          <t>["screens", 9, "intro"]</t>
         </is>
       </c>
     </row>
@@ -9293,12 +9293,12 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #2 › label</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>2 weeks</t>
+          <t>You didn’t flag anything this time. You can go back to the ledger and flag something, or close the file.</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr"/>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 1, "label"]</t>
+          <t>["screens", 9, "none"]</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9325,12 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #2 › phrase</t>
+          <t>whenKicker</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>By two weeks from today.</t>
+          <t>By when</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 1, "phrase"]</t>
+          <t>["screens", 9, "whenKicker"]</t>
         </is>
       </c>
     </row>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #3 › label</t>
+          <t>whenOptions › #1 › label</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>1 week</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 2, "label"]</t>
+          <t>["screens", 9, "whenOptions", 0, "label"]</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #3 › phrase</t>
+          <t>whenOptions › #1 › phrase</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>By one month from today.</t>
+          <t>By one week from today.</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 2, "phrase"]</t>
+          <t>["screens", 9, "whenOptions", 0, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>followUp</t>
+          <t>whenOptions › #2 › label</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Ask me in 30 days whether I did it. One email, and you can stop it any time.</t>
+          <t>2 weeks</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>["screens", 9, "followUp"]</t>
+          <t>["screens", 9, "whenOptions", 1, "label"]</t>
         </is>
       </c>
     </row>
@@ -9453,12 +9453,12 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>followUpPromise</t>
+          <t>whenOptions › #2 › phrase</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>I’ll ask you in 30 days whether you did.</t>
+          <t>By two weeks from today.</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr"/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>["screens", 9, "followUpPromise"]</t>
+          <t>["screens", 9, "whenOptions", 1, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>whenOptions › #3 › label</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Save and close the file →</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>["screens", 9, "button"]</t>
+          <t>["screens", 9, "whenOptions", 2, "label"]</t>
         </is>
       </c>
     </row>
@@ -9517,12 +9517,12 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>whenOptions › #3 › phrase</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>Skip, close the file</t>
+          <t>By one month from today.</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr"/>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>["screens", 9, "skip"]</t>
+          <t>["screens", 9, "whenOptions", 2, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -9544,17 +9544,17 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>followUp</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Incident File 01 · The Monday After</t>
+          <t>Ask me in 30 days whether I did it. One email, and you can stop it any time.</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>["screens", 10, "header", "label"]</t>
+          <t>["screens", 9, "followUp"]</t>
         </is>
       </c>
     </row>
@@ -9576,17 +9576,17 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>followUpPromise</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>I’ll ask you in 30 days whether you did.</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>["screens", 10, "header", "step"]</t>
+          <t>["screens", 9, "followUpPromise"]</t>
         </is>
       </c>
     </row>
@@ -9608,17 +9608,17 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>kicker</t>
+          <t>button</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Your Monday After</t>
+          <t>Save and close the file →</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>["screens", 10, "kicker"]</t>
+          <t>["screens", 9, "button"]</t>
         </is>
       </c>
     </row>
@@ -9640,17 +9640,17 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › prefix</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">You </t>
+          <t>Skip, close the file</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr"/>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "prefix"]</t>
+          <t>["screens", 9, "skip"]</t>
         </is>
       </c>
     </row>
@@ -9677,12 +9677,12 @@
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › A</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>built the list</t>
+          <t>Incident File 01 · The Monday After</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr"/>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "A"]</t>
+          <t>["screens", 10, "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › B</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>pressed the agency</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr"/>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "B"]</t>
+          <t>["screens", 10, "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -9741,12 +9741,12 @@
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › C</t>
+          <t>kicker</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>bridged the gap</t>
+          <t>Your Monday After</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr"/>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "C"]</t>
+          <t>["screens", 10, "kicker"]</t>
         </is>
       </c>
     </row>
@@ -9773,12 +9773,12 @@
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › D</t>
+          <t>mirror › opening › prefix</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>told the workers early</t>
+          <t xml:space="preserve">You </t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr"/>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "D"]</t>
+          <t>["screens", 10, "mirror", "opening", "prefix"]</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › E</t>
+          <t>mirror › opening › phrases › A</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>went to worker representatives early</t>
+          <t>built the list</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr"/>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "E"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "A"]</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › F</t>
+          <t>mirror › opening › phrases › B</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>protected the critical work</t>
+          <t>pressed the agency</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr"/>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "F"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "B"]</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>mirror › middle › #1 › text</t>
+          <t>mirror › opening › phrases › C</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>You now know who these people are.</t>
+          <t>bridged the gap</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr"/>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "middle", 0, "text"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "C"]</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>mirror › middle › #2 › text</t>
+          <t>mirror › opening › phrases › D</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>You still don't have one list of these people.</t>
+          <t>told the workers early</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "middle", 1, "text"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "D"]</t>
         </is>
       </c>
     </row>
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 1 › did</t>
+          <t>mirror › opening › phrases › E</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>You kept the most exposed people paid.</t>
+          <t>went to worker representatives early</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr"/>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "1", "did"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "E"]</t>
         </is>
       </c>
     </row>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 1 › still</t>
+          <t>mirror › opening › phrases › F</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who owns the supplier's supplier.</t>
+          <t>protected the critical work</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "1", "still"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "F"]</t>
         </is>
       </c>
     </row>
@@ -9997,12 +9997,12 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 2 › did</t>
+          <t>mirror › middle › #1 › text</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>You said what you knew and what you didn't, before the group chat did.</t>
+          <t>You now know who these people are.</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "2", "did"]</t>
+          <t>["screens", 10, "mirror", "middle", 0, "text"]</t>
         </is>
       </c>
     </row>
@@ -10029,12 +10029,12 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 2 › still</t>
+          <t>mirror › middle › #2 › text</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>You still can't say when anyone will be paid, or who owns the supplier's supplier.</t>
+          <t>You still don't have one list of these people.</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "2", "still"]</t>
+          <t>["screens", 10, "mirror", "middle", 1, "text"]</t>
         </is>
       </c>
     </row>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 3 › did</t>
+          <t>mirror › ending › parts › 1 › did</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>You made it the CEO's decision, so it had an owner by Saturday.</t>
+          <t>You kept the most exposed people paid.</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "3", "did"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "1", "did"]</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 3 › still</t>
+          <t>mirror › ending › parts › 1 › still</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>You still haven't asked who should have owned the supplier's supplier before it mattered.</t>
+          <t>You still don't know who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr"/>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "3", "still"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "1", "still"]</t>
         </is>
       </c>
     </row>
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 4 › did</t>
+          <t>mirror › ending › parts › 2 › did</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>You know what else this provider touches.</t>
+          <t>You said what you knew and what you didn't, before the group chat did.</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "4", "did"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "2", "did"]</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10157,12 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 4 › still</t>
+          <t>mirror › ending › parts › 2 › still</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>You still haven't decided who watches it.</t>
+          <t>You still can't say when anyone will be paid, or who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr"/>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "4", "still"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "2", "still"]</t>
         </is>
       </c>
     </row>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 5 › did</t>
+          <t>mirror › ending › parts › 3 › did</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>You protected Monday.</t>
+          <t>You made it the CEO's decision, so it had an owner by Saturday.</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "5", "did"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "3", "did"]</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 5 › still</t>
+          <t>mirror › ending › parts › 3 › still</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who will be paid, or who owns the supplier's supplier.</t>
+          <t>You still haven't asked who should have owned the supplier's supplier before it mattered.</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "5", "still"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "3", "still"]</t>
         </is>
       </c>
     </row>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>mirror › fallback</t>
+          <t>mirror › ending › parts › 4 › did</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who owns the supplier's supplier.</t>
+          <t>You know what else this provider touches.</t>
         </is>
       </c>
       <c r="E304" s="4" t="inlineStr"/>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "fallback"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "4", "did"]</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>tagline</t>
+          <t>mirror › ending › parts › 4 › still</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>Lucky, or designed? Only one of those repeats.</t>
+          <t>You still haven't decided who watches it.</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>["screens", 10, "tagline"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "4", "still"]</t>
         </is>
       </c>
     </row>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>takingKicker</t>
+          <t>mirror › ending › parts › 5 › did</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>You’re taking this back</t>
+          <t>You protected Monday.</t>
         </is>
       </c>
       <c r="E306" s="4" t="inlineStr"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>["screens", 10, "takingKicker"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "5", "did"]</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>recorder › kicker</t>
+          <t>mirror › ending › parts › 5 › still</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>Your flight recorder</t>
+          <t>You still don't know who will be paid, or who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr"/>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "kicker"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "5", "still"]</t>
         </is>
       </c>
     </row>
@@ -10381,12 +10381,12 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>recorder › text</t>
+          <t>mirror › fallback</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Want a copy of what you wrote? We’ll email it to you. Nobody else can read it.</t>
+          <t>You still don't know who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "text"]</t>
+          <t>["screens", 10, "mirror", "fallback"]</t>
         </is>
       </c>
     </row>
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>recorder › button</t>
+          <t>tagline</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>Email me my flight recorder</t>
+          <t>Lucky, or designed? Only one of those repeats.</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr"/>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "button"]</t>
+          <t>["screens", 10, "tagline"]</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>recorder › previewNote</t>
+          <t>takingKicker</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>In the finished version, this emails you a copy.</t>
+          <t>You’re taking this back</t>
         </is>
       </c>
       <c r="E310" s="4" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "previewNote"]</t>
+          <t>["screens", 10, "takingKicker"]</t>
         </is>
       </c>
     </row>
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>share › kicker</t>
+          <t>recorder › kicker</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>Pass it on</t>
+          <t>Your flight recorder</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "kicker"]</t>
+          <t>["screens", 10, "recorder", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>share › text</t>
+          <t>recorder › text</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Send this to the person you'd most like to answer it differently.</t>
+          <t>Want a copy of what you wrote? We’ll email it to you. Nobody else can read it.</t>
         </is>
       </c>
       <c r="E312" s="4" t="inlineStr"/>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "text"]</t>
+          <t>["screens", 10, "recorder", "text"]</t>
         </is>
       </c>
     </row>
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>share › button</t>
+          <t>recorder › button</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>Share this file</t>
+          <t>Email me my flight recorder</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "button"]</t>
+          <t>["screens", 10, "recorder", "button"]</t>
         </is>
       </c>
     </row>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>share › copied</t>
+          <t>recorder › previewNote</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Link copied.</t>
+          <t>In the finished version, this emails you a copy.</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr"/>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "copied"]</t>
+          <t>["screens", 10, "recorder", "previewNote"]</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>team › text</t>
+          <t>share › kicker</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>Some of these questions are hard to settle alone. If you'd like to run this with your team, reply to this email and I'll show you how.</t>
+          <t>Pass it on</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>["screens", 10, "team", "text"]</t>
+          <t>["screens", 10, "share", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>team › button</t>
+          <t>share › text</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Reply “team”</t>
+          <t>Send this to the person you'd most like to answer it differently.</t>
         </is>
       </c>
       <c r="E316" s="4" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>["screens", 10, "team", "button"]</t>
+          <t>["screens", 10, "share", "text"]</t>
         </is>
       </c>
     </row>
@@ -10669,12 +10669,12 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>share › button</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>Incident File 02 arrives next month.</t>
+          <t>Share this file</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>["screens", 10, "next"]</t>
+          <t>["screens", 10, "share", "button"]</t>
         </is>
       </c>
     </row>
@@ -10696,17 +10696,17 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>share › copied</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>Link copied.</t>
         </is>
       </c>
       <c r="E318" s="4" t="inlineStr"/>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>["threads", "t1", "header", "label"]</t>
+          <t>["screens", 10, "share", "copied"]</t>
         </is>
       </c>
     </row>
@@ -10728,17 +10728,17 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>team › text</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Some of these questions are hard to settle alone. If you'd like to run this with your team, reply to this email and I'll show you how.</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>["threads", "t1", "header", "step"]</t>
+          <t>["screens", 10, "team", "text"]</t>
         </is>
       </c>
     </row>
@@ -10760,17 +10760,17 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>team › button</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>Reply “team”</t>
         </is>
       </c>
       <c r="E320" s="4" t="inlineStr"/>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>["threads", "t1", "chip", "kicker"]</t>
+          <t>["screens", 10, "team", "button"]</t>
         </is>
       </c>
     </row>
@@ -10792,17 +10792,17 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>Are you owning this?</t>
+          <t>Incident File 02 arrives next month.</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>["threads", "t1", "chip", "title"]</t>
+          <t>["screens", 10, "next"]</t>
         </is>
       </c>
     </row>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Are you owning this?</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr"/>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>["threads", "t1", "title"]</t>
+          <t>["threads", "t1", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>intro › #1 › text</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>You stepped in alongside HR. The CEO has asked who is leading.</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 0, "text"]</t>
+          <t>["threads", "t1", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>intro › #2 › text</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>You agreed HR would lead. The CEO has asked who they should call.</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E324" s="4" t="inlineStr"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 1, "text"]</t>
+          <t>["threads", "t1", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -10925,12 +10925,12 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>intro › #3 › text</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>You took it from HR. The CEO has asked who is leading, and so has HR.</t>
+          <t>Are you owning this?</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 2, "text"]</t>
+          <t>["threads", "t1", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -10957,12 +10957,12 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Front it</t>
+          <t>Are you owning this?</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "title"]</t>
+          <t>["threads", "t1", "title"]</t>
         </is>
       </c>
     </row>
@@ -10989,12 +10989,12 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>intro › #1 › text</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>You are the visible lead, to the CEO and to the workers.</t>
+          <t>You stepped in alongside HR. The CEO has asked who is leading.</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "body"]</t>
+          <t>["threads", "t1", "intro", 0, "text"]</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11021,12 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>intro › #2 › text</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>You can carry the workers' trust and the CEO's confidence at once, and HR will not read it as a takeover.</t>
+          <t>You agreed HR would lead. The CEO has asked who they should call.</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "intro", 1, "text"]</t>
         </is>
       </c>
     </row>
@@ -11053,12 +11053,12 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>intro › #3 › text</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>One clear voice. The CEO and the workers know who to call.</t>
+          <t>You took it from HR. The CEO has asked who is leading, and so has HR.</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t1", "intro", 2, "text"]</t>
         </is>
       </c>
     </row>
@@ -11085,12 +11085,12 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>HR's ownership weakens, and your name is on it if it goes wrong.</t>
+          <t>Front it</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr"/>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -11117,12 +11117,12 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>Back HR, visibly</t>
+          <t>You are the visible lead, to the CEO and to the workers.</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr"/>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "title"]</t>
+          <t>["threads", "t1", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -11149,12 +11149,12 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>You tell the CEO you are supporting the Chief People Officer.</t>
+          <t>You can carry the workers' trust and the CEO's confidence at once, and HR will not read it as a takeover.</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr"/>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "body"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>HR can hold the room with the CEO and the workers, and you will hear in time if it slips.</t>
+          <t>One clear voice. The CEO and the workers know who to call.</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr"/>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>The owner of the relationship stays accountable, and your capacity is kept for the rest of IT.</t>
+          <t>HR's ownership weakens, and your name is on it if it goes wrong.</t>
         </is>
       </c>
       <c r="E334" s="4" t="inlineStr"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11245,12 +11245,12 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>Your influence rests on someone else’s performance, and you may hear late.</t>
+          <t>Back HR, visibly</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -11277,12 +11277,12 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Stay in the background</t>
+          <t>You tell the CEO you are supporting the Chief People Officer.</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "title"]</t>
+          <t>["threads", "t1", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>You help quietly and step forward only if asked.</t>
+          <t>HR can hold the room with the CEO and the workers, and you will hear in time if it slips.</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr"/>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "body"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11341,12 +11341,12 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>You will be asked in time, and HR will tell you when it starts to slip.</t>
+          <t>The owner of the relationship stays accountable, and your capacity is kept for the rest of IT.</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>Your capacity stays free for the rest of IT, and HR keeps ownership of its own relationship.</t>
+          <t>Your influence rests on someone else’s performance, and you may hear late.</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11405,12 +11405,12 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>You hear late, and the delay is invisible until it is not.</t>
+          <t>Stay in the background</t>
         </is>
       </c>
       <c r="E340" s="4" t="inlineStr"/>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -11437,12 +11437,12 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>All three can be reasonable. The question is who the CEO believes owns it.</t>
+          <t>You help quietly and step forward only if asked.</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr"/>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>["threads", "t1", "closing"]</t>
+          <t>["threads", "t1", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -11464,17 +11464,17 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>You will be asked in time, and HR will tell you when it starts to slip.</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr"/>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>["threads", "t2", "header", "label"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11496,17 +11496,17 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Your capacity stays free for the rest of IT, and HR keeps ownership of its own relationship.</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>["threads", "t2", "header", "step"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11528,17 +11528,17 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>You hear late, and the delay is invisible until it is not.</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr"/>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>["threads", "t2", "chip", "kicker"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11560,17 +11560,17 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>All three can be reasonable. The question is who the CEO believes owns it.</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr"/>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>["threads", "t2", "chip", "title"]</t>
+          <t>["threads", "t1", "closing"]</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11597,12 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E346" s="4" t="inlineStr"/>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>["threads", "t2", "title"]</t>
+          <t>["threads", "t2", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -11629,12 +11629,12 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>The agency passed assurance when you bought it. Nobody looked at who pays its workers.</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>["threads", "t2", "intro"]</t>
+          <t>["threads", "t2", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -11661,12 +11661,12 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E348" s="4" t="inlineStr"/>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "title"]</t>
+          <t>["threads", "t2", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>Knows the technology</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr"/>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "body"]</t>
+          <t>["threads", "t2", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -11725,12 +11725,12 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>IT knows what to look for in a payroll provider, and has the standing to ask for it.</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E350" s="4" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "title"]</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>The check is technically sound, and it covers systems IT already protects.</t>
+          <t>The agency passed assurance when you bought it. Nobody looked at who pays its workers.</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr"/>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t2", "intro"]</t>
         </is>
       </c>
     </row>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>IT has to know the contract exists first. Here it never saw it, so the check never starts.</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E352" s="4" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Knows the technology</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr"/>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "title"]</t>
+          <t>["threads", "t2", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -11853,12 +11853,12 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Owns the relationship</t>
+          <t>IT knows what to look for in a payroll provider, and has the standing to ask for it.</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr"/>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "body"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>HR has, or can buy in, the skill to judge a payroll provider's resilience.</t>
+          <t>The check is technically sound, and it covers systems IT already protects.</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr"/>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>The owner of the relationship stays accountable.</t>
+          <t>IT has to know the contract exists first. Here it never saw it, so the check never starts.</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11949,12 +11949,12 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>The check is shallow, which risks being paper again.</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -11981,12 +11981,12 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>The agency</t>
+          <t>Owns the relationship</t>
         </is>
       </c>
       <c r="E358" s="4" t="inlineStr"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "title"]</t>
+          <t>["threads", "t2", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>It's their supply chain</t>
+          <t>HR has, or can buy in, the skill to judge a payroll provider's resilience.</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "body"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12045,12 +12045,12 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>The agency is checking its own supplier, and will tell you honestly if it is not.</t>
+          <t>The owner of the relationship stays accountable.</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr"/>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12077,12 +12077,12 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>The responsibility sits with the party closest to the supplier, and asking costs you nothing.</t>
+          <t>The check is shallow, which risks being paper again.</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>You are relying on a statement, not evidence, from someone who loses the contract if the answer is bad.</t>
+          <t>The agency</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr"/>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>Shared, by design</t>
+          <t>It's their supply chain</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr"/>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "title"]</t>
+          <t>["threads", "t2", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -12173,12 +12173,12 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › body</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Agreed in advance, revisited as the supplier's role changes</t>
+          <t>The agency is checking its own supplier, and will tell you honestly if it is not.</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr"/>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "body"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › assuming</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>Someone agreed in advance who checks what, and keeps that agreement alive as the supplier's role changes.</t>
+          <t>The responsibility sits with the party closest to the supplier, and asking costs you nothing.</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › gain</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Nothing falls between IT and HR, and the check is revisited when the supplier changes.</t>
+          <t>You are relying on a statement, not evidence, from someone who loses the contract if the answer is bad.</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12269,12 +12269,12 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › cost</t>
+          <t>options › #4 › title</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>It takes effort before anything has gone wrong, which is hard to justify, and agreements like this drift if nobody owns them.</t>
+          <t>Shared, by design</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 3, "title"]</t>
         </is>
       </c>
     </row>
@@ -12301,12 +12301,12 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #4 › body</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>All four can be reasonable. The question is whether anyone decided this agency was critical.</t>
+          <t>Agreed in advance, revisited as the supplier's role changes</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr"/>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>["threads", "t2", "closing"]</t>
+          <t>["threads", "t2", "options", 3, "body"]</t>
         </is>
       </c>
     </row>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #4 › reveal › assuming</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>A question about what a sensible owner would check, not what the law requires.</t>
+          <t>Someone agreed in advance who checks what, and keeps that agreement alive as the supplier's role changes.</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr"/>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>["threads", "t2", "disclaimer"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12365,12 +12365,12 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>takeBack › label</t>
+          <t>options › #4 › reveal › gain</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Ask who should have checked the agency’s payroll provider.</t>
+          <t>Nothing falls between IT and HR, and the check is revisited when the supplier changes.</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "label"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>takeBack › commit</t>
+          <t>options › #4 › reveal › cost</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>Ask who should have checked the agency’s payroll provider, and write down the answer.</t>
+          <t>It takes effort before anything has gone wrong, which is hard to justify, and agreements like this drift if nobody owns them.</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "commit"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12429,12 +12429,12 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>takeBack › from</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>All four can be reasonable. The question is whether anyone decided this agency was critical.</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "from"]</t>
+          <t>["threads", "t2", "closing"]</t>
         </is>
       </c>
     </row>
@@ -12456,17 +12456,17 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>A question about what a sensible owner would check, not what the law requires.</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr"/>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>["threads", "t3", "header", "label"]</t>
+          <t>["threads", "t2", "disclaimer"]</t>
         </is>
       </c>
     </row>
@@ -12488,17 +12488,17 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>takeBack › label</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>Ask who should have checked the agency’s payroll provider.</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>["threads", "t3", "header", "step"]</t>
+          <t>["threads", "t2", "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -12520,17 +12520,17 @@
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>takeBack › commit</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>Ask who should have checked the agency’s payroll provider, and write down the answer.</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr"/>
@@ -12542,7 +12542,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "kicker"]</t>
+          <t>["threads", "t2", "takeBack", "commit"]</t>
         </is>
       </c>
     </row>
@@ -12552,17 +12552,17 @@
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>takeBack › from</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>The clock</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "title"]</t>
+          <t>["threads", "t2", "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -12589,12 +12589,12 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>chip › sub</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>Does anyone’s clock start now?</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr"/>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "sub"]</t>
+          <t>["threads", "t3", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -12621,12 +12621,12 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>The clock.</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr"/>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>["threads", "t3", "title"]</t>
+          <t>["threads", "t3", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -12653,12 +12653,12 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>situation › time</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 09:10</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr"/>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>["threads", "t3", "situation", "time"]</t>
+          <t>["threads", "t3", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -12685,12 +12685,12 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>situation › text</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>The agency’s payroll provider “cannot rule out” a security incident. Pay data is personal data. What do you do about the clock?</t>
+          <t>The clock</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr"/>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>["threads", "t3", "situation", "text"]</t>
+          <t>["threads", "t3", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>chip › sub</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>Wait for confirmation</t>
+          <t>Does anyone’s clock start now?</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr"/>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "title"]</t>
+          <t>["threads", "t3", "chip", "sub"]</t>
         </is>
       </c>
     </row>
@@ -12749,12 +12749,12 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Nothing to act on until someone says it is an incident.</t>
+          <t>The clock.</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "body"]</t>
+          <t>["threads", "t3", "title"]</t>
         </is>
       </c>
     </row>
@@ -12781,12 +12781,12 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>situation › time</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>Nothing starts until someone confirms an incident, and nobody will later ask what you knew on Saturday.</t>
+          <t>Saturday, 09:10</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "situation", "time"]</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>situation › text</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>You do not raise an alarm over a maybe.</t>
+          <t>The agency’s payroll provider “cannot rule out” a security incident. Pay data is personal data. What do you do about the clock?</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t3", "situation", "text"]</t>
         </is>
       </c>
     </row>
@@ -12845,12 +12845,12 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>If the clock runs from when you became aware, time has already passed, and you have no record of what you knew.</t>
+          <t>Wait for confirmation</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr"/>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -12877,12 +12877,12 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Note when you were told</t>
+          <t>Nothing to act on until someone says it is an incident.</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr"/>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "title"]</t>
+          <t>["threads", "t3", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -12909,12 +12909,12 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>Start a timestamped log of what you knew and when.</t>
+          <t>Nothing starts until someone confirms an incident, and nobody will later ask what you knew on Saturday.</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "body"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12941,12 +12941,12 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>The record you start now will matter later, and someone else is deciding who reports.</t>
+          <t>You do not raise an alarm over a maybe.</t>
         </is>
       </c>
       <c r="E388" s="4" t="inlineStr"/>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12973,12 +12973,12 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>You can show what you knew and when.</t>
+          <t>If the clock runs from when you became aware, time has already passed, and you have no record of what you knew.</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr"/>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>A log is not a decision. Someone still has to own the call.</t>
+          <t>Note when you were told</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr"/>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -13037,12 +13037,12 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>Ask your data protection lead</t>
+          <t>Start a timestamped log of what you knew and when.</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr"/>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "title"]</t>
+          <t>["threads", "t3", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Are you a controller or a processor here, and who tells the regulator?</t>
+          <t>The record you start now will matter later, and someone else is deciding who reports.</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "body"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13101,12 +13101,12 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>You have a data protection lead, they can be reached on a Saturday, and they can say what your role is.</t>
+          <t>You can show what you knew and when.</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>You get a view early on whether you are a controller or a processor here, and who has to tell whom.</t>
+          <t>A log is not a decision. Someone still has to own the call.</t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr"/>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13165,12 +13165,12 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>If nobody can be reached, hours pass. And the honest answer may be "it depends".</t>
+          <t>Ask your data protection lead</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -13197,12 +13197,12 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Ask the agency in writing</t>
+          <t>Are you a controller or a processor here, and who tells the regulator?</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "title"]</t>
+          <t>["threads", "t3", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › body</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>Has it told its customers, and has its provider told it?</t>
+          <t>You have a data protection lead, they can be reached on a Saturday, and they can say what your role is.</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "body"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13261,12 +13261,12 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › assuming</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>The agency knows what its provider has told it, and will answer in writing.</t>
+          <t>You get a view early on whether you are a controller or a processor here, and who has to tell whom.</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13293,12 +13293,12 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › gain</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>You have a dated record of what you asked and what you were told.</t>
+          <t>If nobody can be reached, hours pass. And the honest answer may be "it depends".</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13325,12 +13325,12 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › cost</t>
+          <t>options › #4 › title</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>A written question can slow things down and make the agency defensive. It may not have the answer either.</t>
+          <t>Ask the agency in writing</t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 3, "title"]</t>
         </is>
       </c>
     </row>
@@ -13357,12 +13357,12 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #4 › body</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>The clock may start when you become aware, not when someone confirms.</t>
+          <t>Has it told its customers, and has its provider told it?</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr"/>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>["threads", "t3", "closing"]</t>
+          <t>["threads", "t3", "options", 3, "body"]</t>
         </is>
       </c>
     </row>
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #4 › reveal › assuming</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Questions to check with your data protection lead or counsel. Not legal advice.</t>
+          <t>The agency knows what its provider has told it, and will answer in writing.</t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr"/>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>["threads", "t3", "disclaimer"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13416,17 +13416,17 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #4 › reveal › gain</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>You have a dated record of what you asked and what you were told.</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr"/>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>["threads", "t4", "header", "label"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13448,17 +13448,17 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #4 › reveal › cost</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>A written question can slow things down and make the agency defensive. It may not have the answer either.</t>
         </is>
       </c>
       <c r="E404" s="4" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>["threads", "t4", "header", "step"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13480,17 +13480,17 @@
       </c>
       <c r="B405" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 14:00 · Pull a thread</t>
+          <t>The clock may start when you become aware, not when someone confirms.</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr"/>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "kicker"]</t>
+          <t>["threads", "t3", "closing"]</t>
         </is>
       </c>
     </row>
@@ -13512,17 +13512,17 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>A neighbour will pay its contractors directly</t>
+          <t>Questions to check with your data protection lead or counsel. Not legal advice.</t>
         </is>
       </c>
       <c r="E406" s="4" t="inlineStr"/>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "title"]</t>
+          <t>["threads", "t3", "disclaimer"]</t>
         </is>
       </c>
     </row>
@@ -13549,12 +13549,12 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>chip › sub</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>Your workers have seen it.</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "sub"]</t>
+          <t>["threads", "t4", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -13581,12 +13581,12 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 14:00</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E408" s="4" t="inlineStr"/>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>["threads", "t4", "time"]</t>
+          <t>["threads", "t4", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>You're not the only customer.</t>
+          <t>Saturday, 14:00 · Pull a thread</t>
         </is>
       </c>
       <c r="E409" s="4" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>["threads", "t4", "title"]</t>
+          <t>["threads", "t4", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -13645,12 +13645,12 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>situation › text</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>A neighbouring organisation that uses the same agency announces it will pay its contractors directly. Your workers have seen it.</t>
+          <t>A neighbour will pay its contractors directly</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr"/>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>["threads", "t4", "situation", "text"]</t>
+          <t>["threads", "t4", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -13677,12 +13677,12 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>prompt</t>
+          <t>chip › sub</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>What do you do? Pick one.</t>
+          <t>Your workers have seen it.</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr"/>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>["threads", "t4", "prompt"]</t>
+          <t>["threads", "t4", "chip", "sub"]</t>
         </is>
       </c>
     </row>
@@ -13709,12 +13709,12 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>time</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Call the other customers and agree a common line</t>
+          <t>Saturday, 14:00</t>
         </is>
       </c>
       <c r="E412" s="4" t="inlineStr"/>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 0, "title"]</t>
+          <t>["threads", "t4", "time"]</t>
         </is>
       </c>
     </row>
@@ -13741,12 +13741,12 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>Wait and let them move first</t>
+          <t>You're not the only customer.</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr"/>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 1, "title"]</t>
+          <t>["threads", "t4", "title"]</t>
         </is>
       </c>
     </row>
@@ -13773,12 +13773,12 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>situation › text</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Pay directly too, now</t>
+          <t>A neighbouring organisation that uses the same agency announces it will pay its contractors directly. Your workers have seen it.</t>
         </is>
       </c>
       <c r="E414" s="4" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 2, "title"]</t>
+          <t>["threads", "t4", "situation", "text"]</t>
         </is>
       </c>
     </row>
@@ -13805,12 +13805,12 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>prompt</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>Hold your line and explain why</t>
+          <t>What do you do? Pick one.</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 3, "title"]</t>
+          <t>["threads", "t4", "prompt"]</t>
         </is>
       </c>
     </row>
@@ -13837,12 +13837,12 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>options › #5 › title</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Take it to a shared forum or the agency</t>
+          <t>Call the other customers and agree a common line</t>
         </is>
       </c>
       <c r="E416" s="4" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 4, "title"]</t>
+          <t>["threads", "t4", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>Coordinating with other customers may have limits depending on sector and country. Check before you act.</t>
+          <t>Wait and let them move first</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr"/>
@@ -13885,6 +13885,134 @@
         </is>
       </c>
       <c r="H417" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 1, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="inlineStr">
+        <is>
+          <t>options › #3 › title</t>
+        </is>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>Pay directly too, now</t>
+        </is>
+      </c>
+      <c r="E418" s="4" t="inlineStr"/>
+      <c r="F418" s="3" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 2, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="3" t="n">
+        <v>418</v>
+      </c>
+      <c r="B419" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="inlineStr">
+        <is>
+          <t>options › #4 › title</t>
+        </is>
+      </c>
+      <c r="D419" s="3" t="inlineStr">
+        <is>
+          <t>Hold your line and explain why</t>
+        </is>
+      </c>
+      <c r="E419" s="4" t="inlineStr"/>
+      <c r="F419" s="3" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 3, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="3" t="n">
+        <v>419</v>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="inlineStr">
+        <is>
+          <t>options › #5 › title</t>
+        </is>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>Take it to a shared forum or the agency</t>
+        </is>
+      </c>
+      <c r="E420" s="4" t="inlineStr"/>
+      <c r="F420" s="3" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 4, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+      <c r="D421" s="3" t="inlineStr">
+        <is>
+          <t>Coordinating with other customers may have limits depending on sector and country. Check before you act.</t>
+        </is>
+      </c>
+      <c r="E421" s="4" t="inlineStr"/>
+      <c r="F421" s="3" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
         <is>
           <t>["threads", "t4", "disclaimer"]</t>
         </is>
@@ -13958,7 +14086,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -13990,7 +14118,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -14022,7 +14150,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -14054,7 +14182,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -14086,7 +14214,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -14118,7 +14246,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -14150,7 +14278,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -14182,7 +14310,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -14214,7 +14342,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -14246,7 +14374,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -14278,7 +14406,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -14310,7 +14438,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -14342,7 +14470,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -14374,7 +14502,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -14406,7 +14534,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -14438,7 +14566,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -14470,7 +14598,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -14502,7 +14630,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -14534,7 +14662,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -14566,7 +14694,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -14598,7 +14726,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -14630,7 +14758,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -14662,7 +14790,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -14694,7 +14822,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -14726,7 +14854,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -14758,7 +14886,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -14790,7 +14918,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -14822,7 +14950,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -14854,7 +14982,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -14886,7 +15014,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -14918,7 +15046,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -14950,7 +15078,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -14982,7 +15110,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -15014,7 +15142,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -15046,7 +15174,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -15078,7 +15206,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -15110,7 +15238,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -15142,7 +15270,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -15174,7 +15302,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -15206,7 +15334,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -15238,7 +15366,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -15270,7 +15398,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -15302,7 +15430,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -15334,7 +15462,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -15366,7 +15494,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -15398,7 +15526,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -15430,7 +15558,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -15462,7 +15590,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -15494,7 +15622,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -15526,7 +15654,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -15624,7 +15752,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -15656,7 +15784,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -15688,7 +15816,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -15720,7 +15848,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -15752,7 +15880,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -15784,7 +15912,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -15816,7 +15944,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -15848,7 +15976,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -15880,7 +16008,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -15912,7 +16040,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -15944,7 +16072,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -15976,7 +16104,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -16008,7 +16136,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -16040,7 +16168,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -16072,7 +16200,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -16104,7 +16232,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -16136,7 +16264,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -16168,7 +16296,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -16200,7 +16328,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -16232,7 +16360,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -16264,7 +16392,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -16296,7 +16424,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -16328,7 +16456,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -16360,7 +16488,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -16392,7 +16520,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -16424,7 +16552,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -16456,7 +16584,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -16488,7 +16616,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -16520,7 +16648,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -16552,7 +16680,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -16584,7 +16712,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -16616,7 +16744,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -16648,7 +16776,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -16680,7 +16808,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -16712,7 +16840,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -16744,7 +16872,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -16776,7 +16904,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -16808,7 +16936,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -16840,7 +16968,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -16872,7 +17000,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -16904,7 +17032,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -16936,7 +17064,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -16968,7 +17096,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -17000,7 +17128,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -17032,7 +17160,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -17064,7 +17192,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -17096,7 +17224,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -17128,7 +17256,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -17160,7 +17288,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -17192,7 +17320,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -17224,7 +17352,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -17256,7 +17384,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -17288,7 +17416,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -17320,7 +17448,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -17352,7 +17480,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -17384,7 +17512,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -17416,7 +17544,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -17448,7 +17576,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -17480,7 +17608,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -17512,7 +17640,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -17544,7 +17672,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17704,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -17608,7 +17736,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -17640,7 +17768,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -17672,7 +17800,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -17704,7 +17832,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -17736,7 +17864,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -17768,7 +17896,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -17800,7 +17928,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -17832,7 +17960,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -17864,7 +17992,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -17896,7 +18024,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -17928,7 +18056,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -17960,7 +18088,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -17992,7 +18120,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
@@ -18024,7 +18152,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
@@ -18056,7 +18184,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
@@ -18088,7 +18216,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -18120,7 +18248,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
@@ -18218,7 +18346,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -18250,7 +18378,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -18282,7 +18410,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -18314,7 +18442,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -18346,7 +18474,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -18378,7 +18506,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -18410,7 +18538,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -18442,7 +18570,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -18474,7 +18602,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -18506,7 +18634,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -18538,7 +18666,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -18570,7 +18698,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -18602,7 +18730,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -18634,7 +18762,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -18732,7 +18860,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -18764,7 +18892,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -18796,7 +18924,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -18828,7 +18956,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -18860,7 +18988,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -18892,7 +19020,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -18924,7 +19052,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -18956,7 +19084,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -18988,7 +19116,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -19020,7 +19148,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -19052,7 +19180,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -19084,7 +19212,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -19116,7 +19244,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -19148,7 +19276,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -19180,7 +19308,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -19212,7 +19340,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -19244,7 +19372,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -19276,7 +19404,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -19308,7 +19436,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -19340,7 +19468,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -19372,7 +19500,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -19404,7 +19532,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -19436,7 +19564,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -19468,7 +19596,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -19500,7 +19628,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -19532,7 +19660,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -19564,7 +19692,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -19596,7 +19724,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -19628,7 +19756,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -19660,7 +19788,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -19692,7 +19820,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -19724,7 +19852,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -19756,7 +19884,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -19788,7 +19916,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -19820,7 +19948,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -19852,7 +19980,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -19884,7 +20012,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -19916,7 +20044,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -19948,7 +20076,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -19980,7 +20108,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -20012,7 +20140,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -5618,7 +5618,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>No names or confidential detail. Write it as a pattern. Private to you: encrypted, and the author can’t read it. Timestamped, saved before the ledger.</t>
+          <t>No names or confidential detail. Write it as a pattern. Encrypted and private to you: The Monday After team can’t read it. Timestamped, saved before the ledger.</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr"/>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Only you and the author see your forecast.</t>
+          <t>Only you and The Monday After team see your forecast.</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr"/>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only you can see this. The author of </t>
+          <t xml:space="preserve">Only you can see this. </t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Only you can see this. The author of \""}</t>
+          <t>{"kind": "code", "raw": "\"Only you can see this. \""}</t>
         </is>
       </c>
     </row>
@@ -18776,7 +18776,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> can't read your flight recorder.</t>
+          <t xml:space="preserve"> team can't read your flight recorder.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\" can't read your flight recorder.\""}</t>
+          <t>{"kind": "code", "raw": "\" team can't read your flight recorder.\""}</t>
         </is>
       </c>
     </row>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8653,16 +8653,16 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="inlineStr"/>
+          <t>rows › #6 › variants › #2 › detail › intro</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Who is allowed to make which call, and whether everyone knows it.</t>
+        </is>
+      </c>
       <c r="E254" s="4" t="inlineStr"/>
-      <c r="F254" s="3" t="inlineStr">
-        <is>
-          <t>COPY NEEDED: Decision rights, Drain version: detail page</t>
-        </is>
-      </c>
+      <c r="F254" s="3" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
           <t>site/scenarios/incident-file-01.json</t>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › takeBack › label</t>
+          <t>rows › #6 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Write down who decides whether to pay workers outside the usual chain, and check they know it.</t>
+          <t>The CEO asked who was leading and heard two answers. The agency and the workers got mixed messages while IT and HR sorted it out between them.</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr"/>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › takeBack › from</t>
+          <t>rows › #6 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Decision rights</t>
+          <t>Nobody has agreed who owns a supplier incident. It’s still settled on the day, by whoever picks up the phone.</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › dimension</t>
+          <t>rows › #6 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>The same question is asked again, in the middle of the next incident, and gets the same two answers.</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr"/>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "dimension"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #1 › summary</t>
+          <t>rows › #6 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>You decided what stopped first, so the rest of the work slowed on purpose.</t>
+          <t>There are clear accountabilities for each department and the boundaries are respected. Until a crisis cuts across two departments and no one is sure who should lead.</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8813,12 +8813,12 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #1 › detail</t>
+          <t>rows › #6 › takeBack › label</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>You made a proactive decision to communicate that some work has slowed. Colleagues understand why and your teams are working under less pressure as a result.</t>
+          <t>Write down who decides whether to pay workers outside the usual chain, and check they know it.</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr"/>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 0, "detail"]</t>
+          <t>["screens", 8, "rows", 5, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › summary</t>
+          <t>rows › #6 › takeBack › from</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Planned work stopped while you looked after this, and nobody counted what.</t>
+          <t>Decision rights</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -8877,12 +8877,12 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › intro</t>
+          <t>rows › #7 › dimension</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>What the rest of the organisation did not get done because of the response.</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 6, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › monday</t>
+          <t>rows › #7 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Three people left planned work to cover the weekend. They are compensated but tired. What's the impact on their planned work?</t>
+          <t>You decided what stopped first, so the rest of the work slowed on purpose.</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #7 › variants › #1 › detail</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>Two pieces of work have slipped. The reasons are not on any report.</t>
+          <t>You made a proactive decision to communicate that some work has slowed. Colleagues understand why and your teams are working under less pressure as a result.</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail"]</t>
         </is>
       </c>
     </row>
@@ -8973,12 +8973,12 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › nextTime</t>
+          <t>rows › #7 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>The same work stops first again, because nobody agreed in advance what should.</t>
+          <t>Planned work stopped while you looked after this, and nobody counted what.</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › paper</t>
+          <t>rows › #7 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>The portfolio report is green for now. The impact of this weekend won't be visible immediately.</t>
+          <t>What the rest of the organisation did not get done because of the response.</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr"/>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › takeBack › label</t>
+          <t>rows › #7 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>List the work you would stop first in an incident, and tell the people it affects.</t>
+          <t>Three people left planned work to cover the weekend. They are compensated but tired. What's the impact on their planned work?</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr"/>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -9069,12 +9069,12 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › takeBack › from</t>
+          <t>rows › #7 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Two pieces of work have slipped. The reasons are not on any report.</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>footnote</t>
+          <t>rows › #7 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Tap a row for three months on and next time. Flag what you’d take back.</t>
+          <t>The same work stops first again, because nobody agreed in advance what should.</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>["screens", 8, "footnote"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>rows › #7 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>Choose what to take back →</t>
+          <t>The portfolio report is green for now. The impact of this weekend won't be visible immediately.</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr"/>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>["screens", 8, "button"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -9160,17 +9160,17 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>rows › #7 › takeBack › label</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Your move</t>
+          <t>List the work you would stop first in an incident, and tell the people it affects.</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>["screens", 9, "header", "label"]</t>
+          <t>["screens", 8, "rows", 6, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -9192,17 +9192,17 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>rows › #7 › takeBack › from</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>5 of 5</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr"/>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>["screens", 9, "header", "step"]</t>
+          <t>["screens", 8, "rows", 6, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -9224,17 +9224,17 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>footnote</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Take one thing back.</t>
+          <t>Tap a row for three months on and next time. Flag what you’d take back.</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr"/>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>["screens", 9, "title"]</t>
+          <t>["screens", 8, "footnote"]</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>button</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>You flagged {count}. Pick the one you’ll actually do. One is enough.</t>
+          <t>Choose what to take back →</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr"/>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>["screens", 9, "intro"]</t>
+          <t>["screens", 8, "button"]</t>
         </is>
       </c>
     </row>
@@ -9293,12 +9293,12 @@
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>You didn’t flag anything this time. You can go back to the ledger and flag something, or close the file.</t>
+          <t>The Monday After · Your move</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr"/>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>["screens", 9, "none"]</t>
+          <t>["screens", 9, "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -9325,12 +9325,12 @@
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>whenKicker</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>By when</t>
+          <t>5 of 5</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenKicker"]</t>
+          <t>["screens", 9, "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #1 › label</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>1 week</t>
+          <t>Take one thing back.</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 0, "label"]</t>
+          <t>["screens", 9, "title"]</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #1 › phrase</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>By one week from today.</t>
+          <t>You flagged {count}. Pick the one you’ll actually do. One is enough.</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 0, "phrase"]</t>
+          <t>["screens", 9, "intro"]</t>
         </is>
       </c>
     </row>
@@ -9421,12 +9421,12 @@
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #2 › label</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>2 weeks</t>
+          <t>You didn’t flag anything this time. You can go back to the ledger and flag something, or close the file.</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 1, "label"]</t>
+          <t>["screens", 9, "none"]</t>
         </is>
       </c>
     </row>
@@ -9453,12 +9453,12 @@
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #2 › phrase</t>
+          <t>whenKicker</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>By two weeks from today.</t>
+          <t>By when</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr"/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 1, "phrase"]</t>
+          <t>["screens", 9, "whenKicker"]</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #3 › label</t>
+          <t>whenOptions › #1 › label</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>1 week</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 2, "label"]</t>
+          <t>["screens", 9, "whenOptions", 0, "label"]</t>
         </is>
       </c>
     </row>
@@ -9517,12 +9517,12 @@
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #3 › phrase</t>
+          <t>whenOptions › #1 › phrase</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>By one month from today.</t>
+          <t>By one week from today.</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr"/>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 2, "phrase"]</t>
+          <t>["screens", 9, "whenOptions", 0, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>followUp</t>
+          <t>whenOptions › #2 › label</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Ask me in 30 days whether I did it. One email, and you can stop it any time.</t>
+          <t>2 weeks</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>["screens", 9, "followUp"]</t>
+          <t>["screens", 9, "whenOptions", 1, "label"]</t>
         </is>
       </c>
     </row>
@@ -9581,12 +9581,12 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>followUpPromise</t>
+          <t>whenOptions › #2 › phrase</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>I’ll ask you in 30 days whether you did.</t>
+          <t>By two weeks from today.</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>["screens", 9, "followUpPromise"]</t>
+          <t>["screens", 9, "whenOptions", 1, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>whenOptions › #3 › label</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Save and close the file →</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>["screens", 9, "button"]</t>
+          <t>["screens", 9, "whenOptions", 2, "label"]</t>
         </is>
       </c>
     </row>
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>whenOptions › #3 › phrase</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>Skip, close the file</t>
+          <t>By one month from today.</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr"/>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>["screens", 9, "skip"]</t>
+          <t>["screens", 9, "whenOptions", 2, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -9672,17 +9672,17 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>followUp</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Incident File 01 · The Monday After</t>
+          <t>Ask me in 30 days whether I did it. One email, and you can stop it any time.</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr"/>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>["screens", 10, "header", "label"]</t>
+          <t>["screens", 9, "followUp"]</t>
         </is>
       </c>
     </row>
@@ -9704,17 +9704,17 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>followUpPromise</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>I’ll ask you in 30 days whether you did.</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr"/>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>["screens", 10, "header", "step"]</t>
+          <t>["screens", 9, "followUpPromise"]</t>
         </is>
       </c>
     </row>
@@ -9736,17 +9736,17 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>kicker</t>
+          <t>button</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Your Monday After</t>
+          <t>Save and close the file →</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr"/>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>["screens", 10, "kicker"]</t>
+          <t>["screens", 9, "button"]</t>
         </is>
       </c>
     </row>
@@ -9768,17 +9768,17 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › prefix</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">You </t>
+          <t>Skip, close the file</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr"/>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "prefix"]</t>
+          <t>["screens", 9, "skip"]</t>
         </is>
       </c>
     </row>
@@ -9805,12 +9805,12 @@
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › A</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>built the list</t>
+          <t>Incident File 01 · The Monday After</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr"/>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "A"]</t>
+          <t>["screens", 10, "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9837,12 @@
       </c>
       <c r="C291" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › B</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>pressed the agency</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr"/>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "B"]</t>
+          <t>["screens", 10, "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › C</t>
+          <t>kicker</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>bridged the gap</t>
+          <t>Your Monday After</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr"/>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "C"]</t>
+          <t>["screens", 10, "kicker"]</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › D</t>
+          <t>mirror › opening › prefix</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>told the workers early</t>
+          <t xml:space="preserve">You </t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "D"]</t>
+          <t>["screens", 10, "mirror", "opening", "prefix"]</t>
         </is>
       </c>
     </row>
@@ -9933,12 +9933,12 @@
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › E</t>
+          <t>mirror › opening › phrases › A</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>went to worker representatives early</t>
+          <t>built the list</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr"/>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "E"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "A"]</t>
         </is>
       </c>
     </row>
@@ -9965,12 +9965,12 @@
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › F</t>
+          <t>mirror › opening › phrases › B</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>protected the critical work</t>
+          <t>pressed the agency</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "F"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "B"]</t>
         </is>
       </c>
     </row>
@@ -9997,12 +9997,12 @@
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>mirror › middle › #1 › text</t>
+          <t>mirror › opening › phrases › C</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>You now know who these people are.</t>
+          <t>bridged the gap</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "middle", 0, "text"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "C"]</t>
         </is>
       </c>
     </row>
@@ -10029,12 +10029,12 @@
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>mirror › middle › #2 › text</t>
+          <t>mirror › opening › phrases › D</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>You still don't have one list of these people.</t>
+          <t>told the workers early</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "middle", 1, "text"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "D"]</t>
         </is>
       </c>
     </row>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 1 › did</t>
+          <t>mirror › opening › phrases › E</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>You kept the most exposed people paid.</t>
+          <t>went to worker representatives early</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "1", "did"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "E"]</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 1 › still</t>
+          <t>mirror › opening › phrases › F</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who owns the supplier's supplier.</t>
+          <t>protected the critical work</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr"/>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "1", "still"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "F"]</t>
         </is>
       </c>
     </row>
@@ -10125,12 +10125,12 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 2 › did</t>
+          <t>mirror › middle › #1 › text</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>You said what you knew and what you didn't, before the group chat did.</t>
+          <t>You now know who these people are.</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "2", "did"]</t>
+          <t>["screens", 10, "mirror", "middle", 0, "text"]</t>
         </is>
       </c>
     </row>
@@ -10157,12 +10157,12 @@
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 2 › still</t>
+          <t>mirror › middle › #2 › text</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>You still can't say when anyone will be paid, or who owns the supplier's supplier.</t>
+          <t>You still don't have one list of these people.</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr"/>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "2", "still"]</t>
+          <t>["screens", 10, "mirror", "middle", 1, "text"]</t>
         </is>
       </c>
     </row>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 3 › did</t>
+          <t>mirror › ending › parts › 1 › did</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>You made it the CEO's decision, so it had an owner by Saturday.</t>
+          <t>You kept the most exposed people paid.</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "3", "did"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "1", "did"]</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 3 › still</t>
+          <t>mirror › ending › parts › 1 › still</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>You still haven't asked who should have owned the supplier's supplier before it mattered.</t>
+          <t>You still don't know who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "3", "still"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "1", "still"]</t>
         </is>
       </c>
     </row>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 4 › did</t>
+          <t>mirror › ending › parts › 2 › did</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>You know what else this provider touches.</t>
+          <t>You said what you knew and what you didn't, before the group chat did.</t>
         </is>
       </c>
       <c r="E304" s="4" t="inlineStr"/>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "4", "did"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "2", "did"]</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 4 › still</t>
+          <t>mirror › ending › parts › 2 › still</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>You still haven't decided who watches it.</t>
+          <t>You still can't say when anyone will be paid, or who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "4", "still"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "2", "still"]</t>
         </is>
       </c>
     </row>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 5 › did</t>
+          <t>mirror › ending › parts › 3 › did</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>You protected Monday.</t>
+          <t>You made it the CEO's decision, so it had an owner by Saturday.</t>
         </is>
       </c>
       <c r="E306" s="4" t="inlineStr"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "5", "did"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "3", "did"]</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 5 › still</t>
+          <t>mirror › ending › parts › 3 › still</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who will be paid, or who owns the supplier's supplier.</t>
+          <t>You still haven't asked who should have owned the supplier's supplier before it mattered.</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr"/>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "5", "still"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "3", "still"]</t>
         </is>
       </c>
     </row>
@@ -10381,12 +10381,12 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>mirror › fallback</t>
+          <t>mirror › ending › parts › 4 › did</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who owns the supplier's supplier.</t>
+          <t>You know what else this provider touches.</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "fallback"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "4", "did"]</t>
         </is>
       </c>
     </row>
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>tagline</t>
+          <t>mirror › ending › parts › 4 › still</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>Lucky, or designed? Only one of those repeats.</t>
+          <t>You still haven't decided who watches it.</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr"/>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>["screens", 10, "tagline"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "4", "still"]</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>takingKicker</t>
+          <t>mirror › ending › parts › 5 › did</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>You’re taking this back</t>
+          <t>You protected Monday.</t>
         </is>
       </c>
       <c r="E310" s="4" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>["screens", 10, "takingKicker"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "5", "did"]</t>
         </is>
       </c>
     </row>
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>recorder › kicker</t>
+          <t>mirror › ending › parts › 5 › still</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>Your flight recorder</t>
+          <t>You still don't know who will be paid, or who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "kicker"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "5", "still"]</t>
         </is>
       </c>
     </row>
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>recorder › text</t>
+          <t>mirror › fallback</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Want a copy of what you wrote? We’ll email it to you. Nobody else can read it.</t>
+          <t>You still don't know who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E312" s="4" t="inlineStr"/>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "text"]</t>
+          <t>["screens", 10, "mirror", "fallback"]</t>
         </is>
       </c>
     </row>
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>recorder › button</t>
+          <t>tagline</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>Email me my flight recorder</t>
+          <t>Lucky, or designed? Only one of those repeats.</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "button"]</t>
+          <t>["screens", 10, "tagline"]</t>
         </is>
       </c>
     </row>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>recorder › previewNote</t>
+          <t>takingKicker</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>In the finished version, this emails you a copy.</t>
+          <t>You’re taking this back</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr"/>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "previewNote"]</t>
+          <t>["screens", 10, "takingKicker"]</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>share › kicker</t>
+          <t>recorder › kicker</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>Pass it on</t>
+          <t>Your flight recorder</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "kicker"]</t>
+          <t>["screens", 10, "recorder", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>share › text</t>
+          <t>recorder › text</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Send this to the person you'd most like to answer it differently.</t>
+          <t>Want a copy of what you wrote? We’ll email it to you. Nobody else can read it.</t>
         </is>
       </c>
       <c r="E316" s="4" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "text"]</t>
+          <t>["screens", 10, "recorder", "text"]</t>
         </is>
       </c>
     </row>
@@ -10669,12 +10669,12 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>share › button</t>
+          <t>recorder › button</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>Share this file</t>
+          <t>Email me my flight recorder</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "button"]</t>
+          <t>["screens", 10, "recorder", "button"]</t>
         </is>
       </c>
     </row>
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>share › copied</t>
+          <t>recorder › previewNote</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Link copied.</t>
+          <t>In the finished version, this emails you a copy.</t>
         </is>
       </c>
       <c r="E318" s="4" t="inlineStr"/>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "copied"]</t>
+          <t>["screens", 10, "recorder", "previewNote"]</t>
         </is>
       </c>
     </row>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>team › text</t>
+          <t>share › kicker</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>Some of these questions are hard to settle alone. If you'd like to run this with your team, reply to this email and I'll show you how.</t>
+          <t>Pass it on</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>["screens", 10, "team", "text"]</t>
+          <t>["screens", 10, "share", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -10765,12 +10765,12 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>team › button</t>
+          <t>share › text</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Reply “team”</t>
+          <t>Send this to the person you'd most like to answer it differently.</t>
         </is>
       </c>
       <c r="E320" s="4" t="inlineStr"/>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>["screens", 10, "team", "button"]</t>
+          <t>["screens", 10, "share", "text"]</t>
         </is>
       </c>
     </row>
@@ -10797,12 +10797,12 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>share › button</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>Incident File 02 arrives next month.</t>
+          <t>Share this file</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>["screens", 10, "next"]</t>
+          <t>["screens", 10, "share", "button"]</t>
         </is>
       </c>
     </row>
@@ -10824,17 +10824,17 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>share › copied</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>Link copied.</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr"/>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>["threads", "t1", "header", "label"]</t>
+          <t>["screens", 10, "share", "copied"]</t>
         </is>
       </c>
     </row>
@@ -10856,17 +10856,17 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>team › text</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Some of these questions are hard to settle alone. If you'd like to run this with your team, reply to this email and I'll show you how.</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>["threads", "t1", "header", "step"]</t>
+          <t>["screens", 10, "team", "text"]</t>
         </is>
       </c>
     </row>
@@ -10888,17 +10888,17 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>team › button</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>Reply “team”</t>
         </is>
       </c>
       <c r="E324" s="4" t="inlineStr"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>["threads", "t1", "chip", "kicker"]</t>
+          <t>["screens", 10, "team", "button"]</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>Are you owning this?</t>
+          <t>Incident File 02 arrives next month.</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>["threads", "t1", "chip", "title"]</t>
+          <t>["screens", 10, "next"]</t>
         </is>
       </c>
     </row>
@@ -10957,12 +10957,12 @@
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Are you owning this?</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>["threads", "t1", "title"]</t>
+          <t>["threads", "t1", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -10989,12 +10989,12 @@
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>intro › #1 › text</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>You stepped in alongside HR. The CEO has asked who is leading.</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 0, "text"]</t>
+          <t>["threads", "t1", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11021,12 @@
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>intro › #2 › text</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>You agreed HR would lead. The CEO has asked who they should call.</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 1, "text"]</t>
+          <t>["threads", "t1", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -11053,12 +11053,12 @@
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>intro › #3 › text</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>You took it from HR. The CEO has asked who is leading, and so has HR.</t>
+          <t>Are you owning this?</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 2, "text"]</t>
+          <t>["threads", "t1", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -11085,12 +11085,12 @@
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Front it</t>
+          <t>Are you owning this?</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr"/>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "title"]</t>
+          <t>["threads", "t1", "title"]</t>
         </is>
       </c>
     </row>
@@ -11117,12 +11117,12 @@
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>intro › #1 › text</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>You are the visible lead, to the CEO and to the workers.</t>
+          <t>You stepped in alongside HR. The CEO has asked who is leading.</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr"/>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "body"]</t>
+          <t>["threads", "t1", "intro", 0, "text"]</t>
         </is>
       </c>
     </row>
@@ -11149,12 +11149,12 @@
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>intro › #2 › text</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>You can carry the workers' trust and the CEO's confidence at once, and HR will not read it as a takeover.</t>
+          <t>You agreed HR would lead. The CEO has asked who they should call.</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr"/>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "intro", 1, "text"]</t>
         </is>
       </c>
     </row>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>intro › #3 › text</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>One clear voice. The CEO and the workers know who to call.</t>
+          <t>You took it from HR. The CEO has asked who is leading, and so has HR.</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr"/>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t1", "intro", 2, "text"]</t>
         </is>
       </c>
     </row>
@@ -11213,12 +11213,12 @@
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>HR's ownership weakens, and your name is on it if it goes wrong.</t>
+          <t>Front it</t>
         </is>
       </c>
       <c r="E334" s="4" t="inlineStr"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -11245,12 +11245,12 @@
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>Back HR, visibly</t>
+          <t>You are the visible lead, to the CEO and to the workers.</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "title"]</t>
+          <t>["threads", "t1", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -11277,12 +11277,12 @@
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>You tell the CEO you are supporting the Chief People Officer.</t>
+          <t>You can carry the workers' trust and the CEO's confidence at once, and HR will not read it as a takeover.</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "body"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11309,12 +11309,12 @@
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>HR can hold the room with the CEO and the workers, and you will hear in time if it slips.</t>
+          <t>One clear voice. The CEO and the workers know who to call.</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr"/>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11341,12 +11341,12 @@
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>The owner of the relationship stays accountable, and your capacity is kept for the rest of IT.</t>
+          <t>HR's ownership weakens, and your name is on it if it goes wrong.</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11373,12 +11373,12 @@
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>Your influence rests on someone else’s performance, and you may hear late.</t>
+          <t>Back HR, visibly</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -11405,12 +11405,12 @@
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Stay in the background</t>
+          <t>You tell the CEO you are supporting the Chief People Officer.</t>
         </is>
       </c>
       <c r="E340" s="4" t="inlineStr"/>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "title"]</t>
+          <t>["threads", "t1", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -11437,12 +11437,12 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>You help quietly and step forward only if asked.</t>
+          <t>HR can hold the room with the CEO and the workers, and you will hear in time if it slips.</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr"/>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "body"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>You will be asked in time, and HR will tell you when it starts to slip.</t>
+          <t>The owner of the relationship stays accountable, and your capacity is kept for the rest of IT.</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr"/>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>Your capacity stays free for the rest of IT, and HR keeps ownership of its own relationship.</t>
+          <t>Your influence rests on someone else’s performance, and you may hear late.</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11533,12 +11533,12 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>You hear late, and the delay is invisible until it is not.</t>
+          <t>Stay in the background</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr"/>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>All three can be reasonable. The question is who the CEO believes owns it.</t>
+          <t>You help quietly and step forward only if asked.</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr"/>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>["threads", "t1", "closing"]</t>
+          <t>["threads", "t1", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -11592,17 +11592,17 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>You will be asked in time, and HR will tell you when it starts to slip.</t>
         </is>
       </c>
       <c r="E346" s="4" t="inlineStr"/>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>["threads", "t2", "header", "label"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11624,17 +11624,17 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Your capacity stays free for the rest of IT, and HR keeps ownership of its own relationship.</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>["threads", "t2", "header", "step"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11656,17 +11656,17 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>You hear late, and the delay is invisible until it is not.</t>
         </is>
       </c>
       <c r="E348" s="4" t="inlineStr"/>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>["threads", "t2", "chip", "kicker"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11688,17 +11688,17 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>All three can be reasonable. The question is who the CEO believes owns it.</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr"/>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>["threads", "t2", "chip", "title"]</t>
+          <t>["threads", "t1", "closing"]</t>
         </is>
       </c>
     </row>
@@ -11725,12 +11725,12 @@
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E350" s="4" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>["threads", "t2", "title"]</t>
+          <t>["threads", "t2", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>The agency passed assurance when you bought it. Nobody looked at who pays its workers.</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr"/>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>["threads", "t2", "intro"]</t>
+          <t>["threads", "t2", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -11789,12 +11789,12 @@
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E352" s="4" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "title"]</t>
+          <t>["threads", "t2", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -11821,12 +11821,12 @@
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>Knows the technology</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr"/>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "body"]</t>
+          <t>["threads", "t2", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -11853,12 +11853,12 @@
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>IT knows what to look for in a payroll provider, and has the standing to ask for it.</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr"/>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "title"]</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>The check is technically sound, and it covers systems IT already protects.</t>
+          <t>The agency passed assurance when you bought it. Nobody looked at who pays its workers.</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr"/>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t2", "intro"]</t>
         </is>
       </c>
     </row>
@@ -11917,12 +11917,12 @@
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>IT has to know the contract exists first. Here it never saw it, so the check never starts.</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -11949,12 +11949,12 @@
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Knows the technology</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "title"]</t>
+          <t>["threads", "t2", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -11981,12 +11981,12 @@
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Owns the relationship</t>
+          <t>IT knows what to look for in a payroll provider, and has the standing to ask for it.</t>
         </is>
       </c>
       <c r="E358" s="4" t="inlineStr"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "body"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>HR has, or can buy in, the skill to judge a payroll provider's resilience.</t>
+          <t>The check is technically sound, and it covers systems IT already protects.</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12045,12 +12045,12 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>The owner of the relationship stays accountable.</t>
+          <t>IT has to know the contract exists first. Here it never saw it, so the check never starts.</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr"/>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12077,12 +12077,12 @@
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>The check is shallow, which risks being paper again.</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>The agency</t>
+          <t>Owns the relationship</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr"/>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "title"]</t>
+          <t>["threads", "t2", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -12141,12 +12141,12 @@
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>It's their supply chain</t>
+          <t>HR has, or can buy in, the skill to judge a payroll provider's resilience.</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr"/>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "body"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12173,12 +12173,12 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>The agency is checking its own supplier, and will tell you honestly if it is not.</t>
+          <t>The owner of the relationship stays accountable.</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr"/>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12205,12 +12205,12 @@
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>The responsibility sits with the party closest to the supplier, and asking costs you nothing.</t>
+          <t>The check is shallow, which risks being paper again.</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>You are relying on a statement, not evidence, from someone who loses the contract if the answer is bad.</t>
+          <t>The agency</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -12269,12 +12269,12 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>Shared, by design</t>
+          <t>It's their supply chain</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "title"]</t>
+          <t>["threads", "t2", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -12301,12 +12301,12 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › body</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Agreed in advance, revisited as the supplier's role changes</t>
+          <t>The agency is checking its own supplier, and will tell you honestly if it is not.</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr"/>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "body"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › assuming</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>Someone agreed in advance who checks what, and keeps that agreement alive as the supplier's role changes.</t>
+          <t>The responsibility sits with the party closest to the supplier, and asking costs you nothing.</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr"/>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12365,12 +12365,12 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › gain</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Nothing falls between IT and HR, and the check is revisited when the supplier changes.</t>
+          <t>You are relying on a statement, not evidence, from someone who loses the contract if the answer is bad.</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › cost</t>
+          <t>options › #4 › title</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>It takes effort before anything has gone wrong, which is hard to justify, and agreements like this drift if nobody owns them.</t>
+          <t>Shared, by design</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 3, "title"]</t>
         </is>
       </c>
     </row>
@@ -12429,12 +12429,12 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #4 › body</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>All four can be reasonable. The question is whether anyone decided this agency was critical.</t>
+          <t>Agreed in advance, revisited as the supplier's role changes</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>["threads", "t2", "closing"]</t>
+          <t>["threads", "t2", "options", 3, "body"]</t>
         </is>
       </c>
     </row>
@@ -12461,12 +12461,12 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #4 › reveal › assuming</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>A question about what a sensible owner would check, not what the law requires.</t>
+          <t>Someone agreed in advance who checks what, and keeps that agreement alive as the supplier's role changes.</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr"/>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>["threads", "t2", "disclaimer"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>takeBack › label</t>
+          <t>options › #4 › reveal › gain</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Ask who should have checked the agency’s payroll provider.</t>
+          <t>Nothing falls between IT and HR, and the check is revisited when the supplier changes.</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "label"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12525,12 +12525,12 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>takeBack › commit</t>
+          <t>options › #4 › reveal › cost</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>Ask who should have checked the agency’s payroll provider, and write down the answer.</t>
+          <t>It takes effort before anything has gone wrong, which is hard to justify, and agreements like this drift if nobody owns them.</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr"/>
@@ -12542,7 +12542,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "commit"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12557,12 +12557,12 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>takeBack › from</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>All four can be reasonable. The question is whether anyone decided this agency was critical.</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "from"]</t>
+          <t>["threads", "t2", "closing"]</t>
         </is>
       </c>
     </row>
@@ -12584,17 +12584,17 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>A question about what a sensible owner would check, not what the law requires.</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr"/>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>["threads", "t3", "header", "label"]</t>
+          <t>["threads", "t2", "disclaimer"]</t>
         </is>
       </c>
     </row>
@@ -12616,17 +12616,17 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>takeBack › label</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>Ask who should have checked the agency’s payroll provider.</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr"/>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>["threads", "t3", "header", "step"]</t>
+          <t>["threads", "t2", "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -12648,17 +12648,17 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>takeBack › commit</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>Ask who should have checked the agency’s payroll provider, and write down the answer.</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr"/>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "kicker"]</t>
+          <t>["threads", "t2", "takeBack", "commit"]</t>
         </is>
       </c>
     </row>
@@ -12680,17 +12680,17 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>takeBack › from</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>The clock</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr"/>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "title"]</t>
+          <t>["threads", "t2", "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>chip › sub</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>Does anyone’s clock start now?</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr"/>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "sub"]</t>
+          <t>["threads", "t3", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -12749,12 +12749,12 @@
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>The clock.</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>["threads", "t3", "title"]</t>
+          <t>["threads", "t3", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -12781,12 +12781,12 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>situation › time</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 09:10</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>["threads", "t3", "situation", "time"]</t>
+          <t>["threads", "t3", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>situation › text</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>The agency’s payroll provider “cannot rule out” a security incident. Pay data is personal data. What do you do about the clock?</t>
+          <t>The clock</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>["threads", "t3", "situation", "text"]</t>
+          <t>["threads", "t3", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -12845,12 +12845,12 @@
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>chip › sub</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>Wait for confirmation</t>
+          <t>Does anyone’s clock start now?</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr"/>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "title"]</t>
+          <t>["threads", "t3", "chip", "sub"]</t>
         </is>
       </c>
     </row>
@@ -12877,12 +12877,12 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Nothing to act on until someone says it is an incident.</t>
+          <t>The clock.</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr"/>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "body"]</t>
+          <t>["threads", "t3", "title"]</t>
         </is>
       </c>
     </row>
@@ -12909,12 +12909,12 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>situation › time</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>Nothing starts until someone confirms an incident, and nobody will later ask what you knew on Saturday.</t>
+          <t>Saturday, 09:10</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "situation", "time"]</t>
         </is>
       </c>
     </row>
@@ -12941,12 +12941,12 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>situation › text</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>You do not raise an alarm over a maybe.</t>
+          <t>The agency’s payroll provider “cannot rule out” a security incident. Pay data is personal data. What do you do about the clock?</t>
         </is>
       </c>
       <c r="E388" s="4" t="inlineStr"/>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t3", "situation", "text"]</t>
         </is>
       </c>
     </row>
@@ -12973,12 +12973,12 @@
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>If the clock runs from when you became aware, time has already passed, and you have no record of what you knew.</t>
+          <t>Wait for confirmation</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr"/>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -13005,12 +13005,12 @@
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Note when you were told</t>
+          <t>Nothing to act on until someone says it is an incident.</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr"/>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "title"]</t>
+          <t>["threads", "t3", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -13037,12 +13037,12 @@
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>Start a timestamped log of what you knew and when.</t>
+          <t>Nothing starts until someone confirms an incident, and nobody will later ask what you knew on Saturday.</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr"/>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "body"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>The record you start now will matter later, and someone else is deciding who reports.</t>
+          <t>You do not raise an alarm over a maybe.</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13101,12 +13101,12 @@
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>You can show what you knew and when.</t>
+          <t>If the clock runs from when you became aware, time has already passed, and you have no record of what you knew.</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>A log is not a decision. Someone still has to own the call.</t>
+          <t>Note when you were told</t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr"/>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -13165,12 +13165,12 @@
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>Ask your data protection lead</t>
+          <t>Start a timestamped log of what you knew and when.</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "title"]</t>
+          <t>["threads", "t3", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -13197,12 +13197,12 @@
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Are you a controller or a processor here, and who tells the regulator?</t>
+          <t>The record you start now will matter later, and someone else is deciding who reports.</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "body"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>You have a data protection lead, they can be reached on a Saturday, and they can say what your role is.</t>
+          <t>You can show what you knew and when.</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13261,12 +13261,12 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>You get a view early on whether you are a controller or a processor here, and who has to tell whom.</t>
+          <t>A log is not a decision. Someone still has to own the call.</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13293,12 +13293,12 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>If nobody can be reached, hours pass. And the honest answer may be "it depends".</t>
+          <t>Ask your data protection lead</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -13325,12 +13325,12 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Ask the agency in writing</t>
+          <t>Are you a controller or a processor here, and who tells the regulator?</t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "title"]</t>
+          <t>["threads", "t3", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -13357,12 +13357,12 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › body</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>Has it told its customers, and has its provider told it?</t>
+          <t>You have a data protection lead, they can be reached on a Saturday, and they can say what your role is.</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr"/>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "body"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › assuming</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>The agency knows what its provider has told it, and will answer in writing.</t>
+          <t>You get a view early on whether you are a controller or a processor here, and who has to tell whom.</t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr"/>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13421,12 +13421,12 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › gain</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>You have a dated record of what you asked and what you were told.</t>
+          <t>If nobody can be reached, hours pass. And the honest answer may be "it depends".</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr"/>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13453,12 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › cost</t>
+          <t>options › #4 › title</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>A written question can slow things down and make the agency defensive. It may not have the answer either.</t>
+          <t>Ask the agency in writing</t>
         </is>
       </c>
       <c r="E404" s="4" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 3, "title"]</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #4 › body</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>The clock may start when you become aware, not when someone confirms.</t>
+          <t>Has it told its customers, and has its provider told it?</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr"/>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>["threads", "t3", "closing"]</t>
+          <t>["threads", "t3", "options", 3, "body"]</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #4 › reveal › assuming</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Questions to check with your data protection lead or counsel. Not legal advice.</t>
+          <t>The agency knows what its provider has told it, and will answer in writing.</t>
         </is>
       </c>
       <c r="E406" s="4" t="inlineStr"/>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>["threads", "t3", "disclaimer"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13544,17 +13544,17 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #4 › reveal › gain</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>You have a dated record of what you asked and what you were told.</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>["threads", "t4", "header", "label"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13576,17 +13576,17 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #4 › reveal › cost</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>A written question can slow things down and make the agency defensive. It may not have the answer either.</t>
         </is>
       </c>
       <c r="E408" s="4" t="inlineStr"/>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>["threads", "t4", "header", "step"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13608,17 +13608,17 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 14:00 · Pull a thread</t>
+          <t>The clock may start when you become aware, not when someone confirms.</t>
         </is>
       </c>
       <c r="E409" s="4" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "kicker"]</t>
+          <t>["threads", "t3", "closing"]</t>
         </is>
       </c>
     </row>
@@ -13640,17 +13640,17 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>A neighbour will pay its contractors directly</t>
+          <t>Questions to check with your data protection lead or counsel. Not legal advice.</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr"/>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "title"]</t>
+          <t>["threads", "t3", "disclaimer"]</t>
         </is>
       </c>
     </row>
@@ -13677,12 +13677,12 @@
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>chip › sub</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>Your workers have seen it.</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr"/>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "sub"]</t>
+          <t>["threads", "t4", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -13709,12 +13709,12 @@
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 14:00</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E412" s="4" t="inlineStr"/>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>["threads", "t4", "time"]</t>
+          <t>["threads", "t4", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -13741,12 +13741,12 @@
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>You're not the only customer.</t>
+          <t>Saturday, 14:00 · Pull a thread</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr"/>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>["threads", "t4", "title"]</t>
+          <t>["threads", "t4", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -13773,12 +13773,12 @@
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>situation › text</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>A neighbouring organisation that uses the same agency announces it will pay its contractors directly. Your workers have seen it.</t>
+          <t>A neighbour will pay its contractors directly</t>
         </is>
       </c>
       <c r="E414" s="4" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>["threads", "t4", "situation", "text"]</t>
+          <t>["threads", "t4", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -13805,12 +13805,12 @@
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>prompt</t>
+          <t>chip › sub</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>What do you do? Pick one.</t>
+          <t>Your workers have seen it.</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>["threads", "t4", "prompt"]</t>
+          <t>["threads", "t4", "chip", "sub"]</t>
         </is>
       </c>
     </row>
@@ -13837,12 +13837,12 @@
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>time</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Call the other customers and agree a common line</t>
+          <t>Saturday, 14:00</t>
         </is>
       </c>
       <c r="E416" s="4" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 0, "title"]</t>
+          <t>["threads", "t4", "time"]</t>
         </is>
       </c>
     </row>
@@ -13869,12 +13869,12 @@
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>Wait and let them move first</t>
+          <t>You're not the only customer.</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr"/>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 1, "title"]</t>
+          <t>["threads", "t4", "title"]</t>
         </is>
       </c>
     </row>
@@ -13901,12 +13901,12 @@
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>situation › text</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>Pay directly too, now</t>
+          <t>A neighbouring organisation that uses the same agency announces it will pay its contractors directly. Your workers have seen it.</t>
         </is>
       </c>
       <c r="E418" s="4" t="inlineStr"/>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 2, "title"]</t>
+          <t>["threads", "t4", "situation", "text"]</t>
         </is>
       </c>
     </row>
@@ -13933,12 +13933,12 @@
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>prompt</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>Hold your line and explain why</t>
+          <t>What do you do? Pick one.</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr"/>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 3, "title"]</t>
+          <t>["threads", "t4", "prompt"]</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>options › #5 › title</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Take it to a shared forum or the agency</t>
+          <t>Call the other customers and agree a common line</t>
         </is>
       </c>
       <c r="E420" s="4" t="inlineStr"/>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 4, "title"]</t>
+          <t>["threads", "t4", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -13997,12 +13997,12 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>Coordinating with other customers may have limits depending on sector and country. Check before you act.</t>
+          <t>Wait and let them move first</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr"/>
@@ -14013,6 +14013,134 @@
         </is>
       </c>
       <c r="H421" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 1, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="n">
+        <v>421</v>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="inlineStr">
+        <is>
+          <t>options › #3 › title</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>Pay directly too, now</t>
+        </is>
+      </c>
+      <c r="E422" s="4" t="inlineStr"/>
+      <c r="F422" s="3" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 2, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="3" t="n">
+        <v>422</v>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C423" s="3" t="inlineStr">
+        <is>
+          <t>options › #4 › title</t>
+        </is>
+      </c>
+      <c r="D423" s="3" t="inlineStr">
+        <is>
+          <t>Hold your line and explain why</t>
+        </is>
+      </c>
+      <c r="E423" s="4" t="inlineStr"/>
+      <c r="F423" s="3" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 3, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="inlineStr">
+        <is>
+          <t>options › #5 › title</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>Take it to a shared forum or the agency</t>
+        </is>
+      </c>
+      <c r="E424" s="4" t="inlineStr"/>
+      <c r="F424" s="3" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 4, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C425" s="3" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>Coordinating with other customers may have limits depending on sector and country. Check before you act.</t>
+        </is>
+      </c>
+      <c r="E425" s="4" t="inlineStr"/>
+      <c r="F425" s="3" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
         <is>
           <t>["threads", "t4", "disclaimer"]</t>
         </is>
@@ -14086,7 +14214,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -14118,7 +14246,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -14150,7 +14278,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -14182,7 +14310,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -14214,7 +14342,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -14246,7 +14374,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -14278,7 +14406,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -14310,7 +14438,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -14342,7 +14470,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -14374,7 +14502,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -14406,7 +14534,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -14438,7 +14566,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -14470,7 +14598,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -14502,7 +14630,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -14534,7 +14662,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -14566,7 +14694,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -14598,7 +14726,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -14630,7 +14758,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -14662,7 +14790,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -14694,7 +14822,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -14726,7 +14854,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -14758,7 +14886,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -14790,7 +14918,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -14822,7 +14950,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -14854,7 +14982,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -14886,7 +15014,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -14918,7 +15046,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -14950,7 +15078,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -14982,7 +15110,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -15014,7 +15142,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -15046,7 +15174,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -15078,7 +15206,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -15110,7 +15238,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -15142,7 +15270,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -15174,7 +15302,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -15206,7 +15334,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -15238,7 +15366,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -15270,7 +15398,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -15302,7 +15430,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -15334,7 +15462,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -15366,7 +15494,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -15398,7 +15526,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -15430,7 +15558,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -15462,7 +15590,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -15494,7 +15622,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -15526,7 +15654,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -15558,7 +15686,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -15590,7 +15718,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -15622,7 +15750,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -15654,7 +15782,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -15752,7 +15880,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -15784,7 +15912,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -15816,7 +15944,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -15848,7 +15976,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -15880,7 +16008,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -15912,7 +16040,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -15944,7 +16072,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -15976,7 +16104,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -16008,7 +16136,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -16040,7 +16168,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -16072,7 +16200,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -16104,7 +16232,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -16136,7 +16264,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -16168,7 +16296,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -16200,7 +16328,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -16232,7 +16360,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -16264,7 +16392,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -16296,7 +16424,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -16328,7 +16456,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -16360,7 +16488,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -16392,7 +16520,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -16424,7 +16552,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -16456,7 +16584,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -16488,7 +16616,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -16520,7 +16648,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -16552,7 +16680,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -16584,7 +16712,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -16616,7 +16744,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -16648,7 +16776,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -16680,7 +16808,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -16712,7 +16840,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -16744,7 +16872,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -16776,7 +16904,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -16808,7 +16936,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -16840,7 +16968,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -16872,7 +17000,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -16904,7 +17032,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -16936,7 +17064,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -16968,7 +17096,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -17000,7 +17128,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -17032,7 +17160,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -17064,7 +17192,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -17096,7 +17224,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -17128,7 +17256,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -17160,7 +17288,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -17192,7 +17320,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -17224,7 +17352,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -17256,7 +17384,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -17288,7 +17416,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -17320,7 +17448,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -17352,7 +17480,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -17384,7 +17512,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -17416,7 +17544,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -17448,7 +17576,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -17480,7 +17608,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -17512,7 +17640,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -17544,7 +17672,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17704,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -17608,7 +17736,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -17640,7 +17768,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -17672,7 +17800,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -17704,7 +17832,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -17736,7 +17864,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -17768,7 +17896,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -17800,7 +17928,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -17832,7 +17960,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -17864,7 +17992,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -17896,7 +18024,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -17928,7 +18056,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -17960,7 +18088,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -17992,7 +18120,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -18024,7 +18152,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -18056,7 +18184,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -18088,7 +18216,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -18120,7 +18248,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
@@ -18152,7 +18280,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
@@ -18184,7 +18312,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
@@ -18216,7 +18344,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -18248,7 +18376,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
@@ -18346,7 +18474,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -18378,7 +18506,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -18410,7 +18538,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -18442,7 +18570,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -18474,7 +18602,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -18506,7 +18634,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -18538,7 +18666,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -18570,7 +18698,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -18602,7 +18730,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -18634,7 +18762,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -18666,7 +18794,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -18698,7 +18826,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -18730,7 +18858,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -18762,7 +18890,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -18860,7 +18988,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -18892,7 +19020,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -18924,7 +19052,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -18956,7 +19084,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -18988,7 +19116,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -19020,7 +19148,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -19052,7 +19180,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -19084,7 +19212,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -19116,7 +19244,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -19148,7 +19276,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -19180,7 +19308,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -19212,7 +19340,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -19244,7 +19372,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -19276,7 +19404,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -19308,7 +19436,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -19340,7 +19468,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -19372,7 +19500,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -19404,7 +19532,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -19436,7 +19564,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -19468,7 +19596,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -19500,7 +19628,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -19532,7 +19660,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -19564,7 +19692,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -19596,7 +19724,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -19628,7 +19756,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -19660,7 +19788,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -19692,7 +19820,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -19724,7 +19852,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -19756,7 +19884,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -19788,7 +19916,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -19820,7 +19948,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -19852,7 +19980,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -19884,7 +20012,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -19916,7 +20044,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -19948,7 +20076,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -19980,7 +20108,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -20012,7 +20140,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -20044,7 +20172,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -20076,7 +20204,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -20108,7 +20236,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -20140,7 +20268,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #1 › detail</t>
+          <t>rows › #1 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>You have identified gaps in your understanding of supply chain risks. You've used the incident to build a clearer picture and make informed decisions next time.</t>
+          <t>How much you lean on contractors and suppliers, and how many layers deep.</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr"/>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 0, "detail"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #2 › summary</t>
+          <t>rows › #1 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Part of your own incident team is paid through the same chain.</t>
+          <t>You asked what else this provider touches. Part of your own incident team turned out to be paid through the same chain, and now you know.</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr"/>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #2 › detail › intro</t>
+          <t>rows › #1 › variants › #1 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>How much you lean on contractors and suppliers, and how many layers deep.</t>
+          <t>You have a clearer picture of your supply chain risks, beyond the agency. It’s partial, but it’s written down.</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr"/>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -6605,12 +6605,12 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #2 › detail › monday</t>
+          <t>rows › #1 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Part of your own incident team turns out to be paid through the same chain as the workers who might walk.</t>
+          <t>You make informed decisions from a map of your supply chain, not from the first supplier who calls.</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr"/>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -6637,12 +6637,12 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #1 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Nobody has mapped the organisation’s dependence on contractors.</t>
+          <t>Assurance still checks the agency. You now know which questions it doesn’t ask about the suppliers behind it.</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #2 › detail › nextTime</t>
+          <t>rows › #1 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>The next failure exposes similar supply chain dependencies, gaps in your data and dependence on contractors.</t>
+          <t>Part of your own incident team is paid through the same chain.</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr"/>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -6701,12 +6701,12 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>rows › #1 › variants › #2 › detail › paper</t>
+          <t>rows › #1 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Assurance covered the agency. It wasn't designed to interrogate the whole supply chain.</t>
+          <t>How much you lean on contractors and suppliers, and how many layers deep.</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr"/>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › dimension</t>
+          <t>rows › #1 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Single point of failure</t>
+          <t>Part of your own incident team turns out to be paid through the same chain as the workers who might walk.</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr"/>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "dimension"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › summary</t>
+          <t>rows › #1 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>The agency was your only route to these workers. And they were dependent on at least one supplier. You haven't uncovered their other single points of failure.</t>
+          <t>Nobody has mapped the organisation’s dependence on contractors.</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr"/>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › detail › intro</t>
+          <t>rows › #1 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Where one failure stops everything, and how many layers down it sits.</t>
+          <t>The next failure exposes similar supply chain dependencies, gaps in your data and dependence on contractors.</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr"/>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -6829,12 +6829,12 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › detail › monday</t>
+          <t>rows › #1 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Your only route to these workers was one agency. It was dependent on one provider. One failed, so they both failed.</t>
+          <t>Assurance covered the agency. It wasn't designed to interrogate the whole supply chain.</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr"/>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 0, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6861,12 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › detail › threeMonths</t>
+          <t>rows › #2 › dimension</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>The agency has promised a backup plan. Nobody has analysed how dependent your organisation is on the same supplier.</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr"/>
@@ -6878,7 +6878,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 1, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -6893,12 +6893,12 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › detail › nextTime</t>
+          <t>rows › #2 › summary</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>The next single point of failure is one you have not found yet, in a supplier nobody has asked you about.</t>
+          <t>The agency was your only route to these workers. And they were dependent on at least one supplier. You haven't uncovered their other single points of failure.</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr"/>
@@ -6910,7 +6910,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -6925,12 +6925,12 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › detail › paper</t>
+          <t>rows › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Your supplier register lists the agency but does not map the supply chain.</t>
+          <t>Where one failure stops everything, and how many layers down it sits.</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr"/>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › takeBack › label</t>
+          <t>rows › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Pick one supplier and map its dependencies.</t>
+          <t>Your only route to these workers was one agency. It was dependent on one provider. One failed, so they both failed.</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr"/>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>rows › #2 › takeBack › from</t>
+          <t>rows › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Single point of failure</t>
+          <t>The agency has promised a backup plan. Nobody has analysed how dependent your organisation is on the same supplier.</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 1, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › dimension</t>
+          <t>rows › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>The next single point of failure is one you have not found yet, in a supplier nobody has asked you about.</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr"/>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "dimension"]</t>
+          <t>["screens", 8, "rows", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #1 › summary</t>
+          <t>rows › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Three people carried the weekend, and now they're the only ones who know how it worked.</t>
+          <t>Your supplier register lists the agency but does not map the supply chain.</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #1 › detail › intro</t>
+          <t>rows › #2 › takeBack › label</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>How much the people who carried the response have left, and who else can do what they did.</t>
+          <t>Pick one supplier and map its dependencies.</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 1, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -7117,12 +7117,12 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #1 › detail › monday</t>
+          <t>rows › #2 › takeBack › from</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Three people carried the weekend. They did it well, so nobody asked who else could help. Other team members grumble about their lack of opportunity.</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 1, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #1 › detail › threeMonths</t>
+          <t>rows › #3 › dimension</t>
         </is>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>The same three are called first for every incident. The work they put aside has not been picked up.</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr"/>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 2, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -7181,12 +7181,12 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #1 › detail › nextTime</t>
+          <t>rows › #3 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>The next incident starts with the same three people, already tired. They're starting to depend on the overtime involved.</t>
+          <t>Three people carried the weekend, and now they're the only ones who know how it worked.</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #1 › detail › paper</t>
+          <t>rows › #3 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>The incident plan names a team with all the usual suspects. There isn't a plan for what happens when they're burnt out.</t>
+          <t>How much the people who carried the response have left, and who else can do what they did.</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr"/>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -7245,12 +7245,12 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #2 › summary</t>
+          <t>rows › #3 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>The HR team is better placed to manage its suppliers.</t>
+          <t>Three people carried the weekend. They did it well, so nobody asked who else could help. Other team members grumble about their lack of opportunity.</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr"/>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -7277,12 +7277,12 @@
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #2 › detail</t>
+          <t>rows › #3 › variants › #1 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>The HR team has built capability to manage one of its key suppliers and now puts greater value on the IT assurance processes that your team requires.</t>
+          <t>The same three are called first for every incident. The work they put aside has not been picked up.</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr"/>
@@ -7294,7 +7294,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 1, "detail"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -7309,12 +7309,12 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #3 › summary</t>
+          <t>rows › #3 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Three people carried the weekend, and now they're the only ones who know how it worked.</t>
+          <t>The next incident starts with the same three people, already tired. They're starting to depend on the overtime involved.</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 2, "summary"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -7341,12 +7341,12 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #3 › detail › intro</t>
+          <t>rows › #3 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>How much the people who carried the response have left, and who else can do what they did.</t>
+          <t>The incident plan names a team with all the usual suspects. There isn't a plan for what happens when they're burnt out.</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #3 › detail › monday</t>
+          <t>rows › #3 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Three people carried the weekend. They did it well, so nobody asked who else could help. Other team members grumble about their lack of opportunity.</t>
+          <t>The HR team is better placed to manage its suppliers.</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -7405,12 +7405,12 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #3 › detail › threeMonths</t>
+          <t>rows › #3 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>The same three are called first for every incident. The work they put aside has not been picked up.</t>
+          <t>How much the people who carried the response have left, and who else can do what they did.</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr"/>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #3 › detail › nextTime</t>
+          <t>rows › #3 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>The next incident starts with the same three people, already tired. They're starting to depend on the overtime involved.</t>
+          <t>The weekend didn’t fall on the same three people. Others stepped in, and HR built capability to manage one of its key suppliers.</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr"/>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7469,12 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › variants › #3 › detail › paper</t>
+          <t>rows › #3 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>The incident plan names a team with all the usual suspects. There isn't a plan for what happens when they're burnt out.</t>
+          <t>HR handles the agency with more confidence, and now puts greater value on the IT assurance processes your team requires.</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr"/>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › takeBack › label</t>
+          <t>rows › #3 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Name the three people who carry every incident, and one person who could cover each.</t>
+          <t>More than one team can lead a supplier incident, and IT’s people start it rested.</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr"/>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -7533,12 +7533,12 @@
       </c>
       <c r="C219" s="3" t="inlineStr">
         <is>
-          <t>rows › #3 › takeBack › from</t>
+          <t>rows › #3 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>The incident plan still names IT’s usual team. In practice, the load is now shared with HR.</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 2, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › dimension</t>
+          <t>rows › #3 › variants › #3 › summary</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>Three people carried the weekend, and now they're the only ones who know how it worked.</t>
         </is>
       </c>
       <c r="E220" s="4" t="inlineStr"/>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "dimension"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 2, "summary"]</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="C221" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #1 › summary</t>
+          <t>rows › #3 › variants › #3 › detail › intro</t>
         </is>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>IT is firmly in charge, but can it reduce risk?</t>
+          <t>How much the people who carried the response have left, and who else can do what they did.</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr"/>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -7629,12 +7629,12 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #1 › detail</t>
+          <t>rows › #3 › variants › #3 › detail › monday</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>The decision has expanded the scope of your IT function without increasing its budget or capacity. You're better placed to govern the response to the next problem but don't have the levers to reduce the likelihood that there will be a problem.</t>
+          <t>Three people carried the weekend. They did it well, so nobody asked who else could help. Other team members grumble about their lack of opportunity.</t>
         </is>
       </c>
       <c r="E222" s="4" t="inlineStr"/>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 0, "detail"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -7661,12 +7661,12 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #2 › summary</t>
+          <t>rows › #3 › variants › #3 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
         <is>
-          <t>Finance, HR and IT worked together successfully and value IT’s governance processes more highly. How can you use that to increase compliance across the organisation?</t>
+          <t>The same three are called first for every incident. The work they put aside has not been picked up.</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr"/>
@@ -7678,7 +7678,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="C224" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #2 › detail › intro</t>
+          <t>rows › #3 › variants › #3 › detail › nextTime</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>How far people will rely on each other when it is not clear who is in charge.</t>
+          <t>The next incident starts with the same three people, already tired. They're starting to depend on the overtime involved.</t>
         </is>
       </c>
       <c r="E224" s="4" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -7725,12 +7725,12 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #2 › detail › monday</t>
+          <t>rows › #3 › variants › #3 › detail › paper</t>
         </is>
       </c>
       <c r="D225" s="3" t="inlineStr">
         <is>
-          <t>Finance and HR paid people together for the first time, and each saw the other work under pressure.</t>
+          <t>The incident plan names a team with all the usual suspects. There isn't a plan for what happens when they're burnt out.</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr"/>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 2, "variants", 2, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -7757,12 +7757,12 @@
       </c>
       <c r="C226" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #3 › takeBack › label</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>People know who to ring in the other team, and they have started ringing before it is urgent.</t>
+          <t>Name the three people who carry every incident, and one person who could cover each.</t>
         </is>
       </c>
       <c r="E226" s="4" t="inlineStr"/>
@@ -7774,7 +7774,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 2, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #2 › detail › nextTime</t>
+          <t>rows › #3 › takeBack › from</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>The next incident starts with relationships that already work. That only holds while the same people are in post.</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 2, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="C228" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › variants › #2 › detail › paper</t>
+          <t>rows › #4 › dimension</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>The escalation route exists in a document. Whether anyone uses it depends on whether they have worked with the person at the other end.</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E228" s="4" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 3, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › takeBack › label</t>
+          <t>rows › #4 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>Book thirty minutes with your counterpart in Finance or HR before you need them.</t>
+          <t>IT is firmly in charge, but can it reduce risk?</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr"/>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>rows › #4 › takeBack › from</t>
+          <t>rows › #4 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Trust</t>
+          <t>How far people will rely on each other when it is not clear who is in charge.</t>
         </is>
       </c>
       <c r="E230" s="4" t="inlineStr"/>
@@ -7902,7 +7902,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 3, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C231" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › dimension</t>
+          <t>rows › #4 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D231" s="3" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>You took the incident from HR and ran it. It worked, and everyone now looks to IT when something goes wrong.</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "dimension"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C232" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #1 › summary</t>
+          <t>rows › #4 › variants › #1 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>You have a list of these workers that nobody had on Friday.</t>
+          <t>The decision has expanded the scope of your IT function without increasing its budget or capacity. HR has stepped back from supplier risk it used to own.</t>
         </is>
       </c>
       <c r="E232" s="4" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #1 › detail › intro</t>
+          <t>rows › #4 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>How much of the organisation you can see, and how quickly.</t>
+          <t>You’re better placed to govern the response to the next problem, but you don’t have the levers to reduce the likelihood that there will be one.</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="C234" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #1 › detail › monday</t>
+          <t>rows › #4 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>You have a list of these workers that nobody had on Friday.</t>
+          <t>HR still owns the agency contract on paper. In practice, everyone expects IT to answer for it.</t>
         </is>
       </c>
       <c r="E234" s="4" t="inlineStr"/>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8045,12 +8045,12 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #1 › detail › threeMonths</t>
+          <t>rows › #4 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
         <is>
-          <t>The list is already out of date unless someone owns it. Contractors have started and left since.</t>
+          <t>Finance, HR and IT worked together successfully and value IT’s governance processes more highly. How can you use that to increase compliance across the organisation?</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr"/>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8077,12 @@
       </c>
       <c r="C236" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #1 › detail › nextTime</t>
+          <t>rows › #4 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>You start from a list, not a guess, if you keep it.</t>
+          <t>How far people will rely on each other when it is not clear who is in charge.</t>
         </is>
       </c>
       <c r="E236" s="4" t="inlineStr"/>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8109,12 @@
       </c>
       <c r="C237" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #1 › detail › paper</t>
+          <t>rows › #4 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>The contract register is complete. It lists the agency. It does not list the people the agency provides.</t>
+          <t>Finance and HR paid people together for the first time, and each saw the other work under pressure.</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › summary</t>
+          <t>rows › #4 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>It was handled quietly. Responsibility still sits with the agency, but you don’t have an organisational view of your contractors for when the next incident occurs.</t>
+          <t>People know who to ring in the other team, and they have started ringing before it is urgent.</t>
         </is>
       </c>
       <c r="E238" s="4" t="inlineStr"/>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="C239" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › detail › intro</t>
+          <t>rows › #4 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D239" s="3" t="inlineStr">
         <is>
-          <t>How much of the organisation you can see, and how quickly.</t>
+          <t>The next incident starts with relationships that already work. That only holds while the same people are in post.</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr"/>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C240" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › detail › monday</t>
+          <t>rows › #4 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Pay landed and the questions stopped. Getting there took calls to managers, HR and the agency, pieced together by hand over a weekend.</t>
+          <t>The escalation route exists in a document. Whether anyone uses it depends on whether they have worked with the person at the other end.</t>
         </is>
       </c>
       <c r="E240" s="4" t="inlineStr"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 3, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="C241" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #4 › takeBack › label</t>
         </is>
       </c>
       <c r="D241" s="3" t="inlineStr">
         <is>
-          <t>Nobody wrote down what was found. The names and contacts gathered that weekend sit in inboxes and notebooks.</t>
+          <t>Book thirty minutes with your counterpart in Finance or HR before you need them.</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 3, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="C242" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › detail › nextTime</t>
+          <t>rows › #4 › takeBack › from</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>You start from a guess again, and do the same unusual work to find the same people.</t>
+          <t>Trust</t>
         </is>
       </c>
       <c r="E242" s="4" t="inlineStr"/>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 3, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -8301,12 +8301,12 @@
       </c>
       <c r="C243" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › variants › #2 › detail › paper</t>
+          <t>rows › #5 › dimension</t>
         </is>
       </c>
       <c r="D243" s="3" t="inlineStr">
         <is>
-          <t>The incident log says resolved, no lasting impact. It doesn’t record that nobody could list the people affected.</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 4, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -8333,12 +8333,12 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › takeBack › label</t>
+          <t>rows › #5 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Find out whether one list of contractors exists, and who owns it.</t>
+          <t>You have a list of these workers that nobody had on Friday.</t>
         </is>
       </c>
       <c r="E244" s="4" t="inlineStr"/>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8365,12 +8365,12 @@
       </c>
       <c r="C245" s="3" t="inlineStr">
         <is>
-          <t>rows › #5 › takeBack › from</t>
+          <t>rows › #5 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>Visibility</t>
+          <t>How much of the organisation you can see, and how quickly.</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr"/>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 4, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8397,12 +8397,12 @@
       </c>
       <c r="C246" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › dimension</t>
+          <t>rows › #5 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Decision rights</t>
+          <t>You have a list of these workers that nobody had on Friday.</t>
         </is>
       </c>
       <c r="E246" s="4" t="inlineStr"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "dimension"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › summary</t>
+          <t>rows › #5 › variants › #1 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>You and HR settled who decides before the CEO had to ask.</t>
+          <t>The list is already out of date unless someone owns it. Contractors have started and left since.</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr"/>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8461,12 +8461,12 @@
       </c>
       <c r="C248" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › intro</t>
+          <t>rows › #5 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Who is allowed to make which call, and whether everyone knows it.</t>
+          <t>You start from a list, not a guess, if you keep it.</t>
         </is>
       </c>
       <c r="E248" s="4" t="inlineStr"/>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C249" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › monday</t>
+          <t>rows › #5 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>The CEO asked who was leading and got one answer.</t>
+          <t>The contract register is complete. It lists the agency. It does not list the people the agency provides.</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr"/>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8525,12 +8525,12 @@
       </c>
       <c r="C250" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › threeMonths</t>
+          <t>rows › #5 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>The agreement was spoken, not written. People remember it differently, and the next contract will be signed without it.</t>
+          <t>It was handled quietly. Responsibility still sits with the agency, but you don’t have an organisational view of your contractors for when the next incident occurs.</t>
         </is>
       </c>
       <c r="E250" s="4" t="inlineStr"/>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8557,12 +8557,12 @@
       </c>
       <c r="C251" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › nextTime</t>
+          <t>rows › #5 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D251" s="3" t="inlineStr">
         <is>
-          <t>The same question is answered in minutes, if the answer is written down.</t>
+          <t>How much of the organisation you can see, and how quickly.</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr"/>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="C252" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #1 › detail › paper</t>
+          <t>rows › #5 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>The delegation scheme says who can sign off payments. But there wasn't clear governance for agreeing to step outside the process.</t>
+          <t>Pay landed and the questions stopped. Getting there took calls to managers, HR and the agency, pieced together by hand over a weekend.</t>
         </is>
       </c>
       <c r="E252" s="4" t="inlineStr"/>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8621,12 +8621,12 @@
       </c>
       <c r="C253" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › summary</t>
+          <t>rows › #5 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>The CEO asked who was leading and heard two answers.</t>
+          <t>Nobody wrote down what was found. The names and contacts gathered that weekend sit in inboxes and notebooks.</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr"/>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8653,12 +8653,12 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail › intro</t>
+          <t>rows › #5 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Who is allowed to make which call, and whether everyone knows it.</t>
+          <t>You start from a guess again, and do the same unusual work to find the same people.</t>
         </is>
       </c>
       <c r="E254" s="4" t="inlineStr"/>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8685,12 +8685,12 @@
       </c>
       <c r="C255" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail › monday</t>
+          <t>rows › #5 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>The CEO asked who was leading and heard two answers. The agency and the workers got mixed messages while IT and HR sorted it out between them.</t>
+          <t>The incident log says resolved, no lasting impact. It doesn’t record that nobody could list the people affected.</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr"/>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 4, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #5 › takeBack › label</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Nobody has agreed who owns a supplier incident. It’s still settled on the day, by whoever picks up the phone.</t>
+          <t>Find out whether one list of contractors exists, and who owns it.</t>
         </is>
       </c>
       <c r="E256" s="4" t="inlineStr"/>
@@ -8734,7 +8734,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 4, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="C257" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail › nextTime</t>
+          <t>rows › #5 › takeBack › from</t>
         </is>
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>The same question is asked again, in the middle of the next incident, and gets the same two answers.</t>
+          <t>Visibility</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr"/>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 4, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › variants › #2 › detail › paper</t>
+          <t>rows › #6 › dimension</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>There are clear accountabilities for each department and the boundaries are respected. Until a crisis cuts across two departments and no one is sure who should lead.</t>
+          <t>Decision rights</t>
         </is>
       </c>
       <c r="E258" s="4" t="inlineStr"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 5, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -8813,12 +8813,12 @@
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › takeBack › label</t>
+          <t>rows › #6 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Write down who decides whether to pay workers outside the usual chain, and check they know it.</t>
+          <t>You and HR settled who decides before the CEO had to ask.</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr"/>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>rows › #6 › takeBack › from</t>
+          <t>rows › #6 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Decision rights</t>
+          <t>Who is allowed to make which call, and whether everyone knows it.</t>
         </is>
       </c>
       <c r="E260" s="4" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 5, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -8877,12 +8877,12 @@
       </c>
       <c r="C261" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › dimension</t>
+          <t>rows › #6 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>The CEO asked who was leading and got one answer.</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "dimension"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -8909,12 +8909,12 @@
       </c>
       <c r="C262" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #1 › summary</t>
+          <t>rows › #6 › variants › #1 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>You decided what stopped first, so the rest of the work slowed on purpose.</t>
+          <t>The agreement was spoken, not written. People remember it differently, and the next contract will be signed without it.</t>
         </is>
       </c>
       <c r="E262" s="4" t="inlineStr"/>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 0, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="C263" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #1 › detail</t>
+          <t>rows › #6 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D263" s="3" t="inlineStr">
         <is>
-          <t>You made a proactive decision to communicate that some work has slowed. Colleagues understand why and your teams are working under less pressure as a result.</t>
+          <t>The same question is answered in minutes, if the answer is written down.</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr"/>
@@ -8958,7 +8958,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 0, "detail"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -8973,12 +8973,12 @@
       </c>
       <c r="C264" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › summary</t>
+          <t>rows › #6 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Planned work stopped while you looked after this, and nobody counted what.</t>
+          <t>The delegation scheme says who can sign off payments. But there wasn't clear governance for agreeing to step outside the process.</t>
         </is>
       </c>
       <c r="E264" s="4" t="inlineStr"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "summary"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -9005,12 +9005,12 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › intro</t>
+          <t>rows › #6 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>What the rest of the organisation did not get done because of the response.</t>
+          <t>The CEO asked who was leading and heard two answers.</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr"/>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "intro"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="C266" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › monday</t>
+          <t>rows › #6 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Three people left planned work to cover the weekend. They are compensated but tired. What's the impact on their planned work?</t>
+          <t>Who is allowed to make which call, and whether everyone knows it.</t>
         </is>
       </c>
       <c r="E266" s="4" t="inlineStr"/>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "monday"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -9069,12 +9069,12 @@
       </c>
       <c r="C267" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › threeMonths</t>
+          <t>rows › #6 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
         <is>
-          <t>Two pieces of work have slipped. The reasons are not on any report.</t>
+          <t>The CEO asked who was leading and heard two answers. The agency and the workers got mixed messages while IT and HR sorted it out between them.</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "threeMonths"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -9101,12 +9101,12 @@
       </c>
       <c r="C268" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › nextTime</t>
+          <t>rows › #6 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>The same work stops first again, because nobody agreed in advance what should.</t>
+          <t>Nobody has agreed who owns a supplier incident. It’s still settled on the day, by whoever picks up the phone.</t>
         </is>
       </c>
       <c r="E268" s="4" t="inlineStr"/>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "nextTime"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -9133,12 +9133,12 @@
       </c>
       <c r="C269" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › variants › #2 › detail › paper</t>
+          <t>rows › #6 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D269" s="3" t="inlineStr">
         <is>
-          <t>The portfolio report is green for now. The impact of this weekend won't be visible immediately.</t>
+          <t>The same question is asked again, in the middle of the next incident, and gets the same two answers.</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr"/>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "paper"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="C270" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › takeBack › label</t>
+          <t>rows › #6 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>List the work you would stop first in an incident, and tell the people it affects.</t>
+          <t>There are clear accountabilities for each department and the boundaries are respected. Until a crisis cuts across two departments and no one is sure who should lead.</t>
         </is>
       </c>
       <c r="E270" s="4" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "takeBack", "label"]</t>
+          <t>["screens", 8, "rows", 5, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C271" s="3" t="inlineStr">
         <is>
-          <t>rows › #7 › takeBack › from</t>
+          <t>rows › #6 › takeBack › label</t>
         </is>
       </c>
       <c r="D271" s="3" t="inlineStr">
         <is>
-          <t>Delivery</t>
+          <t>Write down who decides whether to pay workers outside the usual chain, and check they know it.</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr"/>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>["screens", 8, "rows", 6, "takeBack", "from"]</t>
+          <t>["screens", 8, "rows", 5, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="C272" s="3" t="inlineStr">
         <is>
-          <t>footnote</t>
+          <t>rows › #6 › takeBack › from</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Tap a row for three months on and next time. Flag what you’d take back.</t>
+          <t>Decision rights</t>
         </is>
       </c>
       <c r="E272" s="4" t="inlineStr"/>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>["screens", 8, "footnote"]</t>
+          <t>["screens", 8, "rows", 5, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -9261,12 +9261,12 @@
       </c>
       <c r="C273" s="3" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>rows › #7 › dimension</t>
         </is>
       </c>
       <c r="D273" s="3" t="inlineStr">
         <is>
-          <t>Choose what to take back →</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr"/>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>["screens", 8, "button"]</t>
+          <t>["screens", 8, "rows", 6, "dimension"]</t>
         </is>
       </c>
     </row>
@@ -9288,17 +9288,17 @@
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C274" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>rows › #7 › variants › #1 › summary</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Your move</t>
+          <t>You decided what stopped first, so the rest of the work slowed on purpose.</t>
         </is>
       </c>
       <c r="E274" s="4" t="inlineStr"/>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>["screens", 9, "header", "label"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "summary"]</t>
         </is>
       </c>
     </row>
@@ -9320,17 +9320,17 @@
       </c>
       <c r="B275" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C275" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>rows › #7 › variants › #1 › detail › intro</t>
         </is>
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>5 of 5</t>
+          <t>What the rest of the organisation did not get done because of the response.</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr"/>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>["screens", 9, "header", "step"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -9352,17 +9352,17 @@
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C276" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>rows › #7 › variants › #1 › detail › monday</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Take one thing back.</t>
+          <t>You made a proactive decision about what to pause, and told people why. Work slowed on purpose and in the open.</t>
         </is>
       </c>
       <c r="E276" s="4" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>["screens", 9, "title"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -9384,17 +9384,17 @@
       </c>
       <c r="B277" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C277" s="3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>rows › #7 › variants › #1 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D277" s="3" t="inlineStr">
         <is>
-          <t>You flagged {count}. Pick the one you’ll actually do. One is enough.</t>
+          <t>The paused work has restarted. Colleagues understood the delay, and your teams worked under less pressure as a result.</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>["screens", 9, "intro"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -9416,17 +9416,17 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C278" s="3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>rows › #7 › variants › #1 › detail › nextTime</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>You didn’t flag anything this time. You can go back to the ledger and flag something, or close the file.</t>
+          <t>You start from a list of what stops first, agreed before anyone needs it.</t>
         </is>
       </c>
       <c r="E278" s="4" t="inlineStr"/>
@@ -9438,7 +9438,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>["screens", 9, "none"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -9448,17 +9448,17 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C279" s="3" t="inlineStr">
         <is>
-          <t>whenKicker</t>
+          <t>rows › #7 › variants › #1 › detail › paper</t>
         </is>
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>By when</t>
+          <t>The portfolio report shows the delay, with its reason. Nobody is surprised by it.</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr"/>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenKicker"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 0, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -9480,17 +9480,17 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #1 › label</t>
+          <t>rows › #7 › variants › #2 › summary</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>1 week</t>
+          <t>Planned work stopped while you looked after this, and nobody counted what.</t>
         </is>
       </c>
       <c r="E280" s="4" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 0, "label"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "summary"]</t>
         </is>
       </c>
     </row>
@@ -9512,17 +9512,17 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #1 › phrase</t>
+          <t>rows › #7 › variants › #2 › detail › intro</t>
         </is>
       </c>
       <c r="D281" s="3" t="inlineStr">
         <is>
-          <t>By one week from today.</t>
+          <t>What the rest of the organisation did not get done because of the response.</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr"/>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 0, "phrase"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "intro"]</t>
         </is>
       </c>
     </row>
@@ -9544,17 +9544,17 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C282" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #2 › label</t>
+          <t>rows › #7 › variants › #2 › detail › monday</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>2 weeks</t>
+          <t>Three people left planned work to cover the weekend. They are compensated but tired. What's the impact on their planned work?</t>
         </is>
       </c>
       <c r="E282" s="4" t="inlineStr"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 1, "label"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "monday"]</t>
         </is>
       </c>
     </row>
@@ -9576,17 +9576,17 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #2 › phrase</t>
+          <t>rows › #7 › variants › #2 › detail › threeMonths</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>By two weeks from today.</t>
+          <t>Two pieces of work have slipped. The reasons are not on any report.</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 1, "phrase"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "threeMonths"]</t>
         </is>
       </c>
     </row>
@@ -9608,17 +9608,17 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C284" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #3 › label</t>
+          <t>rows › #7 › variants › #2 › detail › nextTime</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>The same work stops first again, because nobody agreed in advance what should.</t>
         </is>
       </c>
       <c r="E284" s="4" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 2, "label"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "nextTime"]</t>
         </is>
       </c>
     </row>
@@ -9640,17 +9640,17 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C285" s="3" t="inlineStr">
         <is>
-          <t>whenOptions › #3 › phrase</t>
+          <t>rows › #7 › variants › #2 › detail › paper</t>
         </is>
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>By one month from today.</t>
+          <t>The portfolio report is green for now. The impact of this weekend won't be visible immediately.</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr"/>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>["screens", 9, "whenOptions", 2, "phrase"]</t>
+          <t>["screens", 8, "rows", 6, "variants", 1, "detail", "paper"]</t>
         </is>
       </c>
     </row>
@@ -9672,17 +9672,17 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C286" s="3" t="inlineStr">
         <is>
-          <t>followUp</t>
+          <t>rows › #7 › takeBack › label</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Ask me in 30 days whether I did it. One email, and you can stop it any time.</t>
+          <t>List the work you would stop first in an incident, and tell the people it affects.</t>
         </is>
       </c>
       <c r="E286" s="4" t="inlineStr"/>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>["screens", 9, "followUp"]</t>
+          <t>["screens", 8, "rows", 6, "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -9704,17 +9704,17 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
         <is>
-          <t>followUpPromise</t>
+          <t>rows › #7 › takeBack › from</t>
         </is>
       </c>
       <c r="D287" s="3" t="inlineStr">
         <is>
-          <t>I’ll ask you in 30 days whether you did.</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr"/>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>["screens", 9, "followUpPromise"]</t>
+          <t>["screens", 8, "rows", 6, "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -9736,17 +9736,17 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C288" s="3" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>footnote</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Save and close the file →</t>
+          <t>Tap a row for three months on and next time. Flag what you’d take back.</t>
         </is>
       </c>
       <c r="E288" s="4" t="inlineStr"/>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>["screens", 9, "button"]</t>
+          <t>["screens", 8, "footnote"]</t>
         </is>
       </c>
     </row>
@@ -9768,17 +9768,17 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>Screen 11 · Take one thing back</t>
+          <t>Screen 10 · Ledger</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>button</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>Skip, close the file</t>
+          <t>Choose what to take back →</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr"/>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>["screens", 9, "skip"]</t>
+          <t>["screens", 8, "button"]</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Incident File 01 · The Monday After</t>
+          <t>The Monday After · Your move</t>
         </is>
       </c>
       <c r="E290" s="4" t="inlineStr"/>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>["screens", 10, "header", "label"]</t>
+          <t>["screens", 9, "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C291" s="3" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>5 of 5</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr"/>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>["screens", 10, "header", "step"]</t>
+          <t>["screens", 9, "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -9864,17 +9864,17 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C292" s="3" t="inlineStr">
         <is>
-          <t>kicker</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Your Monday After</t>
+          <t>Take one thing back.</t>
         </is>
       </c>
       <c r="E292" s="4" t="inlineStr"/>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>["screens", 10, "kicker"]</t>
+          <t>["screens", 9, "title"]</t>
         </is>
       </c>
     </row>
@@ -9896,17 +9896,17 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C293" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › prefix</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">You </t>
+          <t>You flagged {count}. Pick the one you’ll actually do. One is enough.</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "prefix"]</t>
+          <t>["screens", 9, "intro"]</t>
         </is>
       </c>
     </row>
@@ -9928,17 +9928,17 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C294" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › A</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>built the list</t>
+          <t>You didn’t flag anything this time. You can go back to the ledger and flag something, or close the file.</t>
         </is>
       </c>
       <c r="E294" s="4" t="inlineStr"/>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "A"]</t>
+          <t>["screens", 9, "none"]</t>
         </is>
       </c>
     </row>
@@ -9960,17 +9960,17 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C295" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › B</t>
+          <t>whenKicker</t>
         </is>
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>pressed the agency</t>
+          <t>By when</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "B"]</t>
+          <t>["screens", 9, "whenKicker"]</t>
         </is>
       </c>
     </row>
@@ -9992,17 +9992,17 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C296" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › C</t>
+          <t>whenOptions › #1 › label</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>bridged the gap</t>
+          <t>1 week</t>
         </is>
       </c>
       <c r="E296" s="4" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "C"]</t>
+          <t>["screens", 9, "whenOptions", 0, "label"]</t>
         </is>
       </c>
     </row>
@@ -10024,17 +10024,17 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › D</t>
+          <t>whenOptions › #1 › phrase</t>
         </is>
       </c>
       <c r="D297" s="3" t="inlineStr">
         <is>
-          <t>told the workers early</t>
+          <t>By one week from today.</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "D"]</t>
+          <t>["screens", 9, "whenOptions", 0, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › E</t>
+          <t>whenOptions › #2 › label</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>went to worker representatives early</t>
+          <t>2 weeks</t>
         </is>
       </c>
       <c r="E298" s="4" t="inlineStr"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "E"]</t>
+          <t>["screens", 9, "whenOptions", 1, "label"]</t>
         </is>
       </c>
     </row>
@@ -10088,17 +10088,17 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C299" s="3" t="inlineStr">
         <is>
-          <t>mirror › opening › phrases › F</t>
+          <t>whenOptions › #2 › phrase</t>
         </is>
       </c>
       <c r="D299" s="3" t="inlineStr">
         <is>
-          <t>protected the critical work</t>
+          <t>By two weeks from today.</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr"/>
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "opening", "phrases", "F"]</t>
+          <t>["screens", 9, "whenOptions", 1, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -10120,17 +10120,17 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>mirror › middle › #1 › text</t>
+          <t>whenOptions › #3 › label</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>You now know who these people are.</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="E300" s="4" t="inlineStr"/>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "middle", 0, "text"]</t>
+          <t>["screens", 9, "whenOptions", 2, "label"]</t>
         </is>
       </c>
     </row>
@@ -10152,17 +10152,17 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C301" s="3" t="inlineStr">
         <is>
-          <t>mirror › middle › #2 › text</t>
+          <t>whenOptions › #3 › phrase</t>
         </is>
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>You still don't have one list of these people.</t>
+          <t>By one month from today.</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr"/>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "middle", 1, "text"]</t>
+          <t>["screens", 9, "whenOptions", 2, "phrase"]</t>
         </is>
       </c>
     </row>
@@ -10184,17 +10184,17 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 1 › did</t>
+          <t>followUp</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>You kept the most exposed people paid.</t>
+          <t>Ask me in 30 days whether I did it. One email, and you can stop it any time.</t>
         </is>
       </c>
       <c r="E302" s="4" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "1", "did"]</t>
+          <t>["screens", 9, "followUp"]</t>
         </is>
       </c>
     </row>
@@ -10216,17 +10216,17 @@
       </c>
       <c r="B303" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C303" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 1 › still</t>
+          <t>followUpPromise</t>
         </is>
       </c>
       <c r="D303" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who owns the supplier's supplier.</t>
+          <t>I’ll ask you in 30 days whether you did.</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "1", "still"]</t>
+          <t>["screens", 9, "followUpPromise"]</t>
         </is>
       </c>
     </row>
@@ -10248,17 +10248,17 @@
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C304" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 2 › did</t>
+          <t>button</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>You said what you knew and what you didn't, before the group chat did.</t>
+          <t>Save and close the file →</t>
         </is>
       </c>
       <c r="E304" s="4" t="inlineStr"/>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "2", "did"]</t>
+          <t>["screens", 9, "button"]</t>
         </is>
       </c>
     </row>
@@ -10280,17 +10280,17 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>Screen 12 · Closing</t>
+          <t>Screen 11 · Take one thing back</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 2 › still</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>You still can't say when anyone will be paid, or who owns the supplier's supplier.</t>
+          <t>Skip, close the file</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "2", "still"]</t>
+          <t>["screens", 9, "skip"]</t>
         </is>
       </c>
     </row>
@@ -10317,12 +10317,12 @@
       </c>
       <c r="C306" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 3 › did</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>You made it the CEO's decision, so it had an owner by Saturday.</t>
+          <t>Incident File 01 · The Monday After</t>
         </is>
       </c>
       <c r="E306" s="4" t="inlineStr"/>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "3", "did"]</t>
+          <t>["screens", 10, "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -10349,12 +10349,12 @@
       </c>
       <c r="C307" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 3 › still</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D307" s="3" t="inlineStr">
         <is>
-          <t>You still haven't asked who should have owned the supplier's supplier before it mattered.</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr"/>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "3", "still"]</t>
+          <t>["screens", 10, "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -10381,12 +10381,12 @@
       </c>
       <c r="C308" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 4 › did</t>
+          <t>kicker</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>You know what else this provider touches.</t>
+          <t>Your Monday After</t>
         </is>
       </c>
       <c r="E308" s="4" t="inlineStr"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "4", "did"]</t>
+          <t>["screens", 10, "kicker"]</t>
         </is>
       </c>
     </row>
@@ -10413,12 +10413,12 @@
       </c>
       <c r="C309" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 4 › still</t>
+          <t>mirror › opening › prefix</t>
         </is>
       </c>
       <c r="D309" s="3" t="inlineStr">
         <is>
-          <t>You still haven't decided who watches it.</t>
+          <t xml:space="preserve">You </t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr"/>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "4", "still"]</t>
+          <t>["screens", 10, "mirror", "opening", "prefix"]</t>
         </is>
       </c>
     </row>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 5 › did</t>
+          <t>mirror › opening › phrases › A</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>You protected Monday.</t>
+          <t>built the list</t>
         </is>
       </c>
       <c r="E310" s="4" t="inlineStr"/>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "5", "did"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "A"]</t>
         </is>
       </c>
     </row>
@@ -10477,12 +10477,12 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>mirror › ending › parts › 5 › still</t>
+          <t>mirror › opening › phrases › B</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who will be paid, or who owns the supplier's supplier.</t>
+          <t>pressed the agency</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr"/>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "ending", "parts", "5", "still"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "B"]</t>
         </is>
       </c>
     </row>
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>mirror › fallback</t>
+          <t>mirror › opening › phrases › C</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>You still don't know who owns the supplier's supplier.</t>
+          <t>bridged the gap</t>
         </is>
       </c>
       <c r="E312" s="4" t="inlineStr"/>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>["screens", 10, "mirror", "fallback"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "C"]</t>
         </is>
       </c>
     </row>
@@ -10541,12 +10541,12 @@
       </c>
       <c r="C313" s="3" t="inlineStr">
         <is>
-          <t>tagline</t>
+          <t>mirror › opening › phrases › D</t>
         </is>
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>Lucky, or designed? Only one of those repeats.</t>
+          <t>told the workers early</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>["screens", 10, "tagline"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "D"]</t>
         </is>
       </c>
     </row>
@@ -10573,12 +10573,12 @@
       </c>
       <c r="C314" s="3" t="inlineStr">
         <is>
-          <t>takingKicker</t>
+          <t>mirror › opening › phrases › E</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>You’re taking this back</t>
+          <t>went to worker representatives early</t>
         </is>
       </c>
       <c r="E314" s="4" t="inlineStr"/>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>["screens", 10, "takingKicker"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "E"]</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C315" s="3" t="inlineStr">
         <is>
-          <t>recorder › kicker</t>
+          <t>mirror › opening › phrases › F</t>
         </is>
       </c>
       <c r="D315" s="3" t="inlineStr">
         <is>
-          <t>Your flight recorder</t>
+          <t>protected the critical work</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr"/>
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "kicker"]</t>
+          <t>["screens", 10, "mirror", "opening", "phrases", "F"]</t>
         </is>
       </c>
     </row>
@@ -10637,12 +10637,12 @@
       </c>
       <c r="C316" s="3" t="inlineStr">
         <is>
-          <t>recorder › text</t>
+          <t>mirror › middle › #1 › text</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Want a copy of what you wrote? We’ll email it to you. Nobody else can read it.</t>
+          <t>You now know who these people are.</t>
         </is>
       </c>
       <c r="E316" s="4" t="inlineStr"/>
@@ -10654,7 +10654,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "text"]</t>
+          <t>["screens", 10, "mirror", "middle", 0, "text"]</t>
         </is>
       </c>
     </row>
@@ -10669,12 +10669,12 @@
       </c>
       <c r="C317" s="3" t="inlineStr">
         <is>
-          <t>recorder › button</t>
+          <t>mirror › middle › #2 › text</t>
         </is>
       </c>
       <c r="D317" s="3" t="inlineStr">
         <is>
-          <t>Email me my flight recorder</t>
+          <t>You still don't have one list of these people.</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "button"]</t>
+          <t>["screens", 10, "mirror", "middle", 1, "text"]</t>
         </is>
       </c>
     </row>
@@ -10701,12 +10701,12 @@
       </c>
       <c r="C318" s="3" t="inlineStr">
         <is>
-          <t>recorder › previewNote</t>
+          <t>mirror › ending › parts › 1 › did</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>In the finished version, this emails you a copy.</t>
+          <t>You kept the most exposed people paid.</t>
         </is>
       </c>
       <c r="E318" s="4" t="inlineStr"/>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>["screens", 10, "recorder", "previewNote"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "1", "did"]</t>
         </is>
       </c>
     </row>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>share › kicker</t>
+          <t>mirror › ending › parts › 1 › still</t>
         </is>
       </c>
       <c r="D319" s="3" t="inlineStr">
         <is>
-          <t>Pass it on</t>
+          <t>You still don't know who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr"/>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "kicker"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "1", "still"]</t>
         </is>
       </c>
     </row>
@@ -10765,12 +10765,12 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>share › text</t>
+          <t>mirror › ending › parts › 2 › did</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Send this to the person you'd most like to answer it differently.</t>
+          <t>You said what you knew and what you didn't, before the group chat did.</t>
         </is>
       </c>
       <c r="E320" s="4" t="inlineStr"/>
@@ -10782,7 +10782,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "text"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "2", "did"]</t>
         </is>
       </c>
     </row>
@@ -10797,12 +10797,12 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>share › button</t>
+          <t>mirror › ending › parts › 2 › still</t>
         </is>
       </c>
       <c r="D321" s="3" t="inlineStr">
         <is>
-          <t>Share this file</t>
+          <t>You still can't say when anyone will be paid, or who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr"/>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "button"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "2", "still"]</t>
         </is>
       </c>
     </row>
@@ -10829,12 +10829,12 @@
       </c>
       <c r="C322" s="3" t="inlineStr">
         <is>
-          <t>share › copied</t>
+          <t>mirror › ending › parts › 3 › did</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Link copied.</t>
+          <t>You made it the CEO's decision, so it had an owner by Saturday.</t>
         </is>
       </c>
       <c r="E322" s="4" t="inlineStr"/>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>["screens", 10, "share", "copied"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "3", "did"]</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="C323" s="3" t="inlineStr">
         <is>
-          <t>team › text</t>
+          <t>mirror › ending › parts › 3 › still</t>
         </is>
       </c>
       <c r="D323" s="3" t="inlineStr">
         <is>
-          <t>Some of these questions are hard to settle alone. If you'd like to run this with your team, reply to this email and I'll show you how.</t>
+          <t>You still haven't asked who should have owned the supplier's supplier before it mattered.</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>["screens", 10, "team", "text"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "3", "still"]</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="C324" s="3" t="inlineStr">
         <is>
-          <t>team › button</t>
+          <t>mirror › ending › parts › 4 › did</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Reply “team”</t>
+          <t>You know what else this provider touches.</t>
         </is>
       </c>
       <c r="E324" s="4" t="inlineStr"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>["screens", 10, "team", "button"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "4", "did"]</t>
         </is>
       </c>
     </row>
@@ -10925,12 +10925,12 @@
       </c>
       <c r="C325" s="3" t="inlineStr">
         <is>
-          <t>next</t>
+          <t>mirror › ending › parts › 4 › still</t>
         </is>
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>Incident File 02 arrives next month.</t>
+          <t>You still haven't decided who watches it.</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr"/>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>["screens", 10, "next"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "4", "still"]</t>
         </is>
       </c>
     </row>
@@ -10952,17 +10952,17 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C326" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>mirror › ending › parts › 5 › did</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>You protected Monday.</t>
         </is>
       </c>
       <c r="E326" s="4" t="inlineStr"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>["threads", "t1", "header", "label"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "5", "did"]</t>
         </is>
       </c>
     </row>
@@ -10984,17 +10984,17 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C327" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>mirror › ending › parts › 5 › still</t>
         </is>
       </c>
       <c r="D327" s="3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>You still don't know who will be paid, or who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr"/>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>["threads", "t1", "header", "step"]</t>
+          <t>["screens", 10, "mirror", "ending", "parts", "5", "still"]</t>
         </is>
       </c>
     </row>
@@ -11016,17 +11016,17 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C328" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>mirror › fallback</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>You still don't know who owns the supplier's supplier.</t>
         </is>
       </c>
       <c r="E328" s="4" t="inlineStr"/>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>["threads", "t1", "chip", "kicker"]</t>
+          <t>["screens", 10, "mirror", "fallback"]</t>
         </is>
       </c>
     </row>
@@ -11048,17 +11048,17 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C329" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>tagline</t>
         </is>
       </c>
       <c r="D329" s="3" t="inlineStr">
         <is>
-          <t>Are you owning this?</t>
+          <t>Lucky, or designed? Only one of those repeats.</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr"/>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>["threads", "t1", "chip", "title"]</t>
+          <t>["screens", 10, "tagline"]</t>
         </is>
       </c>
     </row>
@@ -11080,17 +11080,17 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>takingKicker</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Are you owning this?</t>
+          <t>You’re taking this back</t>
         </is>
       </c>
       <c r="E330" s="4" t="inlineStr"/>
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>["threads", "t1", "title"]</t>
+          <t>["screens", 10, "takingKicker"]</t>
         </is>
       </c>
     </row>
@@ -11112,17 +11112,17 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C331" s="3" t="inlineStr">
         <is>
-          <t>intro › #1 › text</t>
+          <t>recorder › kicker</t>
         </is>
       </c>
       <c r="D331" s="3" t="inlineStr">
         <is>
-          <t>You stepped in alongside HR. The CEO has asked who is leading.</t>
+          <t>Your flight recorder</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr"/>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 0, "text"]</t>
+          <t>["screens", 10, "recorder", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -11144,17 +11144,17 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C332" s="3" t="inlineStr">
         <is>
-          <t>intro › #2 › text</t>
+          <t>recorder › text</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>You agreed HR would lead. The CEO has asked who they should call.</t>
+          <t>Want a copy of what you wrote? We’ll email it to you. Nobody else can read it.</t>
         </is>
       </c>
       <c r="E332" s="4" t="inlineStr"/>
@@ -11166,7 +11166,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 1, "text"]</t>
+          <t>["screens", 10, "recorder", "text"]</t>
         </is>
       </c>
     </row>
@@ -11176,17 +11176,17 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C333" s="3" t="inlineStr">
         <is>
-          <t>intro › #3 › text</t>
+          <t>recorder › button</t>
         </is>
       </c>
       <c r="D333" s="3" t="inlineStr">
         <is>
-          <t>You took it from HR. The CEO has asked who is leading, and so has HR.</t>
+          <t>Email me my flight recorder</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr"/>
@@ -11198,7 +11198,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>["threads", "t1", "intro", 2, "text"]</t>
+          <t>["screens", 10, "recorder", "button"]</t>
         </is>
       </c>
     </row>
@@ -11208,17 +11208,17 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C334" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>recorder › previewNote</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Front it</t>
+          <t>In the finished version, this emails you a copy.</t>
         </is>
       </c>
       <c r="E334" s="4" t="inlineStr"/>
@@ -11230,7 +11230,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "title"]</t>
+          <t>["screens", 10, "recorder", "previewNote"]</t>
         </is>
       </c>
     </row>
@@ -11240,17 +11240,17 @@
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C335" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>share › kicker</t>
         </is>
       </c>
       <c r="D335" s="3" t="inlineStr">
         <is>
-          <t>You are the visible lead, to the CEO and to the workers.</t>
+          <t>Pass it on</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr"/>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "body"]</t>
+          <t>["screens", 10, "share", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -11272,17 +11272,17 @@
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C336" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>share › text</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>You can carry the workers' trust and the CEO's confidence at once, and HR will not read it as a takeover.</t>
+          <t>Send this to the person you'd most like to answer it differently.</t>
         </is>
       </c>
       <c r="E336" s="4" t="inlineStr"/>
@@ -11294,7 +11294,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "assuming"]</t>
+          <t>["screens", 10, "share", "text"]</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C337" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>share › button</t>
         </is>
       </c>
       <c r="D337" s="3" t="inlineStr">
         <is>
-          <t>One clear voice. The CEO and the workers know who to call.</t>
+          <t>Share this file</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr"/>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "gain"]</t>
+          <t>["screens", 10, "share", "button"]</t>
         </is>
       </c>
     </row>
@@ -11336,17 +11336,17 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C338" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>share › copied</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>HR's ownership weakens, and your name is on it if it goes wrong.</t>
+          <t>Link copied.</t>
         </is>
       </c>
       <c r="E338" s="4" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 0, "reveal", "cost"]</t>
+          <t>["screens", 10, "share", "copied"]</t>
         </is>
       </c>
     </row>
@@ -11368,17 +11368,17 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>team › text</t>
         </is>
       </c>
       <c r="D339" s="3" t="inlineStr">
         <is>
-          <t>Back HR, visibly</t>
+          <t>Some of these questions are hard to settle alone. If you'd like to run this with your team, reply to this email and I'll show you how.</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "title"]</t>
+          <t>["screens", 10, "team", "text"]</t>
         </is>
       </c>
     </row>
@@ -11400,17 +11400,17 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C340" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>team › button</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>You tell the CEO you are supporting the Chief People Officer.</t>
+          <t>Reply “team”</t>
         </is>
       </c>
       <c r="E340" s="4" t="inlineStr"/>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "body"]</t>
+          <t>["screens", 10, "team", "button"]</t>
         </is>
       </c>
     </row>
@@ -11432,17 +11432,17 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>Thread · Are you owning this?</t>
+          <t>Screen 12 · Closing</t>
         </is>
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>next</t>
         </is>
       </c>
       <c r="D341" s="3" t="inlineStr">
         <is>
-          <t>HR can hold the room with the CEO and the workers, and you will hear in time if it slips.</t>
+          <t>Incident File 02 arrives next month.</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr"/>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "assuming"]</t>
+          <t>["screens", 10, "next"]</t>
         </is>
       </c>
     </row>
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C342" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>The owner of the relationship stays accountable, and your capacity is kept for the rest of IT.</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E342" s="4" t="inlineStr"/>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t1", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D343" s="3" t="inlineStr">
         <is>
-          <t>Your influence rests on someone else’s performance, and you may hear late.</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t1", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -11533,12 +11533,12 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Stay in the background</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E344" s="4" t="inlineStr"/>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "title"]</t>
+          <t>["threads", "t1", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C345" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D345" s="3" t="inlineStr">
         <is>
-          <t>You help quietly and step forward only if asked.</t>
+          <t>Are you owning this?</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr"/>
@@ -11582,7 +11582,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "body"]</t>
+          <t>["threads", "t1", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -11597,12 +11597,12 @@
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>You will be asked in time, and HR will tell you when it starts to slip.</t>
+          <t>Are you owning this?</t>
         </is>
       </c>
       <c r="E346" s="4" t="inlineStr"/>
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "title"]</t>
         </is>
       </c>
     </row>
@@ -11629,12 +11629,12 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>intro › #1 › text</t>
         </is>
       </c>
       <c r="D347" s="3" t="inlineStr">
         <is>
-          <t>Your capacity stays free for the rest of IT, and HR keeps ownership of its own relationship.</t>
+          <t>You stepped in alongside HR. The CEO has asked who is leading.</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t1", "intro", 0, "text"]</t>
         </is>
       </c>
     </row>
@@ -11661,12 +11661,12 @@
       </c>
       <c r="C348" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>intro › #2 › text</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>You hear late, and the delay is invisible until it is not.</t>
+          <t>You agreed HR would lead. The CEO has asked who they should call.</t>
         </is>
       </c>
       <c r="E348" s="4" t="inlineStr"/>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>["threads", "t1", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t1", "intro", 1, "text"]</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>intro › #3 › text</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>All three can be reasonable. The question is who the CEO believes owns it.</t>
+          <t>You took it from HR. The CEO has asked who is leading, and so has HR.</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr"/>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>["threads", "t1", "closing"]</t>
+          <t>["threads", "t1", "intro", 2, "text"]</t>
         </is>
       </c>
     </row>
@@ -11720,17 +11720,17 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>Front it</t>
         </is>
       </c>
       <c r="E350" s="4" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>["threads", "t2", "header", "label"]</t>
+          <t>["threads", "t1", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -11752,17 +11752,17 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D351" s="3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>You are the visible lead, to the CEO and to the workers.</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr"/>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>["threads", "t2", "header", "step"]</t>
+          <t>["threads", "t1", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -11784,17 +11784,17 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C352" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>You can carry the workers' trust and the CEO's confidence at once, and HR will not read it as a takeover.</t>
         </is>
       </c>
       <c r="E352" s="4" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>["threads", "t2", "chip", "kicker"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11816,17 +11816,17 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D353" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>One clear voice. The CEO and the workers know who to call.</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr"/>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>["threads", "t2", "chip", "title"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -11848,17 +11848,17 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C354" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>HR's ownership weakens, and your name is on it if it goes wrong.</t>
         </is>
       </c>
       <c r="E354" s="4" t="inlineStr"/>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>["threads", "t2", "title"]</t>
+          <t>["threads", "t1", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -11880,17 +11880,17 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C355" s="3" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D355" s="3" t="inlineStr">
         <is>
-          <t>The agency passed assurance when you bought it. Nobody looked at who pays its workers.</t>
+          <t>Back HR, visibly</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr"/>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>["threads", "t2", "intro"]</t>
+          <t>["threads", "t1", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -11912,17 +11912,17 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>You tell the CEO you are supporting the Chief People Officer.</t>
         </is>
       </c>
       <c r="E356" s="4" t="inlineStr"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "title"]</t>
+          <t>["threads", "t1", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -11944,17 +11944,17 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D357" s="3" t="inlineStr">
         <is>
-          <t>Knows the technology</t>
+          <t>HR can hold the room with the CEO and the workers, and you will hear in time if it slips.</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "body"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -11976,17 +11976,17 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C358" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>IT knows what to look for in a payroll provider, and has the standing to ask for it.</t>
+          <t>The owner of the relationship stays accountable, and your capacity is kept for the rest of IT.</t>
         </is>
       </c>
       <c r="E358" s="4" t="inlineStr"/>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12008,17 +12008,17 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D359" s="3" t="inlineStr">
         <is>
-          <t>The check is technically sound, and it covers systems IT already protects.</t>
+          <t>Your influence rests on someone else’s performance, and you may hear late.</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t1", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12040,17 +12040,17 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>IT has to know the contract exists first. Here it never saw it, so the check never starts.</t>
+          <t>Stay in the background</t>
         </is>
       </c>
       <c r="E360" s="4" t="inlineStr"/>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t1", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -12072,17 +12072,17 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D361" s="3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>You help quietly and step forward only if asked.</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "title"]</t>
+          <t>["threads", "t1", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -12104,17 +12104,17 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Owns the relationship</t>
+          <t>You will be asked in time, and HR will tell you when it starts to slip.</t>
         </is>
       </c>
       <c r="E362" s="4" t="inlineStr"/>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "body"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12136,17 +12136,17 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D363" s="3" t="inlineStr">
         <is>
-          <t>HR has, or can buy in, the skill to judge a payroll provider's resilience.</t>
+          <t>Your capacity stays free for the rest of IT, and HR keeps ownership of its own relationship.</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr"/>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12168,17 +12168,17 @@
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>The owner of the relationship stays accountable.</t>
+          <t>You hear late, and the delay is invisible until it is not.</t>
         </is>
       </c>
       <c r="E364" s="4" t="inlineStr"/>
@@ -12190,7 +12190,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t1", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12200,17 +12200,17 @@
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>Thread · Who should have checked?</t>
+          <t>Thread · Are you owning this?</t>
         </is>
       </c>
       <c r="C365" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D365" s="3" t="inlineStr">
         <is>
-          <t>The check is shallow, which risks being paper again.</t>
+          <t>All three can be reasonable. The question is who the CEO believes owns it.</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr"/>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t1", "closing"]</t>
         </is>
       </c>
     </row>
@@ -12237,12 +12237,12 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>The agency</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E366" s="4" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "title"]</t>
+          <t>["threads", "t2", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -12269,12 +12269,12 @@
       </c>
       <c r="C367" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>It's their supply chain</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr"/>
@@ -12286,7 +12286,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "body"]</t>
+          <t>["threads", "t2", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -12301,12 +12301,12 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>The agency is checking its own supplier, and will tell you honestly if it is not.</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E368" s="4" t="inlineStr"/>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -12333,12 +12333,12 @@
       </c>
       <c r="C369" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D369" s="3" t="inlineStr">
         <is>
-          <t>The responsibility sits with the party closest to the supplier, and asking costs you nothing.</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr"/>
@@ -12350,7 +12350,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t2", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -12365,12 +12365,12 @@
       </c>
       <c r="C370" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>You are relying on a statement, not evidence, from someone who loses the contract if the answer is bad.</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E370" s="4" t="inlineStr"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t2", "title"]</t>
         </is>
       </c>
     </row>
@@ -12397,12 +12397,12 @@
       </c>
       <c r="C371" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="D371" s="3" t="inlineStr">
         <is>
-          <t>Shared, by design</t>
+          <t>The agency passed assurance when you bought it. Nobody looked at who pays its workers.</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "title"]</t>
+          <t>["threads", "t2", "intro"]</t>
         </is>
       </c>
     </row>
@@ -12429,12 +12429,12 @@
       </c>
       <c r="C372" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › body</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Agreed in advance, revisited as the supplier's role changes</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E372" s="4" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "body"]</t>
+          <t>["threads", "t2", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -12461,12 +12461,12 @@
       </c>
       <c r="C373" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › assuming</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D373" s="3" t="inlineStr">
         <is>
-          <t>Someone agreed in advance who checks what, and keeps that agreement alive as the supplier's role changes.</t>
+          <t>Knows the technology</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr"/>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -12493,12 +12493,12 @@
       </c>
       <c r="C374" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › gain</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Nothing falls between IT and HR, and the check is revisited when the supplier changes.</t>
+          <t>IT knows what to look for in a payroll provider, and has the standing to ask for it.</t>
         </is>
       </c>
       <c r="E374" s="4" t="inlineStr"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "gain"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12525,12 +12525,12 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › cost</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
         <is>
-          <t>It takes effort before anything has gone wrong, which is hard to justify, and agreements like this drift if nobody owns them.</t>
+          <t>The check is technically sound, and it covers systems IT already protects.</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr"/>
@@ -12542,7 +12542,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>["threads", "t2", "options", 3, "reveal", "cost"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12557,12 +12557,12 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>All four can be reasonable. The question is whether anyone decided this agency was critical.</t>
+          <t>IT has to know the contract exists first. Here it never saw it, so the check never starts.</t>
         </is>
       </c>
       <c r="E376" s="4" t="inlineStr"/>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>["threads", "t2", "closing"]</t>
+          <t>["threads", "t2", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12589,12 +12589,12 @@
       </c>
       <c r="C377" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>A question about what a sensible owner would check, not what the law requires.</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr"/>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>["threads", "t2", "disclaimer"]</t>
+          <t>["threads", "t2", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -12621,12 +12621,12 @@
       </c>
       <c r="C378" s="3" t="inlineStr">
         <is>
-          <t>takeBack › label</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Ask who should have checked the agency’s payroll provider.</t>
+          <t>Owns the relationship</t>
         </is>
       </c>
       <c r="E378" s="4" t="inlineStr"/>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "label"]</t>
+          <t>["threads", "t2", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -12653,12 +12653,12 @@
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>takeBack › commit</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>Ask who should have checked the agency’s payroll provider, and write down the answer.</t>
+          <t>HR has, or can buy in, the skill to judge a payroll provider's resilience.</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr"/>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "commit"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12685,12 +12685,12 @@
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
-          <t>takeBack › from</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Who should have checked?</t>
+          <t>The owner of the relationship stays accountable.</t>
         </is>
       </c>
       <c r="E380" s="4" t="inlineStr"/>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>["threads", "t2", "takeBack", "from"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12712,17 +12712,17 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C381" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>The check is shallow, which risks being paper again.</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr"/>
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>["threads", "t3", "header", "label"]</t>
+          <t>["threads", "t2", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12744,17 +12744,17 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>The agency</t>
         </is>
       </c>
       <c r="E382" s="4" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>["threads", "t3", "header", "step"]</t>
+          <t>["threads", "t2", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -12776,17 +12776,17 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>Pull a thread · 1 min</t>
+          <t>It's their supply chain</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "kicker"]</t>
+          <t>["threads", "t2", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -12808,17 +12808,17 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C384" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>The clock</t>
+          <t>The agency is checking its own supplier, and will tell you honestly if it is not.</t>
         </is>
       </c>
       <c r="E384" s="4" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "title"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -12840,17 +12840,17 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C385" s="3" t="inlineStr">
         <is>
-          <t>chip › sub</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D385" s="3" t="inlineStr">
         <is>
-          <t>Does anyone’s clock start now?</t>
+          <t>The responsibility sits with the party closest to the supplier, and asking costs you nothing.</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr"/>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>["threads", "t3", "chip", "sub"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -12872,17 +12872,17 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>The clock.</t>
+          <t>You are relying on a statement, not evidence, from someone who loses the contract if the answer is bad.</t>
         </is>
       </c>
       <c r="E386" s="4" t="inlineStr"/>
@@ -12894,7 +12894,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>["threads", "t3", "title"]</t>
+          <t>["threads", "t2", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -12904,17 +12904,17 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>situation › time</t>
+          <t>options › #4 › title</t>
         </is>
       </c>
       <c r="D387" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 09:10</t>
+          <t>Shared, by design</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>["threads", "t3", "situation", "time"]</t>
+          <t>["threads", "t2", "options", 3, "title"]</t>
         </is>
       </c>
     </row>
@@ -12936,17 +12936,17 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>situation › text</t>
+          <t>options › #4 › body</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>The agency’s payroll provider “cannot rule out” a security incident. Pay data is personal data. What do you do about the clock?</t>
+          <t>Agreed in advance, revisited as the supplier's role changes</t>
         </is>
       </c>
       <c r="E388" s="4" t="inlineStr"/>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>["threads", "t3", "situation", "text"]</t>
+          <t>["threads", "t2", "options", 3, "body"]</t>
         </is>
       </c>
     </row>
@@ -12968,17 +12968,17 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C389" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>options › #4 › reveal › assuming</t>
         </is>
       </c>
       <c r="D389" s="3" t="inlineStr">
         <is>
-          <t>Wait for confirmation</t>
+          <t>Someone agreed in advance who checks what, and keeps that agreement alive as the supplier's role changes.</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr"/>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "title"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13000,17 +13000,17 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C390" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › body</t>
+          <t>options › #4 › reveal › gain</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Nothing to act on until someone says it is an incident.</t>
+          <t>Nothing falls between IT and HR, and the check is revisited when the supplier changes.</t>
         </is>
       </c>
       <c r="E390" s="4" t="inlineStr"/>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "body"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13032,17 +13032,17 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C391" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › assuming</t>
+          <t>options › #4 › reveal › cost</t>
         </is>
       </c>
       <c r="D391" s="3" t="inlineStr">
         <is>
-          <t>Nothing starts until someone confirms an incident, and nobody will later ask what you knew on Saturday.</t>
+          <t>It takes effort before anything has gone wrong, which is hard to justify, and agreements like this drift if nobody owns them.</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr"/>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "options", 3, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13064,17 +13064,17 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C392" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › gain</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>You do not raise an alarm over a maybe.</t>
+          <t>All four can be reasonable. The question is whether anyone decided this agency was critical.</t>
         </is>
       </c>
       <c r="E392" s="4" t="inlineStr"/>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "gain"]</t>
+          <t>["threads", "t2", "closing"]</t>
         </is>
       </c>
     </row>
@@ -13096,17 +13096,17 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C393" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › reveal › cost</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="D393" s="3" t="inlineStr">
         <is>
-          <t>If the clock runs from when you became aware, time has already passed, and you have no record of what you knew.</t>
+          <t>A question about what a sensible owner would check, not what the law requires.</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 0, "reveal", "cost"]</t>
+          <t>["threads", "t2", "disclaimer"]</t>
         </is>
       </c>
     </row>
@@ -13128,17 +13128,17 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>takeBack › label</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Note when you were told</t>
+          <t>Ask who should have checked the agency’s payroll provider.</t>
         </is>
       </c>
       <c r="E394" s="4" t="inlineStr"/>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "title"]</t>
+          <t>["threads", "t2", "takeBack", "label"]</t>
         </is>
       </c>
     </row>
@@ -13160,17 +13160,17 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C395" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › body</t>
+          <t>takeBack › commit</t>
         </is>
       </c>
       <c r="D395" s="3" t="inlineStr">
         <is>
-          <t>Start a timestamped log of what you knew and when.</t>
+          <t>Ask who should have checked the agency’s payroll provider, and write down the answer.</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "body"]</t>
+          <t>["threads", "t2", "takeBack", "commit"]</t>
         </is>
       </c>
     </row>
@@ -13192,17 +13192,17 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Thread · The clock.</t>
+          <t>Thread · Who should have checked?</t>
         </is>
       </c>
       <c r="C396" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › assuming</t>
+          <t>takeBack › from</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>The record you start now will matter later, and someone else is deciding who reports.</t>
+          <t>Who should have checked?</t>
         </is>
       </c>
       <c r="E396" s="4" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "assuming"]</t>
+          <t>["threads", "t2", "takeBack", "from"]</t>
         </is>
       </c>
     </row>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C397" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › gain</t>
+          <t>header › label</t>
         </is>
       </c>
       <c r="D397" s="3" t="inlineStr">
         <is>
-          <t>You can show what you knew and when.</t>
+          <t>The Monday After · Thread</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr"/>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "gain"]</t>
+          <t>["threads", "t3", "header", "label"]</t>
         </is>
       </c>
     </row>
@@ -13261,12 +13261,12 @@
       </c>
       <c r="C398" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › reveal › cost</t>
+          <t>header › step</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>A log is not a decision. Someone still has to own the call.</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="E398" s="4" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 1, "reveal", "cost"]</t>
+          <t>["threads", "t3", "header", "step"]</t>
         </is>
       </c>
     </row>
@@ -13293,12 +13293,12 @@
       </c>
       <c r="C399" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>chip › kicker</t>
         </is>
       </c>
       <c r="D399" s="3" t="inlineStr">
         <is>
-          <t>Ask your data protection lead</t>
+          <t>Pull a thread · 1 min</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "title"]</t>
+          <t>["threads", "t3", "chip", "kicker"]</t>
         </is>
       </c>
     </row>
@@ -13325,12 +13325,12 @@
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › body</t>
+          <t>chip › title</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Are you a controller or a processor here, and who tells the regulator?</t>
+          <t>The clock</t>
         </is>
       </c>
       <c r="E400" s="4" t="inlineStr"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "body"]</t>
+          <t>["threads", "t3", "chip", "title"]</t>
         </is>
       </c>
     </row>
@@ -13357,12 +13357,12 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › assuming</t>
+          <t>chip › sub</t>
         </is>
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
-          <t>You have a data protection lead, they can be reached on a Saturday, and they can say what your role is.</t>
+          <t>Does anyone’s clock start now?</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr"/>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "chip", "sub"]</t>
         </is>
       </c>
     </row>
@@ -13389,12 +13389,12 @@
       </c>
       <c r="C402" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › gain</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>You get a view early on whether you are a controller or a processor here, and who has to tell whom.</t>
+          <t>The clock.</t>
         </is>
       </c>
       <c r="E402" s="4" t="inlineStr"/>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "gain"]</t>
+          <t>["threads", "t3", "title"]</t>
         </is>
       </c>
     </row>
@@ -13421,12 +13421,12 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › reveal › cost</t>
+          <t>situation › time</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>If nobody can be reached, hours pass. And the honest answer may be "it depends".</t>
+          <t>Saturday, 09:10</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr"/>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 2, "reveal", "cost"]</t>
+          <t>["threads", "t3", "situation", "time"]</t>
         </is>
       </c>
     </row>
@@ -13453,12 +13453,12 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>situation › text</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Ask the agency in writing</t>
+          <t>The agency’s payroll provider “cannot rule out” a security incident. Pay data is personal data. What do you do about the clock?</t>
         </is>
       </c>
       <c r="E404" s="4" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "title"]</t>
+          <t>["threads", "t3", "situation", "text"]</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › body</t>
+          <t>options › #1 › title</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
         <is>
-          <t>Has it told its customers, and has its provider told it?</t>
+          <t>Wait for confirmation</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr"/>
@@ -13502,7 +13502,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "body"]</t>
+          <t>["threads", "t3", "options", 0, "title"]</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › assuming</t>
+          <t>options › #1 › body</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>The agency knows what its provider has told it, and will answer in writing.</t>
+          <t>Nothing to act on until someone says it is an incident.</t>
         </is>
       </c>
       <c r="E406" s="4" t="inlineStr"/>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "assuming"]</t>
+          <t>["threads", "t3", "options", 0, "body"]</t>
         </is>
       </c>
     </row>
@@ -13549,12 +13549,12 @@
       </c>
       <c r="C407" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › gain</t>
+          <t>options › #1 › reveal › assuming</t>
         </is>
       </c>
       <c r="D407" s="3" t="inlineStr">
         <is>
-          <t>You have a dated record of what you asked and what you were told.</t>
+          <t>Nothing starts until someone confirms an incident, and nobody will later ask what you knew on Saturday.</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr"/>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "gain"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13581,12 +13581,12 @@
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › reveal › cost</t>
+          <t>options › #1 › reveal › gain</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>A written question can slow things down and make the agency defensive. It may not have the answer either.</t>
+          <t>You do not raise an alarm over a maybe.</t>
         </is>
       </c>
       <c r="E408" s="4" t="inlineStr"/>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>["threads", "t3", "options", 3, "reveal", "cost"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13613,12 +13613,12 @@
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>closing</t>
+          <t>options › #1 › reveal › cost</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>The clock may start when you become aware, not when someone confirms.</t>
+          <t>If the clock runs from when you became aware, time has already passed, and you have no record of what you knew.</t>
         </is>
       </c>
       <c r="E409" s="4" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>["threads", "t3", "closing"]</t>
+          <t>["threads", "t3", "options", 0, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13645,12 +13645,12 @@
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>options › #2 › title</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Questions to check with your data protection lead or counsel. Not legal advice.</t>
+          <t>Note when you were told</t>
         </is>
       </c>
       <c r="E410" s="4" t="inlineStr"/>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>["threads", "t3", "disclaimer"]</t>
+          <t>["threads", "t3", "options", 1, "title"]</t>
         </is>
       </c>
     </row>
@@ -13672,17 +13672,17 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C411" s="3" t="inlineStr">
         <is>
-          <t>header › label</t>
+          <t>options › #2 › body</t>
         </is>
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>The Monday After · Thread</t>
+          <t>Start a timestamped log of what you knew and when.</t>
         </is>
       </c>
       <c r="E411" s="4" t="inlineStr"/>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>["threads", "t4", "header", "label"]</t>
+          <t>["threads", "t3", "options", 1, "body"]</t>
         </is>
       </c>
     </row>
@@ -13704,17 +13704,17 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C412" s="3" t="inlineStr">
         <is>
-          <t>header › step</t>
+          <t>options › #2 › reveal › assuming</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>The record you start now will matter later, and someone else is deciding who reports.</t>
         </is>
       </c>
       <c r="E412" s="4" t="inlineStr"/>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>["threads", "t4", "header", "step"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13736,17 +13736,17 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C413" s="3" t="inlineStr">
         <is>
-          <t>chip › kicker</t>
+          <t>options › #2 › reveal › gain</t>
         </is>
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 14:00 · Pull a thread</t>
+          <t>You can show what you knew and when.</t>
         </is>
       </c>
       <c r="E413" s="4" t="inlineStr"/>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "kicker"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13768,17 +13768,17 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>chip › title</t>
+          <t>options › #2 › reveal › cost</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>A neighbour will pay its contractors directly</t>
+          <t>A log is not a decision. Someone still has to own the call.</t>
         </is>
       </c>
       <c r="E414" s="4" t="inlineStr"/>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "title"]</t>
+          <t>["threads", "t3", "options", 1, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13800,17 +13800,17 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>chip › sub</t>
+          <t>options › #3 › title</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>Your workers have seen it.</t>
+          <t>Ask your data protection lead</t>
         </is>
       </c>
       <c r="E415" s="4" t="inlineStr"/>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>["threads", "t4", "chip", "sub"]</t>
+          <t>["threads", "t3", "options", 2, "title"]</t>
         </is>
       </c>
     </row>
@@ -13832,17 +13832,17 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>options › #3 › body</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Saturday, 14:00</t>
+          <t>Are you a controller or a processor here, and who tells the regulator?</t>
         </is>
       </c>
       <c r="E416" s="4" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>["threads", "t4", "time"]</t>
+          <t>["threads", "t3", "options", 2, "body"]</t>
         </is>
       </c>
     </row>
@@ -13864,17 +13864,17 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>options › #3 › reveal › assuming</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
         <is>
-          <t>You're not the only customer.</t>
+          <t>You have a data protection lead, they can be reached on a Saturday, and they can say what your role is.</t>
         </is>
       </c>
       <c r="E417" s="4" t="inlineStr"/>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>["threads", "t4", "title"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -13896,17 +13896,17 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>situation › text</t>
+          <t>options › #3 › reveal › gain</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>A neighbouring organisation that uses the same agency announces it will pay its contractors directly. Your workers have seen it.</t>
+          <t>You get a view early on whether you are a controller or a processor here, and who has to tell whom.</t>
         </is>
       </c>
       <c r="E418" s="4" t="inlineStr"/>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>["threads", "t4", "situation", "text"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -13928,17 +13928,17 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>prompt</t>
+          <t>options › #3 › reveal › cost</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>What do you do? Pick one.</t>
+          <t>If nobody can be reached, hours pass. And the honest answer may be "it depends".</t>
         </is>
       </c>
       <c r="E419" s="4" t="inlineStr"/>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>["threads", "t4", "prompt"]</t>
+          <t>["threads", "t3", "options", 2, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -13960,17 +13960,17 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>options › #1 › title</t>
+          <t>options › #4 › title</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Call the other customers and agree a common line</t>
+          <t>Ask the agency in writing</t>
         </is>
       </c>
       <c r="E420" s="4" t="inlineStr"/>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 0, "title"]</t>
+          <t>["threads", "t3", "options", 3, "title"]</t>
         </is>
       </c>
     </row>
@@ -13992,17 +13992,17 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>options › #2 › title</t>
+          <t>options › #4 › body</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>Wait and let them move first</t>
+          <t>Has it told its customers, and has its provider told it?</t>
         </is>
       </c>
       <c r="E421" s="4" t="inlineStr"/>
@@ -14014,7 +14014,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 1, "title"]</t>
+          <t>["threads", "t3", "options", 3, "body"]</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>options › #3 › title</t>
+          <t>options › #4 › reveal › assuming</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>Pay directly too, now</t>
+          <t>The agency knows what its provider has told it, and will answer in writing.</t>
         </is>
       </c>
       <c r="E422" s="4" t="inlineStr"/>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 2, "title"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "assuming"]</t>
         </is>
       </c>
     </row>
@@ -14056,17 +14056,17 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>options › #4 › title</t>
+          <t>options › #4 › reveal › gain</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>Hold your line and explain why</t>
+          <t>You have a dated record of what you asked and what you were told.</t>
         </is>
       </c>
       <c r="E423" s="4" t="inlineStr"/>
@@ -14078,7 +14078,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 3, "title"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "gain"]</t>
         </is>
       </c>
     </row>
@@ -14088,17 +14088,17 @@
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>options › #5 › title</t>
+          <t>options › #4 › reveal › cost</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Take it to a shared forum or the agency</t>
+          <t>A written question can slow things down and make the agency defensive. It may not have the answer either.</t>
         </is>
       </c>
       <c r="E424" s="4" t="inlineStr"/>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>["threads", "t4", "options", 4, "title"]</t>
+          <t>["threads", "t3", "options", 3, "reveal", "cost"]</t>
         </is>
       </c>
     </row>
@@ -14120,17 +14120,17 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>Thread · You're not the only customer.</t>
+          <t>Thread · The clock.</t>
         </is>
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>closing</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>Coordinating with other customers may have limits depending on sector and country. Check before you act.</t>
+          <t>The clock may start when you become aware, not when someone confirms.</t>
         </is>
       </c>
       <c r="E425" s="4" t="inlineStr"/>
@@ -14141,6 +14141,518 @@
         </is>
       </c>
       <c r="H425" t="inlineStr">
+        <is>
+          <t>["threads", "t3", "closing"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>Thread · The clock.</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+      <c r="D426" s="3" t="inlineStr">
+        <is>
+          <t>Questions to check with your data protection lead or counsel. Not legal advice.</t>
+        </is>
+      </c>
+      <c r="E426" s="4" t="inlineStr"/>
+      <c r="F426" s="3" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>["threads", "t3", "disclaimer"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="3" t="n">
+        <v>426</v>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C427" s="3" t="inlineStr">
+        <is>
+          <t>header › label</t>
+        </is>
+      </c>
+      <c r="D427" s="3" t="inlineStr">
+        <is>
+          <t>The Monday After · Thread</t>
+        </is>
+      </c>
+      <c r="E427" s="4" t="inlineStr"/>
+      <c r="F427" s="3" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "header", "label"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="3" t="n">
+        <v>427</v>
+      </c>
+      <c r="B428" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="inlineStr">
+        <is>
+          <t>header › step</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E428" s="4" t="inlineStr"/>
+      <c r="F428" s="3" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "header", "step"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="3" t="n">
+        <v>428</v>
+      </c>
+      <c r="B429" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C429" s="3" t="inlineStr">
+        <is>
+          <t>chip › kicker</t>
+        </is>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>Saturday, 14:00 · Pull a thread</t>
+        </is>
+      </c>
+      <c r="E429" s="4" t="inlineStr"/>
+      <c r="F429" s="3" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "chip", "kicker"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="3" t="n">
+        <v>429</v>
+      </c>
+      <c r="B430" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="inlineStr">
+        <is>
+          <t>chip › title</t>
+        </is>
+      </c>
+      <c r="D430" s="3" t="inlineStr">
+        <is>
+          <t>A neighbour will pay its contractors directly</t>
+        </is>
+      </c>
+      <c r="E430" s="4" t="inlineStr"/>
+      <c r="F430" s="3" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "chip", "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="3" t="n">
+        <v>430</v>
+      </c>
+      <c r="B431" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="inlineStr">
+        <is>
+          <t>chip › sub</t>
+        </is>
+      </c>
+      <c r="D431" s="3" t="inlineStr">
+        <is>
+          <t>Your workers have seen it.</t>
+        </is>
+      </c>
+      <c r="E431" s="4" t="inlineStr"/>
+      <c r="F431" s="3" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "chip", "sub"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="3" t="n">
+        <v>431</v>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>Saturday, 14:00</t>
+        </is>
+      </c>
+      <c r="E432" s="4" t="inlineStr"/>
+      <c r="F432" s="3" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "time"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="3" t="n">
+        <v>432</v>
+      </c>
+      <c r="B433" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="E433" s="4" t="inlineStr"/>
+      <c r="F433" s="3" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="3" t="n">
+        <v>433</v>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="inlineStr">
+        <is>
+          <t>situation › text</t>
+        </is>
+      </c>
+      <c r="D434" s="3" t="inlineStr">
+        <is>
+          <t>A neighbouring organisation that uses the same agency announces it will pay its contractors directly. Your workers have seen it.</t>
+        </is>
+      </c>
+      <c r="E434" s="4" t="inlineStr"/>
+      <c r="F434" s="3" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "situation", "text"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="3" t="n">
+        <v>434</v>
+      </c>
+      <c r="B435" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="inlineStr">
+        <is>
+          <t>prompt</t>
+        </is>
+      </c>
+      <c r="D435" s="3" t="inlineStr">
+        <is>
+          <t>What do you do? Pick one.</t>
+        </is>
+      </c>
+      <c r="E435" s="4" t="inlineStr"/>
+      <c r="F435" s="3" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "prompt"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="3" t="n">
+        <v>435</v>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>options › #1 › title</t>
+        </is>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>Call the other customers and agree a common line</t>
+        </is>
+      </c>
+      <c r="E436" s="4" t="inlineStr"/>
+      <c r="F436" s="3" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 0, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="3" t="n">
+        <v>436</v>
+      </c>
+      <c r="B437" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="inlineStr">
+        <is>
+          <t>options › #2 › title</t>
+        </is>
+      </c>
+      <c r="D437" s="3" t="inlineStr">
+        <is>
+          <t>Wait and let them move first</t>
+        </is>
+      </c>
+      <c r="E437" s="4" t="inlineStr"/>
+      <c r="F437" s="3" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 1, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="3" t="n">
+        <v>437</v>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>options › #3 › title</t>
+        </is>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>Pay directly too, now</t>
+        </is>
+      </c>
+      <c r="E438" s="4" t="inlineStr"/>
+      <c r="F438" s="3" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 2, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="B439" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C439" s="3" t="inlineStr">
+        <is>
+          <t>options › #4 › title</t>
+        </is>
+      </c>
+      <c r="D439" s="3" t="inlineStr">
+        <is>
+          <t>Hold your line and explain why</t>
+        </is>
+      </c>
+      <c r="E439" s="4" t="inlineStr"/>
+      <c r="F439" s="3" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 3, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="3" t="n">
+        <v>439</v>
+      </c>
+      <c r="B440" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="inlineStr">
+        <is>
+          <t>options › #5 › title</t>
+        </is>
+      </c>
+      <c r="D440" s="3" t="inlineStr">
+        <is>
+          <t>Take it to a shared forum or the agency</t>
+        </is>
+      </c>
+      <c r="E440" s="4" t="inlineStr"/>
+      <c r="F440" s="3" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>["threads", "t4", "options", 4, "title"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="B441" s="3" t="inlineStr">
+        <is>
+          <t>Thread · You're not the only customer.</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>Coordinating with other customers may have limits depending on sector and country. Check before you act.</t>
+        </is>
+      </c>
+      <c r="E441" s="4" t="inlineStr"/>
+      <c r="F441" s="3" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>site/scenarios/incident-file-01.json</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
         <is>
           <t>["threads", "t4", "disclaimer"]</t>
         </is>
@@ -14214,7 +14726,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -14246,7 +14758,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -14278,7 +14790,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -14310,7 +14822,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -14342,7 +14854,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -14374,7 +14886,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -14406,7 +14918,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -14438,7 +14950,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -14470,7 +14982,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -14502,7 +15014,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -14534,7 +15046,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -14566,7 +15078,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -14598,7 +15110,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -14630,7 +15142,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -14662,7 +15174,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -14694,7 +15206,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -14726,7 +15238,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -14758,7 +15270,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -14790,7 +15302,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -14822,7 +15334,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -14854,7 +15366,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -14886,7 +15398,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -14918,7 +15430,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>447</v>
+        <v>463</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -14950,7 +15462,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -14982,7 +15494,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -15014,7 +15526,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>450</v>
+        <v>466</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -15046,7 +15558,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -15078,7 +15590,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -15110,7 +15622,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -15142,7 +15654,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -15174,7 +15686,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -15206,7 +15718,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -15238,7 +15750,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -15270,7 +15782,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -15302,7 +15814,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -15334,7 +15846,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>460</v>
+        <v>476</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -15366,7 +15878,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>461</v>
+        <v>477</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -15398,7 +15910,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -15430,7 +15942,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -15462,7 +15974,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -15494,7 +16006,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -15526,7 +16038,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -15558,7 +16070,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -15590,7 +16102,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -15622,7 +16134,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -15654,7 +16166,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -15686,7 +16198,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -15718,7 +16230,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -15750,7 +16262,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -15782,7 +16294,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -15880,7 +16392,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>475</v>
+        <v>491</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -15912,7 +16424,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -15944,7 +16456,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>477</v>
+        <v>493</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -15976,7 +16488,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -16008,7 +16520,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -16040,7 +16552,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -16072,7 +16584,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -16104,7 +16616,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -16136,7 +16648,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -16168,7 +16680,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -16200,7 +16712,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -16232,7 +16744,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -16264,7 +16776,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -16296,7 +16808,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -16328,7 +16840,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -16360,7 +16872,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -16392,7 +16904,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -16424,7 +16936,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -16456,7 +16968,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -16488,7 +17000,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>494</v>
+        <v>510</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -16520,7 +17032,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -16552,7 +17064,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>496</v>
+        <v>512</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -16584,7 +17096,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -16616,7 +17128,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -16648,7 +17160,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -16680,7 +17192,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -16712,7 +17224,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -16744,7 +17256,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -16776,7 +17288,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -16808,7 +17320,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -16840,7 +17352,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -16872,7 +17384,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -16904,7 +17416,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -16936,7 +17448,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -16968,7 +17480,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -17000,7 +17512,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -17032,7 +17544,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -17064,7 +17576,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -17096,7 +17608,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -17128,7 +17640,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -17160,7 +17672,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -17192,7 +17704,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -17224,7 +17736,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -17256,7 +17768,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -17288,7 +17800,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -17320,7 +17832,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -17352,7 +17864,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -17384,7 +17896,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -17416,7 +17928,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -17448,7 +17960,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -17480,7 +17992,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -17512,7 +18024,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -17544,7 +18056,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -17576,7 +18088,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -17608,7 +18120,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -17640,7 +18152,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -17672,7 +18184,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -17704,7 +18216,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -17736,7 +18248,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -17768,7 +18280,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -17800,7 +18312,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -17832,7 +18344,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -17864,7 +18376,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -17896,7 +18408,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -17928,7 +18440,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -17960,7 +18472,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -17992,7 +18504,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -18024,7 +18536,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -18056,7 +18568,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -18088,7 +18600,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -18120,7 +18632,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -18152,7 +18664,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -18184,7 +18696,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -18216,7 +18728,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -18248,7 +18760,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
@@ -18280,7 +18792,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
@@ -18312,7 +18824,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
@@ -18344,7 +18856,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -18376,7 +18888,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
@@ -18474,7 +18986,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -18506,7 +19018,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -18538,7 +19050,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -18570,7 +19082,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -18602,7 +19114,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -18634,7 +19146,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -18666,7 +19178,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -18698,7 +19210,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -18730,7 +19242,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>562</v>
+        <v>578</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -18762,7 +19274,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -18794,7 +19306,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -18826,7 +19338,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>565</v>
+        <v>581</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -18858,7 +19370,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>566</v>
+        <v>582</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -18890,7 +19402,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>567</v>
+        <v>583</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -18988,7 +19500,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -19020,7 +19532,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -19052,7 +19564,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -19084,7 +19596,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -19116,7 +19628,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -19148,7 +19660,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -19180,7 +19692,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>574</v>
+        <v>590</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -19212,7 +19724,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>575</v>
+        <v>591</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -19244,7 +19756,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -19276,7 +19788,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -19308,7 +19820,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>578</v>
+        <v>594</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -19340,7 +19852,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -19372,7 +19884,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>580</v>
+        <v>596</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -19404,7 +19916,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -19436,7 +19948,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -19468,7 +19980,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -19500,7 +20012,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -19532,7 +20044,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -19564,7 +20076,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -19596,7 +20108,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -19628,7 +20140,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>588</v>
+        <v>604</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -19660,7 +20172,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -19692,7 +20204,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>590</v>
+        <v>606</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -19724,7 +20236,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>591</v>
+        <v>607</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -19756,7 +20268,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -19788,7 +20300,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -19820,7 +20332,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>594</v>
+        <v>610</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -19852,7 +20364,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>595</v>
+        <v>611</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -19884,7 +20396,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -19916,7 +20428,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>597</v>
+        <v>613</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -19948,7 +20460,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>598</v>
+        <v>614</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -19980,7 +20492,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>599</v>
+        <v>615</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -20012,7 +20524,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -20044,7 +20556,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>601</v>
+        <v>617</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -20076,7 +20588,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>602</v>
+        <v>618</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -20108,7 +20620,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>603</v>
+        <v>619</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -20140,7 +20652,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -20172,7 +20684,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -20204,7 +20716,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>606</v>
+        <v>622</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -20236,7 +20748,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>607</v>
+        <v>623</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -20268,7 +20780,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -14669,7 +14669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16042,7 +16042,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Message · expired link</t>
+          <t>Follow-up page · expired link</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -16052,19 +16052,19 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.</t>
+          <t>This link has expired or isn't valid. Reply to any Monday After email if you'd like to tell us anyway.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>backend/src/service.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.\""}</t>
+          <t>{"kind": "code", "raw": "\"This link has expired or isn't valid. Reply to any Monday After email if you'd like to tell us anyway.\""}</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Message · too many tries</t>
+          <t>Follow-up page · after answering Yes</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -16084,19 +16084,19 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Too many requests. Please wait a little and try again.</t>
+          <t>You did it.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>backend/src/service.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Too many requests. Please wait a little and try again.\""}</t>
+          <t>{"kind": "code", "raw": "\"You did it.\""}</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Sign-up page · busy</t>
+          <t>Follow-up page · after answering Partly</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -16116,19 +16116,19 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>We're getting a lot of sign-ups right now. Please try again in an hour.</t>
+          <t>You did part of it.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>backend/src/service.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"We're getting a lot of sign-ups right now. Please try again in an hour.\""}</t>
+          <t>{"kind": "code", "raw": "\"You did part of it.\""}</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>App · email me my flight recorder, nothing saved</t>
+          <t>Follow-up page · after answering Not yet</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -16148,19 +16148,19 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>There's no saved flight recorder for this file.</t>
+          <t>Not yet.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>backend/src/service.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"There's no saved flight recorder for this file.\""}</t>
+          <t>{"kind": "code", "raw": "\"Not yet.\""}</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Manage page</t>
+          <t>Follow-up page · after answering (end)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -16180,19 +16180,19 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>You're unsubscribed, so there's nothing to pause.</t>
+          <t xml:space="preserve"> That's saved with your answers for this file.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>backend/src/service.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"You're unsubscribed, so there's nothing to pause.\""}</t>
+          <t>{"kind": "code", "raw": "\" That's saved with your answers for this file.\""}</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Sign-up page · empty email</t>
+          <t>Follow-up page (then the file name)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -16212,19 +16212,19 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Email is missing</t>
+          <t xml:space="preserve">30 days ago, at the end of </t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>backend/src/validate.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Email is missing\""}</t>
+          <t>{"kind": "code", "raw": "\"30 days ago, at the end of \""}</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Sign-up page · bad email</t>
+          <t>Follow-up page (end)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -16244,19 +16244,19 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>That doesn't look like an email address</t>
+          <t>, you chose one thing to take back.</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>backend/src/validate.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"That doesn't look like an email address\""}</t>
+          <t>{"kind": "code", "raw": "\", you chose one thing to take back.\""}</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Flight recorder · too long (then a number)</t>
+          <t>Follow-up page · answers deleted</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -16276,19 +16276,19 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Please keep each entry under </t>
+          <t>There's nothing to answer for this file any more.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>backend/src/validate.ts</t>
+          <t>backend/src/service.ts</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Please keep each entry under \""}</t>
+          <t>{"kind": "code", "raw": "\"There's nothing to answer for this file any more.\""}</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Flight recorder · first hour empty</t>
+          <t>Follow-up page</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -16308,17 +16308,305 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Please write something for the first hour</t>
+          <t>Please choose one of the answers.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
+          <t>backend/src/service.ts</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Please choose one of the answers.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Message · expired link</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>backend/src/service.ts</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>492</v>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Message · too many tries</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Too many requests. Please wait a little and try again.</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>backend/src/service.ts</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Too many requests. Please wait a little and try again.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>493</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Sign-up page · busy</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>We're getting a lot of sign-ups right now. Please try again in an hour.</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>backend/src/service.ts</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"We're getting a lot of sign-ups right now. Please try again in an hour.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>App · email me my flight recorder, nothing saved</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>There's no saved flight recorder for this file.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>backend/src/service.ts</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"There's no saved flight recorder for this file.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>495</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Manage page</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>You're unsubscribed, so there's nothing to pause.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>backend/src/service.ts</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"You're unsubscribed, so there's nothing to pause.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>496</v>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Sign-up page · empty email</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Email is missing</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>backend/src/validate.ts</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Email is missing\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>497</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Sign-up page · bad email</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>That doesn't look like an email address</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>backend/src/validate.ts</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"That doesn't look like an email address\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>498</v>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Flight recorder · too long (then a number)</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Please keep each entry under </t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>backend/src/validate.ts</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Please keep each entry under \""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>499</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Flight recorder · first hour empty</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Please write something for the first hour</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>backend/src/validate.ts</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>{"kind": "code", "raw": "\"Please write something for the first hour\""}</t>
         </is>
@@ -16335,7 +16623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16392,7 +16680,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -16424,7 +16712,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -16456,7 +16744,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -16488,7 +16776,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -16520,7 +16808,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -16552,7 +16840,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -16584,7 +16872,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -16616,7 +16904,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -16648,7 +16936,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -16680,7 +16968,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -16712,7 +17000,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -16744,7 +17032,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -16776,7 +17064,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -16808,7 +17096,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -16840,7 +17128,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -16872,7 +17160,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -16904,7 +17192,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -16936,7 +17224,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -16968,7 +17256,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -17000,7 +17288,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -17032,7 +17320,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -17064,7 +17352,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -17096,7 +17384,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -17128,7 +17416,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -17160,7 +17448,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -17192,7 +17480,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -17224,7 +17512,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -17256,7 +17544,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -17288,7 +17576,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -17320,7 +17608,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -17352,7 +17640,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -17384,7 +17672,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -17416,7 +17704,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -17448,7 +17736,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -17480,7 +17768,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -17512,7 +17800,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -17544,7 +17832,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17864,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -17608,7 +17896,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -17640,7 +17928,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -17672,7 +17960,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -17704,7 +17992,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -17736,7 +18024,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -17768,7 +18056,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -17800,7 +18088,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -17832,7 +18120,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -17864,7 +18152,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -17896,7 +18184,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -17928,7 +18216,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -17960,7 +18248,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -17992,7 +18280,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -18024,7 +18312,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -18056,7 +18344,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -18088,7 +18376,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -18120,7 +18408,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -18152,7 +18440,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -18184,7 +18472,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -18216,7 +18504,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -18248,7 +18536,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -18280,7 +18568,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -18312,7 +18600,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -18344,7 +18632,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -18376,7 +18664,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -18408,7 +18696,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -18440,7 +18728,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -18472,7 +18760,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -18504,7 +18792,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -18536,7 +18824,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -18568,7 +18856,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -18600,7 +18888,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -18632,7 +18920,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -18664,7 +18952,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -18696,7 +18984,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -18728,11 +19016,11 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Page not found</t>
+          <t>30-day follow-up page</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -18742,29 +19030,29 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Page not found · The Monday After</t>
+          <t>Did you do it? · The Monday After</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>site/404.html</t>
+          <t>site/followup.html</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Page not found \u00b7 The Monday After&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Did you do it? \u00b7 The Monday After&lt;"}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Page not found</t>
+          <t>30-day follow-up page</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -18781,7 +19069,7 @@
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>site/404.html</t>
+          <t>site/followup.html</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -18792,127 +19080,607 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Page not found</t>
+          <t>30-day follow-up page</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Monday, 09:00</t>
+          <t>30 days on</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>site/404.html</t>
+          <t>site/followup.html</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;Monday, 09:00&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;30 days on&lt;"}</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Page not found</t>
+          <t>30-day follow-up page</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>heading</t>
+          <t>paragraph</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>This page isn't here.</t>
+          <t>Checking your link…</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>site/404.html</t>
+          <t>site/followup.html</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;This page isn't here.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Checking your link\u2026&lt;"}</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Page not found</t>
+          <t>30-day follow-up page</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>paragraph</t>
+          <t>heading</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>The address may be mistyped, or the page has moved. If you came from a Monday After email, try its link again.</t>
+          <t>Did you do it?</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>site/404.html</t>
+          <t>site/followup.html</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;The address may be mistyped, or the page has moved. If you came from a Monday After email, try its link again.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;Did you do it?&lt;"}</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Page not found</t>
+          <t>30-day follow-up page</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>paragraph</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Go to The Monday After</t>
+          <t>30 days ago, you chose one thing to take back.</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;30 days ago, you chose one thing to take back.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>579</v>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>You said you'd take this back</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;You said you'd take this back&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>580</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Choose one. You can change it while this link works.</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Choose one. You can change it while this link works.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>581</v>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Yes, I did it</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Yes, I did it&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>582</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Partly&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Not yet</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Not yet&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>584</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Thanks.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Thanks.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>585</v>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>That's saved with your answers for this file.</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;That's saved with your answers for this file.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>586</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Use the link in your email.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Use the link in your email.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>587</v>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up page</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>This page opens from the link in your 30-day follow-up email.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>site/followup.html</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;This page opens from the link in your 30-day follow-up email.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>588</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Page not found</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>browser tab title</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Page not found · The Monday After</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
           <t>site/404.html</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Page not found \u00b7 The Monday After&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>589</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Page not found</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>The Monday After</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>site/404.html</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;The Monday After&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>590</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Page not found</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Monday, 09:00</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>site/404.html</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;Monday, 09:00&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>591</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Page not found</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>This page isn't here.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>site/404.html</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;This page isn't here.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>592</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Page not found</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>paragraph</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>The address may be mistyped, or the page has moved. If you came from a Monday After email, try its link again.</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>site/404.html</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>{"kind": "text", "raw": "&gt;The address may be mistyped, or the page has moved. If you came from a Monday After email, try its link again.&lt;"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>593</v>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Page not found</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Go to The Monday After</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>site/404.html</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
         <is>
           <t>{"kind": "text", "raw": "&gt;Go to The Monday After&lt;"}</t>
         </is>
@@ -18929,7 +19697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -18986,7 +19754,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>570</v>
+        <v>594</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -19018,7 +19786,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -19050,7 +19818,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -19082,7 +19850,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>573</v>
+        <v>597</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -19114,7 +19882,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -19146,7 +19914,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -19178,7 +19946,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -19210,7 +19978,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -19242,7 +20010,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -19274,7 +20042,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -19306,7 +20074,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>580</v>
+        <v>604</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -19338,7 +20106,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>581</v>
+        <v>605</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -19370,7 +20138,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>582</v>
+        <v>606</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -19402,7 +20170,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>583</v>
+        <v>607</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -19429,6 +20197,166 @@
       <c r="H15" t="inlineStr">
         <is>
           <t>{"kind": "code", "raw": "\" team can't read your flight recorder.\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>608</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up email · subject (then the file name)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Did you do it? </t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>backend/src/emails.ts</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Did you do it? \""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>609</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up email (then the file name)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30 days ago, at the end of </t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>backend/src/emails.ts</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"30 days ago, at the end of \""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>610</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up email (then the action)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>, you chose one thing to take back:</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>backend/src/emails.ts</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\", you chose one thing to take back:\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>611</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up email (then the link)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Did you do it? Tell us with one tap:</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>backend/src/emails.ts</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Did you do it? Tell us with one tap:\""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>612</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>30-day follow-up email</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Your answer is kept with your other answers for this file. This is the only reminder we'll send about it.</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>backend/src/emails.ts</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Your answer is kept with your other answers for this file. This is the only reminder we'll send about it.\""}</t>
         </is>
       </c>
     </row>
@@ -19500,7 +20428,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>584</v>
+        <v>613</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -19532,7 +20460,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>585</v>
+        <v>614</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -19564,7 +20492,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>586</v>
+        <v>615</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -19596,7 +20524,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -19628,7 +20556,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -19660,7 +20588,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -19692,7 +20620,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>590</v>
+        <v>619</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -19724,7 +20652,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -19756,7 +20684,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -19788,7 +20716,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -19820,7 +20748,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -19852,7 +20780,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -19884,7 +20812,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -19916,7 +20844,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -19930,7 +20858,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Your email address&lt;/b&gt;, so we can send you each monthly incident file, confirm that you signed up, and send anything you ask for, such as a copy of your flight recorder.</t>
+          <t>&lt;b&gt;Your email address&lt;/b&gt;, so we can send you each monthly incident file, confirm that you signed up, and send anything you ask for, such as a copy of your flight recorder, or the one email 30 days later asking whether you did the thing you chose to take back.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -19942,13 +20870,13 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Your email address&lt;/b&gt;, so we can send you each monthly incident file, confirm that you signed up, and send anything you ask for, such as a copy of your flight recorder.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Your email address&lt;/b&gt;, so we can send you each monthly incident file, confirm that you signed up, and send anything you ask for, such as a copy of your flight recorder, or the one email 30 days later asking whether you did the thing you chose to take back.&lt;"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -19962,7 +20890,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Your answers in each file&lt;/b&gt;: the choices you make, the threads you open, what you flag, your forecast, and the one thing you choose to take back (with the date you picked). We keep them so you can return and change them, so we can send you reports about your own answers in future, and so we can understand how readers respond to crises and improve each scenario.</t>
+          <t>&lt;b&gt;Your answers in each file&lt;/b&gt;: the choices you make, the threads you open, what you flag, your forecast, and the one thing you choose to take back (with the date you picked and, if you asked us to check in after 30 days, whether you did it). We keep them so you can return and change them, so we can send you reports about your own answers in future, and so we can understand how readers respond to crises and improve each scenario.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -19974,13 +20902,13 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Your answers in each file&lt;/b&gt;: the choices you make, the threads you open, what you flag, your forecast, and the one thing you choose to take back (with the date you picked). We keep them so you can return and change them, so we can send you reports about your own answers in future, and so we can understand how readers respond to crises and improve each scenario.&lt;"}</t>
+          <t>{"kind": "text", "raw": "&gt;&lt;b&gt;Your answers in each file&lt;/b&gt;: the choices you make, the threads you open, what you flag, your forecast, and the one thing you choose to take back (with the date you picked and, if you asked us to check in after 30 days, whether you did it). We keep them so you can return and change them, so we can send you reports about your own answers in future, and so we can understand how readers respond to crises and improve each scenario.&lt;"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -20012,7 +20940,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>600</v>
+        <v>629</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -20044,7 +20972,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -20076,7 +21004,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -20108,7 +21036,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -20140,7 +21068,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -20172,7 +21100,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>605</v>
+        <v>634</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -20204,7 +21132,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -20236,7 +21164,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -20268,7 +21196,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>608</v>
+        <v>637</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -20300,7 +21228,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>609</v>
+        <v>638</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -20332,7 +21260,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>610</v>
+        <v>639</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -20364,7 +21292,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>611</v>
+        <v>640</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -20396,7 +21324,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -20428,7 +21356,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>613</v>
+        <v>642</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -20460,7 +21388,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>614</v>
+        <v>643</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -20492,7 +21420,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>615</v>
+        <v>644</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -20524,7 +21452,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -20556,7 +21484,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>617</v>
+        <v>646</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -20588,7 +21516,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>618</v>
+        <v>647</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -20620,7 +21548,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -20652,7 +21580,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -20684,7 +21612,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>621</v>
+        <v>650</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -20716,7 +21644,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>622</v>
+        <v>651</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -20748,7 +21676,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -20780,7 +21708,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>624</v>
+        <v>653</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -8114,7 +8114,7 @@
       </c>
       <c r="D237" s="3" t="inlineStr">
         <is>
-          <t>Finance and HR paid people together for the first time, and each saw the other work under pressure.</t>
+          <t>Finance, HR and IT worked the problem together, and each saw the others work under pressure.</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr"/>
@@ -8818,7 +8818,7 @@
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>You and HR settled who decides before the CEO had to ask.</t>
+          <t>The CEO asked who was leading and got one answer.</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr"/>

--- a/docs/app-text.xlsx
+++ b/docs/app-text.xlsx
@@ -14669,7 +14669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page · after answering Yes</t>
+          <t>Confirm page · after confirming, when the file is sent (after the file name)</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -16084,7 +16084,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>You did it.</t>
+          <t xml:space="preserve"> is on its way to your inbox. If it hasn't arrived in a few minutes, check your spam folder.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"You did it.\""}</t>
+          <t>{"kind": "code", "raw": "\" is on its way to your inbox. If it hasn't arrived in a few minutes, check your spam folder.\""}</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16106,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page · after answering Partly</t>
+          <t>Follow-up page · after answering Yes</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>You did part of it.</t>
+          <t>You did it.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"You did part of it.\""}</t>
+          <t>{"kind": "code", "raw": "\"You did it.\""}</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page · after answering Not yet</t>
+          <t>Follow-up page · after answering Partly</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -16148,7 +16148,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Not yet.</t>
+          <t>You did part of it.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -16160,7 +16160,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Not yet.\""}</t>
+          <t>{"kind": "code", "raw": "\"You did part of it.\""}</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page · after answering (end)</t>
+          <t>Follow-up page · after answering Not yet</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> That's saved with your answers for this file.</t>
+          <t>Not yet.</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -16192,7 +16192,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\" That's saved with your answers for this file.\""}</t>
+          <t>{"kind": "code", "raw": "\"Not yet.\""}</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page (then the file name)</t>
+          <t>Follow-up page · after answering (end)</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 days ago, at the end of </t>
+          <t xml:space="preserve"> That's saved with your answers for this file.</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"30 days ago, at the end of \""}</t>
+          <t>{"kind": "code", "raw": "\" That's saved with your answers for this file.\""}</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page (end)</t>
+          <t>Follow-up page (then the file name)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -16244,7 +16244,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>, you chose one thing to take back.</t>
+          <t xml:space="preserve">30 days ago, at the end of </t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -16256,7 +16256,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\", you chose one thing to take back.\""}</t>
+          <t>{"kind": "code", "raw": "\"30 days ago, at the end of \""}</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page · answers deleted</t>
+          <t>Follow-up page (end)</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -16276,19 +16276,19 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>There's nothing to answer for this file any more.</t>
+          <t>, you chose one thing to take back.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>backend/src/service.ts</t>
+          <t>site/js/pages.js</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"There's nothing to answer for this file any more.\""}</t>
+          <t>{"kind": "code", "raw": "\", you chose one thing to take back.\""}</t>
         </is>
       </c>
     </row>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Follow-up page</t>
+          <t>Follow-up page · answers deleted</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Please choose one of the answers.</t>
+          <t>There's nothing to answer for this file any more.</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Please choose one of the answers.\""}</t>
+          <t>{"kind": "code", "raw": "\"There's nothing to answer for this file any more.\""}</t>
         </is>
       </c>
     </row>
@@ -16330,7 +16330,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Message · expired link</t>
+          <t>Follow-up page</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.</t>
+          <t>Please choose one of the answers.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.\""}</t>
+          <t>{"kind": "code", "raw": "\"Please choose one of the answers.\""}</t>
         </is>
       </c>
     </row>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Message · too many tries</t>
+          <t>Message · expired link</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Too many requests. Please wait a little and try again.</t>
+          <t>This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Too many requests. Please wait a little and try again.\""}</t>
+          <t>{"kind": "code", "raw": "\"This link has expired or isn't valid. Reply to any Monday After email and we'll send you a fresh one.\""}</t>
         </is>
       </c>
     </row>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Sign-up page · busy</t>
+          <t>Message · too many tries</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>We're getting a lot of sign-ups right now. Please try again in an hour.</t>
+          <t>Too many requests. Please wait a little and try again.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"We're getting a lot of sign-ups right now. Please try again in an hour.\""}</t>
+          <t>{"kind": "code", "raw": "\"Too many requests. Please wait a little and try again.\""}</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>App · email me my flight recorder, nothing saved</t>
+          <t>Sign-up page · busy</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>There's no saved flight recorder for this file.</t>
+          <t>We're getting a lot of sign-ups right now. Please try again in an hour.</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"There's no saved flight recorder for this file.\""}</t>
+          <t>{"kind": "code", "raw": "\"We're getting a lot of sign-ups right now. Please try again in an hour.\""}</t>
         </is>
       </c>
     </row>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Manage page</t>
+          <t>App · email me my flight recorder, nothing saved</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>You're unsubscribed, so there's nothing to pause.</t>
+          <t>There's no saved flight recorder for this file.</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -16480,7 +16480,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"You're unsubscribed, so there's nothing to pause.\""}</t>
+          <t>{"kind": "code", "raw": "\"There's no saved flight recorder for this file.\""}</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Sign-up page · empty email</t>
+          <t>Manage page</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -16500,19 +16500,19 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Email is missing</t>
+          <t>You're unsubscribed, so there's nothing to pause.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>backend/src/validate.ts</t>
+          <t>backend/src/service.ts</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Email is missing\""}</t>
+          <t>{"kind": "code", "raw": "\"You're unsubscribed, so there's nothing to pause.\""}</t>
         </is>
       </c>
     </row>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Sign-up page · bad email</t>
+          <t>Sign-up page · empty email</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>That doesn't look like an email address</t>
+          <t>Email is missing</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"That doesn't look like an email address\""}</t>
+          <t>{"kind": "code", "raw": "\"Email is missing\""}</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Flight recorder · too long (then a number)</t>
+          <t>Sign-up page · bad email</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Please keep each entry under </t>
+          <t>That doesn't look like an email address</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>{"kind": "code", "raw": "\"Please keep each entry under \""}</t>
+          <t>{"kind": "code", "raw": "\"That doesn't look like an email address\""}</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Flight recorder · first hour empty</t>
+          <t>Flight recorder · too long (then a number)</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Please write something for the first hour</t>
+          <t xml:space="preserve">Please keep each entry under </t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -16607,6 +16607,38 @@
         </is>
       </c>
       <c r="H60" t="inlineStr">
+        <is>
+          <t>{"kind": "code", "raw": "\"Please keep each entry under \""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Flight recorder · first hour empty</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Please write something for the first hour</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>backend/src/validate.ts</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
         <is>
           <t>{"kind": "code", "raw": "\"Please write something for the first hour\""}</t>
         </is>
@@ -16680,7 +16712,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -16712,7 +16744,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -16744,7 +16776,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -16776,7 +16808,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -16808,7 +16840,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -16840,7 +16872,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -16872,7 +16904,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -16904,7 +16936,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -16936,7 +16968,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -16968,7 +17000,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -17000,7 +17032,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -17032,7 +17064,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -17064,7 +17096,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -17096,7 +17128,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -17128,7 +17160,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -17160,7 +17192,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -17192,7 +17224,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -17224,7 +17256,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -17256,7 +17288,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -17288,7 +17320,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -17320,7 +17352,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -17352,7 +17384,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -17384,7 +17416,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -17416,7 +17448,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -17448,7 +17480,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -17480,7 +17512,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -17512,7 +17544,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -17544,7 +17576,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17608,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -17608,7 +17640,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -17640,7 +17672,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -17672,7 +17704,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -17704,7 +17736,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -17736,7 +17768,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -17768,7 +17800,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -17800,7 +17832,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -17832,7 +17864,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -17864,7 +17896,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -17896,7 +17928,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -17928,7 +17960,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -17960,7 +17992,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -17992,7 +18024,7 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -18024,7 +18056,7 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -18056,7 +18088,7 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -18088,7 +18120,7 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -18120,7 +18152,7 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -18152,7 +18184,7 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -18184,7 +18216,7 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -18216,7 +18248,7 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -18248,7 +18280,7 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -18280,7 +18312,7 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -18312,7 +18344,7 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -18344,7 +18376,7 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -18376,7 +18408,7 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -18408,7 +18440,7 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -18440,7 +18472,7 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -18472,7 +18504,7 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -18504,7 +18536,7 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -18536,7 +18568,7 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -18568,7 +18600,7 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -18600,7 +18632,7 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -18632,7 +18664,7 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -18664,7 +18696,7 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -18696,7 +18728,7 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -18728,7 +18760,7 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -18760,7 +18792,7 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -18792,7 +18824,7 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -18824,7 +18856,7 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -18856,7 +18888,7 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -18888,7 +18920,7 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -18920,7 +18952,7 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -18952,7 +18984,7 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -18984,7 +19016,7 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -19016,7 +19048,7 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -19048,7 +19080,7 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
@@ -19080,7 +19112,7 @@
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
@@ -19112,7 +19144,7 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
@@ -19144,7 +19176,7 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -19176,7 +19208,7 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
@@ -19208,7 +19240,7 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
@@ -19240,7 +19272,7 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
@@ -19272,7 +19304,7 @@
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
@@ -19304,7 +19336,7 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
@@ -19336,7 +19368,7 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
@@ -19368,7 +19400,7 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
@@ -19400,7 +19432,7 @@
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
@@ -19432,7 +19464,7 @@
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
@@ -19464,7 +19496,7 @@
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
@@ -19496,7 +19528,7 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
@@ -19528,7 +19560,7 @@
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
@@ -19560,7 +19592,7 @@
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
@@ -19592,7 +19624,7 @@
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
@@ -19624,7 +19656,7 @@
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
@@ -19656,7 +19688,7 @@
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
@@ -19754,7 +19786,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -19786,7 +19818,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -19818,7 +19850,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -19850,7 +19882,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -19882,7 +19914,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -19914,7 +19946,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -19946,7 +19978,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -19978,7 +20010,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -20010,7 +20042,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -20042,7 +20074,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -20074,7 +20106,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -20106,7 +20138,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -20138,7 +20170,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -20170,7 +20202,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -20202,7 +20234,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -20234,7 +20266,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -20266,7 +20298,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -20298,7 +20330,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -20330,7 +20362,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -20428,7 +20460,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -20460,7 +20492,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -20492,7 +20524,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -20524,7 +20556,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -20556,7 +20588,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -20588,7 +20620,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -20620,7 +20652,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -20652,7 +20684,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -20684,7 +20716,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -20716,7 +20748,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -20748,7 +20780,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -20780,7 +20812,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -20812,7 +20844,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -20844,7 +20876,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -20876,7 +20908,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -20908,7 +20940,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -20940,7 +20972,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -20972,7 +21004,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -21004,7 +21036,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -21036,7 +21068,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -21068,7 +21100,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -21100,7 +21132,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -21132,7 +21164,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -21164,7 +21196,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -21196,7 +21228,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -21228,7 +21260,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -21260,7 +21292,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -21292,7 +21324,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -21324,7 +21356,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -21356,7 +21388,7 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -21388,7 +21420,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -21420,7 +21452,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -21452,7 +21484,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -21484,7 +21516,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -21516,7 +21548,7 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -21548,7 +21580,7 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -21580,7 +21612,7 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -21612,7 +21644,7 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -21644,7 +21676,7 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -21676,7 +21708,7 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -21708,7 +21740,7 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
